--- a/adopt_net0/database/data/Components_database.xlsx
+++ b/adopt_net0/database/data/Components_database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Technologies" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Networks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technologies" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Networks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/adopt_net0/database/data/Components_database.xlsx
+++ b/adopt_net0/database/data/Components_database.xlsx
@@ -766,7 +766,7 @@
       </c>
       <c r="AW2" s="2" t="inlineStr">
         <is>
-          <t>plant_size</t>
+          <t>el_consumption_compression</t>
         </is>
       </c>
       <c r="AX2" s="2" t="inlineStr">
@@ -1703,10 +1703,8 @@
       <c r="AV4" t="n">
         <v>10800000</v>
       </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
+      <c r="AW4" t="n">
+        <v>0.09175</v>
       </c>
       <c r="AX4" t="n">
         <v>0.9</v>
@@ -1950,10 +1948,8 @@
       <c r="AV5" t="n">
         <v>11100000</v>
       </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
+      <c r="AW5" t="n">
+        <v>0.09175</v>
       </c>
       <c r="AX5" t="n">
         <v>0.9</v>
@@ -2197,10 +2193,8 @@
       <c r="AV6" t="n">
         <v>2170000</v>
       </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
+      <c r="AW6" t="n">
+        <v>0.09175</v>
       </c>
       <c r="AX6" t="n">
         <v>0.9</v>

--- a/adopt_net0/database/data/Components_database.xlsx
+++ b/adopt_net0/database/data/Components_database.xlsx
@@ -527,49 +527,54 @@
           <t>Performance</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Flow_capacity_relation</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>ScalingFactors</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>ScalingFactors</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>Flexibility</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>Flow_capacity_relation</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>Performance</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>Flexibility</t>
         </is>
       </c>
     </row>
@@ -766,7 +771,7 @@
       </c>
       <c r="AW2" s="2" t="inlineStr">
         <is>
-          <t>plant_size</t>
+          <t>el_consumption_compression</t>
         </is>
       </c>
       <c r="AX2" s="2" t="inlineStr">
@@ -911,397 +916,397 @@
       </c>
       <c r="CA2" s="2" t="inlineStr">
         <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="CB2" s="2" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="CC2" s="2" t="inlineStr">
+        <is>
+          <t>charge_rate</t>
+        </is>
+      </c>
+      <c r="CD2" s="2" t="inlineStr">
+        <is>
+          <t>discharge_rate</t>
+        </is>
+      </c>
+      <c r="CE2" s="2" t="inlineStr">
+        <is>
+          <t>capex_charging_rate</t>
+        </is>
+      </c>
+      <c r="CF2" s="2" t="inlineStr">
+        <is>
+          <t>capex_discharging_rate</t>
+        </is>
+      </c>
+      <c r="CG2" s="2" t="inlineStr">
+        <is>
           <t>performance.out.nitrogen</t>
         </is>
       </c>
-      <c r="CB2" s="2" t="inlineStr">
+      <c r="CH2" s="2" t="inlineStr">
         <is>
           <t>const_capex_aux</t>
         </is>
       </c>
-      <c r="CC2" s="2" t="inlineStr">
+      <c r="CI2" s="2" t="inlineStr">
         <is>
           <t>const_input_output</t>
         </is>
       </c>
-      <c r="CD2" s="2" t="inlineStr">
+      <c r="CJ2" s="2" t="inlineStr">
         <is>
           <t>const_max_input</t>
         </is>
       </c>
-      <c r="CE2" s="2" t="inlineStr">
+      <c r="CK2" s="2" t="inlineStr">
         <is>
           <t>const_opex_variable</t>
         </is>
       </c>
-      <c r="CF2" s="2" t="inlineStr">
+      <c r="CL2" s="2" t="inlineStr">
         <is>
           <t>const_opex_fixed</t>
         </is>
       </c>
-      <c r="CG2" s="2" t="inlineStr">
+      <c r="CM2" s="2" t="inlineStr">
         <is>
           <t>performance.out.methanol</t>
         </is>
       </c>
-      <c r="CH2" s="2" t="inlineStr">
+      <c r="CN2" s="2" t="inlineStr">
         <is>
           <t>performance.out.CO2</t>
         </is>
       </c>
-      <c r="CI2" s="2" t="inlineStr">
+      <c r="CO2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.MPW</t>
         </is>
       </c>
-      <c r="CJ2" s="2" t="inlineStr">
+      <c r="CP2" s="2" t="inlineStr">
         <is>
           <t>ccs.possible</t>
         </is>
       </c>
-      <c r="CK2" s="2" t="inlineStr">
+      <c r="CQ2" s="2" t="inlineStr">
         <is>
           <t>ccs.co2_concentration</t>
         </is>
       </c>
-      <c r="CL2" s="2" t="inlineStr">
+      <c r="CR2" s="2" t="inlineStr">
         <is>
           <t>ccs.ccs_type</t>
         </is>
       </c>
-      <c r="CM2" s="2" t="inlineStr">
+      <c r="CS2" s="2" t="inlineStr">
         <is>
           <t>performance.out.ethylene</t>
         </is>
       </c>
-      <c r="CN2" s="2" t="inlineStr">
+      <c r="CT2" s="2" t="inlineStr">
         <is>
           <t>performance.out.hydrogen</t>
         </is>
       </c>
-      <c r="CO2" s="2" t="inlineStr">
+      <c r="CU2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.CO2</t>
         </is>
       </c>
-      <c r="CP2" s="2" t="inlineStr">
+      <c r="CV2" s="2" t="inlineStr">
         <is>
           <t>performance.out.olefins</t>
         </is>
       </c>
-      <c r="CQ2" s="2" t="inlineStr">
+      <c r="CW2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.naphtha</t>
         </is>
       </c>
-      <c r="CR2" s="2" t="inlineStr">
+      <c r="CX2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.steam</t>
         </is>
       </c>
-      <c r="CS2" s="2" t="inlineStr">
+      <c r="CY2" s="2" t="inlineStr">
         <is>
           <t>performance.out.steam</t>
         </is>
       </c>
-      <c r="CT2" s="2" t="inlineStr">
+      <c r="CZ2" s="2" t="inlineStr">
         <is>
           <t>standby_power_carrier</t>
         </is>
       </c>
-      <c r="CU2" s="2" t="inlineStr">
+      <c r="DA2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.hydrogen</t>
         </is>
       </c>
-      <c r="CV2" s="2" t="inlineStr">
+      <c r="DB2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.feedgas</t>
         </is>
       </c>
-      <c r="CW2" s="2" t="inlineStr">
+      <c r="DC2" s="2" t="inlineStr">
         <is>
           <t>performance.out.syngas</t>
         </is>
       </c>
-      <c r="CX2" s="2" t="inlineStr">
+      <c r="DD2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.ethanol</t>
         </is>
       </c>
-      <c r="CY2" s="2" t="inlineStr">
+      <c r="DE2" s="2" t="inlineStr">
         <is>
           <t>performance.out.crackedgas</t>
         </is>
       </c>
-      <c r="CZ2" s="2" t="inlineStr">
+      <c r="DF2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.crackedgas</t>
         </is>
       </c>
-      <c r="DA2" s="2" t="inlineStr">
+      <c r="DG2" s="2" t="inlineStr">
         <is>
           <t>performance.out.gas</t>
         </is>
       </c>
-      <c r="DB2" s="2" t="inlineStr">
+      <c r="DH2" s="2" t="inlineStr">
         <is>
           <t>performance.out.ammonia</t>
         </is>
       </c>
-      <c r="DC2" s="2" t="inlineStr">
+      <c r="DI2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.HBfeed</t>
         </is>
       </c>
-      <c r="DD2" s="2" t="inlineStr">
+      <c r="DJ2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.syngas</t>
         </is>
       </c>
-      <c r="DE2" s="2" t="inlineStr">
+      <c r="DK2" s="2" t="inlineStr">
         <is>
           <t>performance.out.BTX</t>
         </is>
       </c>
-      <c r="DF2" s="2" t="inlineStr">
+      <c r="DL2" s="2" t="inlineStr">
         <is>
           <t>performance.out.LPG</t>
         </is>
       </c>
-      <c r="DG2" s="2" t="inlineStr">
+      <c r="DM2" s="2" t="inlineStr">
         <is>
           <t>performance.out.pentane</t>
         </is>
       </c>
-      <c r="DH2" s="2" t="inlineStr">
+      <c r="DN2" s="2" t="inlineStr">
         <is>
           <t>performance.out.heatlowT</t>
         </is>
       </c>
-      <c r="DI2" s="2" t="inlineStr">
+      <c r="DO2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.methanol</t>
         </is>
       </c>
-      <c r="DJ2" s="2" t="inlineStr">
+      <c r="DP2" s="2" t="inlineStr">
         <is>
           <t>performance.out.propylene</t>
         </is>
       </c>
-      <c r="DK2" s="2" t="inlineStr">
+      <c r="DQ2" s="2" t="inlineStr">
         <is>
           <t>performance.out.crackergas</t>
         </is>
       </c>
-      <c r="DL2" s="2" t="inlineStr">
+      <c r="DR2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.olefins</t>
         </is>
       </c>
-      <c r="DM2" s="2" t="inlineStr">
+      <c r="DS2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.propane</t>
         </is>
       </c>
-      <c r="DN2" s="2" t="inlineStr">
+      <c r="DT2" s="2" t="inlineStr">
         <is>
           <t>performance.out.HBfeed</t>
         </is>
       </c>
-      <c r="DO2" s="2" t="inlineStr">
+      <c r="DU2" s="2" t="inlineStr">
         <is>
           <t>CAPEX_model</t>
         </is>
       </c>
-      <c r="DP2" s="2" t="inlineStr">
+      <c r="DV2" s="2" t="inlineStr">
         <is>
           <t>unit_CAPEX</t>
         </is>
       </c>
-      <c r="DQ2" s="2" t="inlineStr">
+      <c r="DW2" s="2" t="inlineStr">
         <is>
           <t>fix_CAPEX</t>
         </is>
       </c>
-      <c r="DR2" s="2" t="inlineStr">
+      <c r="DX2" s="2" t="inlineStr">
         <is>
           <t>piecewise_CAPEX.bp_x</t>
         </is>
       </c>
-      <c r="DS2" s="2" t="inlineStr">
+      <c r="DY2" s="2" t="inlineStr">
         <is>
           <t>piecewise_CAPEX.bp_y</t>
         </is>
       </c>
-      <c r="DT2" s="2" t="inlineStr">
+      <c r="DZ2" s="2" t="inlineStr">
         <is>
           <t>OPEX_variable</t>
         </is>
       </c>
-      <c r="DU2" s="2" t="inlineStr">
+      <c r="EA2" s="2" t="inlineStr">
         <is>
           <t>OPEX_fixed</t>
         </is>
       </c>
-      <c r="DV2" s="2" t="inlineStr">
+      <c r="EB2" s="2" t="inlineStr">
         <is>
           <t>steam_production</t>
         </is>
       </c>
-      <c r="DW2" s="2" t="inlineStr">
+      <c r="EC2" s="2" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="DX2" s="2" t="inlineStr">
+      <c r="ED2" s="2" t="inlineStr">
         <is>
           <t>steam_turbine_generator_efficiency</t>
         </is>
       </c>
-      <c r="DY2" s="2" t="inlineStr">
+      <c r="EE2" s="2" t="inlineStr">
         <is>
           <t>size_db</t>
         </is>
       </c>
-      <c r="DZ2" s="2" t="inlineStr">
+      <c r="EF2" s="2" t="inlineStr">
         <is>
           <t>size_ohb</t>
         </is>
       </c>
-      <c r="EA2" s="2" t="inlineStr">
+      <c r="EG2" s="2" t="inlineStr">
         <is>
           <t>max_h2_in</t>
         </is>
       </c>
-      <c r="EB2" s="2" t="inlineStr">
+      <c r="EH2" s="2" t="inlineStr">
         <is>
           <t>max_h2_in_gt</t>
         </is>
       </c>
-      <c r="EC2" s="2" t="inlineStr">
+      <c r="EI2" s="2" t="inlineStr">
         <is>
           <t>rated_power</t>
         </is>
       </c>
-      <c r="ED2" s="2" t="inlineStr">
+      <c r="EJ2" s="2" t="inlineStr">
         <is>
           <t>in_min</t>
         </is>
       </c>
-      <c r="EE2" s="2" t="inlineStr">
+      <c r="EK2" s="2" t="inlineStr">
         <is>
           <t>in_max</t>
         </is>
       </c>
-      <c r="EF2" s="2" t="inlineStr">
+      <c r="EL2" s="2" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="EG2" s="2" t="inlineStr">
+      <c r="EM2" s="2" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="EH2" s="2" t="inlineStr">
+      <c r="EN2" s="2" t="inlineStr">
         <is>
           <t>gamma</t>
         </is>
       </c>
-      <c r="EI2" s="2" t="inlineStr">
+      <c r="EO2" s="2" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="EJ2" s="2" t="inlineStr">
+      <c r="EP2" s="2" t="inlineStr">
         <is>
           <t>T_iso</t>
         </is>
       </c>
-      <c r="EK2" s="2" t="inlineStr">
+      <c r="EQ2" s="2" t="inlineStr">
         <is>
           <t>epsilon</t>
         </is>
       </c>
-      <c r="EL2" s="2" t="inlineStr">
+      <c r="ER2" s="2" t="inlineStr">
         <is>
           <t>max_H2_admixture</t>
         </is>
       </c>
-      <c r="EM2" s="2" t="inlineStr">
+      <c r="ES2" s="2" t="inlineStr">
         <is>
           <t>max_input.hydrogen</t>
         </is>
       </c>
-      <c r="EN2" s="2" t="inlineStr">
+      <c r="ET2" s="2" t="inlineStr">
         <is>
           <t>ramping_rate</t>
         </is>
       </c>
-      <c r="EO2" s="2" t="inlineStr">
+      <c r="EU2" s="2" t="inlineStr">
         <is>
           <t>curtailment</t>
         </is>
       </c>
-      <c r="EP2" s="2" t="inlineStr">
+      <c r="EV2" s="2" t="inlineStr">
         <is>
           <t>var_capex_aux</t>
         </is>
       </c>
-      <c r="EQ2" s="2" t="inlineStr">
+      <c r="EW2" s="2" t="inlineStr">
         <is>
           <t>performance.energy_consumption.in.electricity</t>
         </is>
       </c>
-      <c r="ER2" s="2" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="ES2" s="2" t="inlineStr">
+      <c r="EX2" s="2" t="inlineStr">
         <is>
           <t>injection_capacity_is_decision_var</t>
         </is>
       </c>
-      <c r="ET2" s="2" t="inlineStr">
+      <c r="EY2" s="2" t="inlineStr">
         <is>
           <t>injection_rate_max</t>
         </is>
       </c>
-      <c r="EU2" s="2" t="inlineStr">
+      <c r="EZ2" s="2" t="inlineStr">
         <is>
           <t>capex_injection_cap</t>
         </is>
       </c>
-      <c r="EV2" s="2" t="inlineStr">
+      <c r="FA2" s="2" t="inlineStr">
         <is>
           <t>allow_only_one_direction_precise</t>
-        </is>
-      </c>
-      <c r="EW2" s="2" t="inlineStr">
-        <is>
-          <t>power_energy_ratio</t>
-        </is>
-      </c>
-      <c r="EX2" s="2" t="inlineStr">
-        <is>
-          <t>charge_rate</t>
-        </is>
-      </c>
-      <c r="EY2" s="2" t="inlineStr">
-        <is>
-          <t>discharge_rate</t>
-        </is>
-      </c>
-      <c r="EZ2" s="2" t="inlineStr">
-        <is>
-          <t>capex_charging_power</t>
-        </is>
-      </c>
-      <c r="FA2" s="2" t="inlineStr">
-        <is>
-          <t>capex_discharging_power</t>
         </is>
       </c>
     </row>
@@ -1374,8 +1379,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1703,10 +1710,8 @@
       <c r="AV4" t="n">
         <v>10800000</v>
       </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
+      <c r="AW4" t="n">
+        <v>0.09175</v>
       </c>
       <c r="AX4" t="n">
         <v>0.9</v>
@@ -1950,10 +1955,8 @@
       <c r="AV5" t="n">
         <v>11100000</v>
       </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
+      <c r="AW5" t="n">
+        <v>0.09175</v>
       </c>
       <c r="AX5" t="n">
         <v>0.9</v>
@@ -2197,10 +2200,8 @@
       <c r="AV6" t="n">
         <v>2170000</v>
       </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
+      <c r="AW6" t="n">
+        <v>0.09175</v>
       </c>
       <c r="AX6" t="n">
         <v>0.9</v>
@@ -2635,8 +2636,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>2</v>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2908,8 +2911,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v>1</v>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3181,8 +3186,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S10" t="n">
-        <v>1</v>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3454,8 +3461,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S11" t="n">
-        <v>1</v>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3727,8 +3736,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>2</v>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4000,8 +4011,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>2</v>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4273,8 +4286,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>1</v>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4522,8 +4537,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S15" t="n">
-        <v>1</v>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4773,8 +4790,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>1</v>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -5024,8 +5043,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>1</v>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -5277,8 +5298,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S18" t="n">
-        <v>1</v>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -5554,8 +5577,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S19" t="n">
-        <v>1</v>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -6184,22 +6209,34 @@
       <c r="BV21" t="n">
         <v>0</v>
       </c>
-      <c r="BW21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
         <v>0</v>
       </c>
-      <c r="CA21" t="inlineStr"/>
-      <c r="CB21" t="inlineStr"/>
-      <c r="CC21" t="inlineStr"/>
-      <c r="CD21" t="inlineStr"/>
-      <c r="CE21" t="inlineStr"/>
-      <c r="CF21" t="inlineStr"/>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0</v>
+      </c>
       <c r="CG21" t="inlineStr"/>
       <c r="CH21" t="inlineStr"/>
       <c r="CI21" t="inlineStr"/>
@@ -6596,8 +6633,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S23" t="n">
-        <v>2</v>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -6720,32 +6759,32 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="inlineStr"/>
-      <c r="CA23" t="inlineStr">
+      <c r="CA23" t="inlineStr"/>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr">
         <is>
           <t>0, 4</t>
         </is>
       </c>
-      <c r="CB23" t="n">
+      <c r="CH23" t="n">
         <v>0.001</v>
       </c>
-      <c r="CC23" t="n">
+      <c r="CI23" t="n">
         <v>1</v>
       </c>
-      <c r="CD23" t="n">
+      <c r="CJ23" t="n">
         <v>1</v>
       </c>
-      <c r="CE23" t="n">
+      <c r="CK23" t="n">
         <v>1</v>
       </c>
-      <c r="CF23" t="n">
+      <c r="CL23" t="n">
         <v>1</v>
       </c>
-      <c r="CG23" t="inlineStr"/>
-      <c r="CH23" t="inlineStr"/>
-      <c r="CI23" t="inlineStr"/>
-      <c r="CJ23" t="inlineStr"/>
-      <c r="CK23" t="inlineStr"/>
-      <c r="CL23" t="inlineStr"/>
       <c r="CM23" t="inlineStr"/>
       <c r="CN23" t="inlineStr"/>
       <c r="CO23" t="inlineStr"/>
@@ -6879,8 +6918,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S24" t="n">
-        <v>2</v>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -7009,36 +7050,36 @@
       <c r="CD24" t="inlineStr"/>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="inlineStr"/>
-      <c r="CG24" t="inlineStr">
+      <c r="CG24" t="inlineStr"/>
+      <c r="CH24" t="inlineStr"/>
+      <c r="CI24" t="inlineStr"/>
+      <c r="CJ24" t="inlineStr"/>
+      <c r="CK24" t="inlineStr"/>
+      <c r="CL24" t="inlineStr"/>
+      <c r="CM24" t="inlineStr">
         <is>
           <t>0, 0.322</t>
         </is>
       </c>
-      <c r="CH24" t="inlineStr">
+      <c r="CN24" t="inlineStr">
         <is>
           <t>0, 0.272</t>
         </is>
       </c>
-      <c r="CI24" t="n">
+      <c r="CO24" t="n">
         <v>1</v>
       </c>
-      <c r="CJ24" t="n">
+      <c r="CP24" t="n">
         <v>1</v>
       </c>
-      <c r="CK24" t="n">
+      <c r="CQ24" t="n">
         <v>0.145</v>
       </c>
-      <c r="CL24" t="inlineStr">
+      <c r="CR24" t="inlineStr">
         <is>
           <t>MEA_large</t>
         </is>
       </c>
-      <c r="CM24" t="inlineStr"/>
-      <c r="CN24" t="inlineStr"/>
-      <c r="CO24" t="inlineStr"/>
-      <c r="CP24" t="inlineStr"/>
-      <c r="CQ24" t="inlineStr"/>
-      <c r="CR24" t="inlineStr"/>
       <c r="CS24" t="inlineStr"/>
       <c r="CT24" t="inlineStr"/>
       <c r="CU24" t="inlineStr"/>
@@ -7166,8 +7207,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S25" t="n">
-        <v>2</v>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -7304,25 +7347,25 @@
       <c r="CJ25" t="inlineStr"/>
       <c r="CK25" t="inlineStr"/>
       <c r="CL25" t="inlineStr"/>
-      <c r="CM25" t="inlineStr">
-        <is>
-          <t>0, 0.602</t>
-        </is>
-      </c>
-      <c r="CN25" t="inlineStr">
-        <is>
-          <t>0, 0.019</t>
-        </is>
-      </c>
-      <c r="CO25" t="n">
-        <v>1</v>
-      </c>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
       <c r="CP25" t="inlineStr"/>
       <c r="CQ25" t="inlineStr"/>
       <c r="CR25" t="inlineStr"/>
-      <c r="CS25" t="inlineStr"/>
-      <c r="CT25" t="inlineStr"/>
-      <c r="CU25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>0, 0.602</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
+          <t>0, 0.019</t>
+        </is>
+      </c>
+      <c r="CU25" t="n">
+        <v>1</v>
+      </c>
       <c r="CV25" t="inlineStr"/>
       <c r="CW25" t="inlineStr"/>
       <c r="CX25" t="inlineStr"/>
@@ -7447,8 +7490,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S26" t="n">
-        <v>1</v>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -7574,55 +7619,55 @@
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="inlineStr"/>
       <c r="CA26" t="inlineStr"/>
-      <c r="CB26" t="n">
+      <c r="CB26" t="inlineStr"/>
+      <c r="CC26" t="inlineStr"/>
+      <c r="CD26" t="inlineStr"/>
+      <c r="CE26" t="inlineStr"/>
+      <c r="CF26" t="inlineStr"/>
+      <c r="CG26" t="inlineStr"/>
+      <c r="CH26" t="n">
         <v>1</v>
       </c>
-      <c r="CC26" t="n">
+      <c r="CI26" t="n">
         <v>1</v>
       </c>
-      <c r="CD26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG26" t="inlineStr"/>
-      <c r="CH26" t="inlineStr"/>
-      <c r="CI26" t="inlineStr"/>
       <c r="CJ26" t="n">
         <v>1</v>
       </c>
       <c r="CK26" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="CL26" t="inlineStr">
-        <is>
-          <t>MEA_large</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="CL26" t="n">
+        <v>1</v>
       </c>
       <c r="CM26" t="inlineStr"/>
       <c r="CN26" t="inlineStr"/>
       <c r="CO26" t="inlineStr"/>
-      <c r="CP26" t="inlineStr">
-        <is>
-          <t>0, 1</t>
-        </is>
+      <c r="CP26" t="n">
+        <v>1</v>
       </c>
       <c r="CQ26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>0.082</v>
+        <v>0.062</v>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>MEA_large</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr"/>
       <c r="CT26" t="inlineStr"/>
       <c r="CU26" t="inlineStr"/>
-      <c r="CV26" t="inlineStr"/>
-      <c r="CW26" t="inlineStr"/>
-      <c r="CX26" t="inlineStr"/>
+      <c r="CV26" t="inlineStr">
+        <is>
+          <t>0, 1</t>
+        </is>
+      </c>
+      <c r="CW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX26" t="n">
+        <v>0.082</v>
+      </c>
       <c r="CY26" t="inlineStr"/>
       <c r="CZ26" t="inlineStr"/>
       <c r="DA26" t="inlineStr"/>
@@ -7744,8 +7789,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S27" t="n">
-        <v>2</v>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -7885,31 +7932,31 @@
       <c r="CM27" t="inlineStr"/>
       <c r="CN27" t="inlineStr"/>
       <c r="CO27" t="inlineStr"/>
-      <c r="CP27" t="inlineStr">
+      <c r="CP27" t="inlineStr"/>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="inlineStr"/>
+      <c r="CS27" t="inlineStr"/>
+      <c r="CT27" t="inlineStr"/>
+      <c r="CU27" t="inlineStr"/>
+      <c r="CV27" t="inlineStr">
         <is>
           <t>0, 1</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
+      <c r="CW27" t="n">
         <v>1</v>
       </c>
-      <c r="CR27" t="inlineStr"/>
-      <c r="CS27" t="inlineStr">
+      <c r="CX27" t="inlineStr"/>
+      <c r="CY27" t="inlineStr">
         <is>
           <t>0, 0.05</t>
         </is>
       </c>
-      <c r="CT27" t="inlineStr">
+      <c r="CZ27" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="CU27" t="inlineStr"/>
-      <c r="CV27" t="inlineStr"/>
-      <c r="CW27" t="inlineStr"/>
-      <c r="CX27" t="inlineStr"/>
-      <c r="CY27" t="inlineStr"/>
-      <c r="CZ27" t="inlineStr"/>
       <c r="DA27" t="inlineStr"/>
       <c r="DB27" t="inlineStr"/>
       <c r="DC27" t="inlineStr"/>
@@ -8029,8 +8076,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S28" t="n">
-        <v>2</v>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -8161,35 +8210,35 @@
       <c r="CD28" t="inlineStr"/>
       <c r="CE28" t="inlineStr"/>
       <c r="CF28" t="inlineStr"/>
-      <c r="CG28" t="inlineStr">
-        <is>
-          <t>0, 0.679</t>
-        </is>
-      </c>
+      <c r="CG28" t="inlineStr"/>
       <c r="CH28" t="inlineStr"/>
       <c r="CI28" t="inlineStr"/>
       <c r="CJ28" t="inlineStr"/>
       <c r="CK28" t="inlineStr"/>
       <c r="CL28" t="inlineStr"/>
-      <c r="CM28" t="inlineStr"/>
+      <c r="CM28" t="inlineStr">
+        <is>
+          <t>0, 0.679</t>
+        </is>
+      </c>
       <c r="CN28" t="inlineStr"/>
-      <c r="CO28" t="n">
-        <v>1</v>
-      </c>
+      <c r="CO28" t="inlineStr"/>
       <c r="CP28" t="inlineStr"/>
       <c r="CQ28" t="inlineStr"/>
       <c r="CR28" t="inlineStr"/>
       <c r="CS28" t="inlineStr"/>
       <c r="CT28" t="inlineStr"/>
       <c r="CU28" t="n">
-        <v>4.58</v>
+        <v>1</v>
       </c>
       <c r="CV28" t="inlineStr"/>
       <c r="CW28" t="inlineStr"/>
       <c r="CX28" t="inlineStr"/>
       <c r="CY28" t="inlineStr"/>
       <c r="CZ28" t="inlineStr"/>
-      <c r="DA28" t="inlineStr"/>
+      <c r="DA28" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DB28" t="inlineStr"/>
       <c r="DC28" t="inlineStr"/>
       <c r="DD28" t="inlineStr"/>
@@ -8308,8 +8357,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S29" t="n">
-        <v>2</v>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -8441,11 +8492,7 @@
       <c r="CE29" t="inlineStr"/>
       <c r="CF29" t="inlineStr"/>
       <c r="CG29" t="inlineStr"/>
-      <c r="CH29" t="inlineStr">
-        <is>
-          <t>0, 0.201</t>
-        </is>
-      </c>
+      <c r="CH29" t="inlineStr"/>
       <c r="CI29" t="inlineStr"/>
       <c r="CJ29" t="inlineStr"/>
       <c r="CK29" t="inlineStr"/>
@@ -8453,7 +8500,7 @@
       <c r="CM29" t="inlineStr"/>
       <c r="CN29" t="inlineStr">
         <is>
-          <t>0, 0.927</t>
+          <t>0, 0.201</t>
         </is>
       </c>
       <c r="CO29" t="inlineStr"/>
@@ -8463,19 +8510,23 @@
       <c r="CS29" t="inlineStr"/>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>0, 0.927</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr"/>
-      <c r="CV29" t="n">
-        <v>1</v>
-      </c>
+      <c r="CV29" t="inlineStr"/>
       <c r="CW29" t="inlineStr"/>
       <c r="CX29" t="inlineStr"/>
       <c r="CY29" t="inlineStr"/>
-      <c r="CZ29" t="inlineStr"/>
+      <c r="CZ29" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
       <c r="DA29" t="inlineStr"/>
-      <c r="DB29" t="inlineStr"/>
+      <c r="DB29" t="n">
+        <v>1</v>
+      </c>
       <c r="DC29" t="inlineStr"/>
       <c r="DD29" t="inlineStr"/>
       <c r="DE29" t="inlineStr"/>
@@ -8593,8 +8644,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S30" t="n">
-        <v>2</v>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -8738,26 +8791,26 @@
       <c r="CQ30" t="inlineStr"/>
       <c r="CR30" t="inlineStr"/>
       <c r="CS30" t="inlineStr"/>
-      <c r="CT30" t="inlineStr">
-        <is>
-          <t>electricity</t>
-        </is>
-      </c>
+      <c r="CT30" t="inlineStr"/>
       <c r="CU30" t="inlineStr"/>
-      <c r="CV30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW30" t="inlineStr">
-        <is>
-          <t>0, 0.187</t>
-        </is>
-      </c>
+      <c r="CV30" t="inlineStr"/>
+      <c r="CW30" t="inlineStr"/>
       <c r="CX30" t="inlineStr"/>
       <c r="CY30" t="inlineStr"/>
-      <c r="CZ30" t="inlineStr"/>
+      <c r="CZ30" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
       <c r="DA30" t="inlineStr"/>
-      <c r="DB30" t="inlineStr"/>
-      <c r="DC30" t="inlineStr"/>
+      <c r="DB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC30" t="inlineStr">
+        <is>
+          <t>0, 0.187</t>
+        </is>
+      </c>
       <c r="DD30" t="inlineStr"/>
       <c r="DE30" t="inlineStr"/>
       <c r="DF30" t="inlineStr"/>
@@ -8874,8 +8927,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S31" t="n">
-        <v>2</v>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -9012,32 +9067,32 @@
       <c r="CJ31" t="inlineStr"/>
       <c r="CK31" t="inlineStr"/>
       <c r="CL31" t="inlineStr"/>
-      <c r="CM31" t="inlineStr">
-        <is>
-          <t>0, 0.592</t>
-        </is>
-      </c>
+      <c r="CM31" t="inlineStr"/>
       <c r="CN31" t="inlineStr"/>
       <c r="CO31" t="inlineStr"/>
       <c r="CP31" t="inlineStr"/>
       <c r="CQ31" t="inlineStr"/>
-      <c r="CR31" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="CS31" t="inlineStr"/>
+      <c r="CR31" t="inlineStr"/>
+      <c r="CS31" t="inlineStr">
+        <is>
+          <t>0, 0.592</t>
+        </is>
+      </c>
       <c r="CT31" t="inlineStr"/>
       <c r="CU31" t="inlineStr"/>
       <c r="CV31" t="inlineStr"/>
       <c r="CW31" t="inlineStr"/>
       <c r="CX31" t="n">
-        <v>1</v>
+        <v>0.313</v>
       </c>
       <c r="CY31" t="inlineStr"/>
       <c r="CZ31" t="inlineStr"/>
       <c r="DA31" t="inlineStr"/>
       <c r="DB31" t="inlineStr"/>
       <c r="DC31" t="inlineStr"/>
-      <c r="DD31" t="inlineStr"/>
+      <c r="DD31" t="n">
+        <v>1</v>
+      </c>
       <c r="DE31" t="inlineStr"/>
       <c r="DF31" t="inlineStr"/>
       <c r="DG31" t="inlineStr"/>
@@ -9153,8 +9208,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S32" t="n">
-        <v>1</v>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -9298,29 +9355,29 @@
       <c r="CO32" t="inlineStr"/>
       <c r="CP32" t="inlineStr"/>
       <c r="CQ32" t="inlineStr"/>
-      <c r="CR32" t="n">
-        <v>0.431</v>
-      </c>
+      <c r="CR32" t="inlineStr"/>
       <c r="CS32" t="inlineStr"/>
       <c r="CT32" t="inlineStr"/>
       <c r="CU32" t="inlineStr"/>
       <c r="CV32" t="inlineStr"/>
       <c r="CW32" t="inlineStr"/>
-      <c r="CX32" t="inlineStr"/>
-      <c r="CY32" t="inlineStr">
-        <is>
-          <t>0, 1</t>
-        </is>
-      </c>
-      <c r="CZ32" t="n">
-        <v>1</v>
-      </c>
+      <c r="CX32" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="CY32" t="inlineStr"/>
+      <c r="CZ32" t="inlineStr"/>
       <c r="DA32" t="inlineStr"/>
       <c r="DB32" t="inlineStr"/>
       <c r="DC32" t="inlineStr"/>
       <c r="DD32" t="inlineStr"/>
-      <c r="DE32" t="inlineStr"/>
-      <c r="DF32" t="inlineStr"/>
+      <c r="DE32" t="inlineStr">
+        <is>
+          <t>0, 1</t>
+        </is>
+      </c>
+      <c r="DF32" t="n">
+        <v>1</v>
+      </c>
       <c r="DG32" t="inlineStr"/>
       <c r="DH32" t="inlineStr"/>
       <c r="DI32" t="inlineStr"/>
@@ -9434,8 +9491,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S33" t="n">
-        <v>1</v>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -9588,20 +9647,20 @@
       <c r="CV33" t="inlineStr"/>
       <c r="CW33" t="inlineStr"/>
       <c r="CX33" t="inlineStr"/>
-      <c r="CY33" t="inlineStr">
-        <is>
-          <t>0, 1</t>
-        </is>
-      </c>
-      <c r="CZ33" t="n">
-        <v>1</v>
-      </c>
+      <c r="CY33" t="inlineStr"/>
+      <c r="CZ33" t="inlineStr"/>
       <c r="DA33" t="inlineStr"/>
       <c r="DB33" t="inlineStr"/>
       <c r="DC33" t="inlineStr"/>
       <c r="DD33" t="inlineStr"/>
-      <c r="DE33" t="inlineStr"/>
-      <c r="DF33" t="inlineStr"/>
+      <c r="DE33" t="inlineStr">
+        <is>
+          <t>0, 1</t>
+        </is>
+      </c>
+      <c r="DF33" t="n">
+        <v>1</v>
+      </c>
       <c r="DG33" t="inlineStr"/>
       <c r="DH33" t="inlineStr"/>
       <c r="DI33" t="inlineStr"/>
@@ -9715,8 +9774,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S34" t="n">
-        <v>1</v>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -9857,39 +9918,39 @@
       <c r="CJ34" t="inlineStr"/>
       <c r="CK34" t="inlineStr"/>
       <c r="CL34" t="inlineStr"/>
-      <c r="CM34" t="inlineStr">
-        <is>
-          <t>0, 0.3025</t>
-        </is>
-      </c>
+      <c r="CM34" t="inlineStr"/>
       <c r="CN34" t="inlineStr"/>
       <c r="CO34" t="inlineStr"/>
       <c r="CP34" t="inlineStr"/>
       <c r="CQ34" t="inlineStr"/>
-      <c r="CR34" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="CS34" t="inlineStr"/>
+      <c r="CR34" t="inlineStr"/>
+      <c r="CS34" t="inlineStr">
+        <is>
+          <t>0, 0.3025</t>
+        </is>
+      </c>
       <c r="CT34" t="inlineStr"/>
       <c r="CU34" t="inlineStr"/>
       <c r="CV34" t="inlineStr"/>
       <c r="CW34" t="inlineStr"/>
-      <c r="CX34" t="inlineStr"/>
+      <c r="CX34" t="n">
+        <v>0.492</v>
+      </c>
       <c r="CY34" t="inlineStr"/>
-      <c r="CZ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="DA34" t="inlineStr">
-        <is>
-          <t>0, 2.3491</t>
-        </is>
-      </c>
+      <c r="CZ34" t="inlineStr"/>
+      <c r="DA34" t="inlineStr"/>
       <c r="DB34" t="inlineStr"/>
       <c r="DC34" t="inlineStr"/>
       <c r="DD34" t="inlineStr"/>
       <c r="DE34" t="inlineStr"/>
-      <c r="DF34" t="inlineStr"/>
-      <c r="DG34" t="inlineStr"/>
+      <c r="DF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG34" t="inlineStr">
+        <is>
+          <t>0, 2.3491</t>
+        </is>
+      </c>
       <c r="DH34" t="inlineStr"/>
       <c r="DI34" t="inlineStr"/>
       <c r="DJ34" t="inlineStr"/>
@@ -10002,8 +10063,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S35" t="n">
-        <v>2</v>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -10146,33 +10209,33 @@
       <c r="CP35" t="inlineStr"/>
       <c r="CQ35" t="inlineStr"/>
       <c r="CR35" t="inlineStr"/>
-      <c r="CS35" t="inlineStr">
-        <is>
-          <t>0, 0.114</t>
-        </is>
-      </c>
+      <c r="CS35" t="inlineStr"/>
       <c r="CT35" t="inlineStr"/>
       <c r="CU35" t="inlineStr"/>
       <c r="CV35" t="inlineStr"/>
       <c r="CW35" t="inlineStr"/>
       <c r="CX35" t="inlineStr"/>
-      <c r="CY35" t="inlineStr"/>
+      <c r="CY35" t="inlineStr">
+        <is>
+          <t>0, 0.114</t>
+        </is>
+      </c>
       <c r="CZ35" t="inlineStr"/>
       <c r="DA35" t="inlineStr"/>
-      <c r="DB35" t="inlineStr">
-        <is>
-          <t>0, 0.168</t>
-        </is>
-      </c>
-      <c r="DC35" t="n">
-        <v>1</v>
-      </c>
+      <c r="DB35" t="inlineStr"/>
+      <c r="DC35" t="inlineStr"/>
       <c r="DD35" t="inlineStr"/>
       <c r="DE35" t="inlineStr"/>
       <c r="DF35" t="inlineStr"/>
       <c r="DG35" t="inlineStr"/>
-      <c r="DH35" t="inlineStr"/>
-      <c r="DI35" t="inlineStr"/>
+      <c r="DH35" t="inlineStr">
+        <is>
+          <t>0, 0.168</t>
+        </is>
+      </c>
+      <c r="DI35" t="n">
+        <v>1</v>
+      </c>
       <c r="DJ35" t="inlineStr"/>
       <c r="DK35" t="inlineStr"/>
       <c r="DL35" t="inlineStr"/>
@@ -10283,8 +10346,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S36" t="n">
-        <v>2</v>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -10415,44 +10480,44 @@
       <c r="CD36" t="inlineStr"/>
       <c r="CE36" t="inlineStr"/>
       <c r="CF36" t="inlineStr"/>
-      <c r="CG36" t="inlineStr">
-        <is>
-          <t>0, 0.823</t>
-        </is>
-      </c>
+      <c r="CG36" t="inlineStr"/>
       <c r="CH36" t="inlineStr"/>
       <c r="CI36" t="inlineStr"/>
       <c r="CJ36" t="inlineStr"/>
       <c r="CK36" t="inlineStr"/>
       <c r="CL36" t="inlineStr"/>
-      <c r="CM36" t="inlineStr"/>
+      <c r="CM36" t="inlineStr">
+        <is>
+          <t>0, 0.823</t>
+        </is>
+      </c>
       <c r="CN36" t="inlineStr"/>
       <c r="CO36" t="inlineStr"/>
       <c r="CP36" t="inlineStr"/>
       <c r="CQ36" t="inlineStr"/>
-      <c r="CR36" t="n">
-        <v>0.572</v>
-      </c>
+      <c r="CR36" t="inlineStr"/>
       <c r="CS36" t="inlineStr"/>
       <c r="CT36" t="inlineStr"/>
       <c r="CU36" t="inlineStr"/>
       <c r="CV36" t="inlineStr"/>
       <c r="CW36" t="inlineStr"/>
-      <c r="CX36" t="inlineStr"/>
+      <c r="CX36" t="n">
+        <v>0.572</v>
+      </c>
       <c r="CY36" t="inlineStr"/>
       <c r="CZ36" t="inlineStr"/>
       <c r="DA36" t="inlineStr"/>
       <c r="DB36" t="inlineStr"/>
       <c r="DC36" t="inlineStr"/>
-      <c r="DD36" t="n">
-        <v>1</v>
-      </c>
+      <c r="DD36" t="inlineStr"/>
       <c r="DE36" t="inlineStr"/>
       <c r="DF36" t="inlineStr"/>
       <c r="DG36" t="inlineStr"/>
       <c r="DH36" t="inlineStr"/>
       <c r="DI36" t="inlineStr"/>
-      <c r="DJ36" t="inlineStr"/>
+      <c r="DJ36" t="n">
+        <v>1</v>
+      </c>
       <c r="DK36" t="inlineStr"/>
       <c r="DL36" t="inlineStr"/>
       <c r="DM36" t="inlineStr"/>
@@ -10562,8 +10627,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S37" t="n">
-        <v>1</v>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -10705,50 +10772,50 @@
       <c r="CO37" t="inlineStr"/>
       <c r="CP37" t="inlineStr"/>
       <c r="CQ37" t="inlineStr"/>
-      <c r="CR37" t="n">
-        <v>0.149</v>
-      </c>
+      <c r="CR37" t="inlineStr"/>
       <c r="CS37" t="inlineStr"/>
       <c r="CT37" t="inlineStr"/>
       <c r="CU37" t="inlineStr"/>
       <c r="CV37" t="inlineStr"/>
       <c r="CW37" t="inlineStr"/>
-      <c r="CX37" t="inlineStr"/>
+      <c r="CX37" t="n">
+        <v>0.149</v>
+      </c>
       <c r="CY37" t="inlineStr"/>
       <c r="CZ37" t="inlineStr"/>
       <c r="DA37" t="inlineStr"/>
       <c r="DB37" t="inlineStr"/>
       <c r="DC37" t="inlineStr"/>
       <c r="DD37" t="inlineStr"/>
-      <c r="DE37" t="inlineStr">
+      <c r="DE37" t="inlineStr"/>
+      <c r="DF37" t="inlineStr"/>
+      <c r="DG37" t="inlineStr"/>
+      <c r="DH37" t="inlineStr"/>
+      <c r="DI37" t="inlineStr"/>
+      <c r="DJ37" t="inlineStr"/>
+      <c r="DK37" t="inlineStr">
         <is>
           <t>0, 0.155</t>
         </is>
       </c>
-      <c r="DF37" t="inlineStr">
+      <c r="DL37" t="inlineStr">
         <is>
           <t>0, 0.196</t>
         </is>
       </c>
-      <c r="DG37" t="inlineStr">
+      <c r="DM37" t="inlineStr">
         <is>
           <t>0, 0.043</t>
         </is>
       </c>
-      <c r="DH37" t="inlineStr">
+      <c r="DN37" t="inlineStr">
         <is>
           <t>0, 0.236</t>
         </is>
       </c>
-      <c r="DI37" t="n">
+      <c r="DO37" t="n">
         <v>1</v>
       </c>
-      <c r="DJ37" t="inlineStr"/>
-      <c r="DK37" t="inlineStr"/>
-      <c r="DL37" t="inlineStr"/>
-      <c r="DM37" t="inlineStr"/>
-      <c r="DN37" t="inlineStr"/>
-      <c r="DO37" t="inlineStr"/>
       <c r="DP37" t="inlineStr"/>
       <c r="DQ37" t="inlineStr"/>
       <c r="DR37" t="inlineStr"/>
@@ -10853,8 +10920,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S38" t="n">
-        <v>2</v>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -10991,17 +11060,17 @@
       <c r="CJ38" t="inlineStr"/>
       <c r="CK38" t="inlineStr"/>
       <c r="CL38" t="inlineStr"/>
-      <c r="CM38" t="inlineStr">
-        <is>
-          <t>0, 0.163</t>
-        </is>
-      </c>
+      <c r="CM38" t="inlineStr"/>
       <c r="CN38" t="inlineStr"/>
       <c r="CO38" t="inlineStr"/>
       <c r="CP38" t="inlineStr"/>
       <c r="CQ38" t="inlineStr"/>
       <c r="CR38" t="inlineStr"/>
-      <c r="CS38" t="inlineStr"/>
+      <c r="CS38" t="inlineStr">
+        <is>
+          <t>0, 0.163</t>
+        </is>
+      </c>
       <c r="CT38" t="inlineStr"/>
       <c r="CU38" t="inlineStr"/>
       <c r="CV38" t="inlineStr"/>
@@ -11017,20 +11086,20 @@
       <c r="DF38" t="inlineStr"/>
       <c r="DG38" t="inlineStr"/>
       <c r="DH38" t="inlineStr"/>
-      <c r="DI38" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ38" t="inlineStr">
-        <is>
-          <t>0, 0.165</t>
-        </is>
-      </c>
+      <c r="DI38" t="inlineStr"/>
+      <c r="DJ38" t="inlineStr"/>
       <c r="DK38" t="inlineStr"/>
       <c r="DL38" t="inlineStr"/>
       <c r="DM38" t="inlineStr"/>
       <c r="DN38" t="inlineStr"/>
-      <c r="DO38" t="inlineStr"/>
-      <c r="DP38" t="inlineStr"/>
+      <c r="DO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP38" t="inlineStr">
+        <is>
+          <t>0, 0.165</t>
+        </is>
+      </c>
       <c r="DQ38" t="inlineStr"/>
       <c r="DR38" t="inlineStr"/>
       <c r="DS38" t="inlineStr"/>
@@ -11134,8 +11203,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S39" t="n">
-        <v>1</v>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -11261,55 +11332,55 @@
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="inlineStr"/>
       <c r="CA39" t="inlineStr"/>
-      <c r="CB39" t="n">
+      <c r="CB39" t="inlineStr"/>
+      <c r="CC39" t="inlineStr"/>
+      <c r="CD39" t="inlineStr"/>
+      <c r="CE39" t="inlineStr"/>
+      <c r="CF39" t="inlineStr"/>
+      <c r="CG39" t="inlineStr"/>
+      <c r="CH39" t="n">
         <v>1</v>
       </c>
-      <c r="CC39" t="n">
+      <c r="CI39" t="n">
         <v>1</v>
       </c>
-      <c r="CD39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG39" t="inlineStr"/>
-      <c r="CH39" t="inlineStr"/>
-      <c r="CI39" t="inlineStr"/>
       <c r="CJ39" t="n">
         <v>1</v>
       </c>
       <c r="CK39" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="CL39" t="inlineStr">
-        <is>
-          <t>MEA_large</t>
-        </is>
-      </c>
-      <c r="CM39" t="inlineStr">
-        <is>
-          <t>0, 0.3025</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="CL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM39" t="inlineStr"/>
       <c r="CN39" t="inlineStr"/>
       <c r="CO39" t="inlineStr"/>
-      <c r="CP39" t="inlineStr"/>
+      <c r="CP39" t="n">
+        <v>1</v>
+      </c>
       <c r="CQ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="CS39" t="inlineStr"/>
+        <v>0.062</v>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>MEA_large</t>
+        </is>
+      </c>
+      <c r="CS39" t="inlineStr">
+        <is>
+          <t>0, 0.3025</t>
+        </is>
+      </c>
       <c r="CT39" t="inlineStr"/>
       <c r="CU39" t="inlineStr"/>
       <c r="CV39" t="inlineStr"/>
-      <c r="CW39" t="inlineStr"/>
-      <c r="CX39" t="inlineStr"/>
+      <c r="CW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX39" t="n">
+        <v>0.082</v>
+      </c>
       <c r="CY39" t="inlineStr"/>
       <c r="CZ39" t="inlineStr"/>
       <c r="DA39" t="inlineStr"/>
@@ -11321,22 +11392,22 @@
       <c r="DG39" t="inlineStr"/>
       <c r="DH39" t="inlineStr"/>
       <c r="DI39" t="inlineStr"/>
-      <c r="DJ39" t="inlineStr">
-        <is>
-          <t>0, 0.1363</t>
-        </is>
-      </c>
-      <c r="DK39" t="inlineStr">
-        <is>
-          <t>0, 0.781</t>
-        </is>
-      </c>
+      <c r="DJ39" t="inlineStr"/>
+      <c r="DK39" t="inlineStr"/>
       <c r="DL39" t="inlineStr"/>
       <c r="DM39" t="inlineStr"/>
       <c r="DN39" t="inlineStr"/>
       <c r="DO39" t="inlineStr"/>
-      <c r="DP39" t="inlineStr"/>
-      <c r="DQ39" t="inlineStr"/>
+      <c r="DP39" t="inlineStr">
+        <is>
+          <t>0, 0.1363</t>
+        </is>
+      </c>
+      <c r="DQ39" t="inlineStr">
+        <is>
+          <t>0, 0.781</t>
+        </is>
+      </c>
       <c r="DR39" t="inlineStr"/>
       <c r="DS39" t="inlineStr"/>
       <c r="DT39" t="inlineStr"/>
@@ -11439,8 +11510,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S40" t="n">
-        <v>2</v>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -11577,34 +11650,34 @@
       <c r="CJ40" t="inlineStr"/>
       <c r="CK40" t="inlineStr"/>
       <c r="CL40" t="inlineStr"/>
-      <c r="CM40" t="inlineStr">
-        <is>
-          <t>0, 0.3025</t>
-        </is>
-      </c>
+      <c r="CM40" t="inlineStr"/>
       <c r="CN40" t="inlineStr"/>
       <c r="CO40" t="inlineStr"/>
       <c r="CP40" t="inlineStr"/>
-      <c r="CQ40" t="n">
-        <v>1</v>
-      </c>
+      <c r="CQ40" t="inlineStr"/>
       <c r="CR40" t="inlineStr"/>
       <c r="CS40" t="inlineStr">
         <is>
-          <t>0, 0.05</t>
-        </is>
-      </c>
-      <c r="CT40" t="inlineStr">
-        <is>
-          <t>electricity</t>
-        </is>
-      </c>
+          <t>0, 0.3025</t>
+        </is>
+      </c>
+      <c r="CT40" t="inlineStr"/>
       <c r="CU40" t="inlineStr"/>
       <c r="CV40" t="inlineStr"/>
-      <c r="CW40" t="inlineStr"/>
+      <c r="CW40" t="n">
+        <v>1</v>
+      </c>
       <c r="CX40" t="inlineStr"/>
-      <c r="CY40" t="inlineStr"/>
-      <c r="CZ40" t="inlineStr"/>
+      <c r="CY40" t="inlineStr">
+        <is>
+          <t>0, 0.05</t>
+        </is>
+      </c>
+      <c r="CZ40" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
       <c r="DA40" t="inlineStr"/>
       <c r="DB40" t="inlineStr"/>
       <c r="DC40" t="inlineStr"/>
@@ -11614,22 +11687,22 @@
       <c r="DG40" t="inlineStr"/>
       <c r="DH40" t="inlineStr"/>
       <c r="DI40" t="inlineStr"/>
-      <c r="DJ40" t="inlineStr">
-        <is>
-          <t>0, 0.1363</t>
-        </is>
-      </c>
-      <c r="DK40" t="inlineStr">
-        <is>
-          <t>0, 2.649</t>
-        </is>
-      </c>
+      <c r="DJ40" t="inlineStr"/>
+      <c r="DK40" t="inlineStr"/>
       <c r="DL40" t="inlineStr"/>
       <c r="DM40" t="inlineStr"/>
       <c r="DN40" t="inlineStr"/>
       <c r="DO40" t="inlineStr"/>
-      <c r="DP40" t="inlineStr"/>
-      <c r="DQ40" t="inlineStr"/>
+      <c r="DP40" t="inlineStr">
+        <is>
+          <t>0, 0.1363</t>
+        </is>
+      </c>
+      <c r="DQ40" t="inlineStr">
+        <is>
+          <t>0, 2.649</t>
+        </is>
+      </c>
       <c r="DR40" t="inlineStr"/>
       <c r="DS40" t="inlineStr"/>
       <c r="DT40" t="inlineStr"/>
@@ -11732,8 +11805,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S41" t="n">
-        <v>1</v>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -11868,28 +11943,28 @@
       <c r="CJ41" t="inlineStr"/>
       <c r="CK41" t="inlineStr"/>
       <c r="CL41" t="inlineStr"/>
-      <c r="CM41" t="inlineStr">
-        <is>
-          <t>0, 0.3025</t>
-        </is>
-      </c>
+      <c r="CM41" t="inlineStr"/>
       <c r="CN41" t="inlineStr"/>
       <c r="CO41" t="inlineStr"/>
       <c r="CP41" t="inlineStr"/>
       <c r="CQ41" t="inlineStr"/>
       <c r="CR41" t="inlineStr"/>
-      <c r="CS41" t="inlineStr"/>
-      <c r="CT41" t="inlineStr">
-        <is>
-          <t>electricity</t>
-        </is>
-      </c>
+      <c r="CS41" t="inlineStr">
+        <is>
+          <t>0, 0.3025</t>
+        </is>
+      </c>
+      <c r="CT41" t="inlineStr"/>
       <c r="CU41" t="inlineStr"/>
       <c r="CV41" t="inlineStr"/>
       <c r="CW41" t="inlineStr"/>
       <c r="CX41" t="inlineStr"/>
       <c r="CY41" t="inlineStr"/>
-      <c r="CZ41" t="inlineStr"/>
+      <c r="CZ41" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
       <c r="DA41" t="inlineStr"/>
       <c r="DB41" t="inlineStr"/>
       <c r="DC41" t="inlineStr"/>
@@ -11899,25 +11974,25 @@
       <c r="DG41" t="inlineStr"/>
       <c r="DH41" t="inlineStr"/>
       <c r="DI41" t="inlineStr"/>
-      <c r="DJ41" t="inlineStr">
-        <is>
-          <t>0, 0.1363</t>
-        </is>
-      </c>
-      <c r="DK41" t="inlineStr">
-        <is>
-          <t>0, 0.781</t>
-        </is>
-      </c>
-      <c r="DL41" t="n">
-        <v>1</v>
-      </c>
+      <c r="DJ41" t="inlineStr"/>
+      <c r="DK41" t="inlineStr"/>
+      <c r="DL41" t="inlineStr"/>
       <c r="DM41" t="inlineStr"/>
       <c r="DN41" t="inlineStr"/>
       <c r="DO41" t="inlineStr"/>
-      <c r="DP41" t="inlineStr"/>
-      <c r="DQ41" t="inlineStr"/>
-      <c r="DR41" t="inlineStr"/>
+      <c r="DP41" t="inlineStr">
+        <is>
+          <t>0, 0.1363</t>
+        </is>
+      </c>
+      <c r="DQ41" t="inlineStr">
+        <is>
+          <t>0, 0.781</t>
+        </is>
+      </c>
+      <c r="DR41" t="n">
+        <v>1</v>
+      </c>
       <c r="DS41" t="inlineStr"/>
       <c r="DT41" t="inlineStr"/>
       <c r="DU41" t="inlineStr"/>
@@ -12019,8 +12094,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S42" t="n">
-        <v>2</v>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -12149,32 +12226,32 @@
       <c r="CD42" t="inlineStr"/>
       <c r="CE42" t="inlineStr"/>
       <c r="CF42" t="inlineStr"/>
-      <c r="CG42" t="inlineStr">
+      <c r="CG42" t="inlineStr"/>
+      <c r="CH42" t="inlineStr"/>
+      <c r="CI42" t="inlineStr"/>
+      <c r="CJ42" t="inlineStr"/>
+      <c r="CK42" t="inlineStr"/>
+      <c r="CL42" t="inlineStr"/>
+      <c r="CM42" t="inlineStr">
         <is>
           <t>0, 1.47</t>
         </is>
       </c>
-      <c r="CH42" t="inlineStr"/>
-      <c r="CI42" t="n">
+      <c r="CN42" t="inlineStr"/>
+      <c r="CO42" t="n">
         <v>1</v>
       </c>
-      <c r="CJ42" t="n">
+      <c r="CP42" t="n">
         <v>1</v>
       </c>
-      <c r="CK42" t="n">
+      <c r="CQ42" t="n">
         <v>0.157</v>
       </c>
-      <c r="CL42" t="inlineStr">
+      <c r="CR42" t="inlineStr">
         <is>
           <t>MEA_large</t>
         </is>
       </c>
-      <c r="CM42" t="inlineStr"/>
-      <c r="CN42" t="inlineStr"/>
-      <c r="CO42" t="inlineStr"/>
-      <c r="CP42" t="inlineStr"/>
-      <c r="CQ42" t="inlineStr"/>
-      <c r="CR42" t="inlineStr"/>
       <c r="CS42" t="inlineStr"/>
       <c r="CT42" t="inlineStr"/>
       <c r="CU42" t="inlineStr"/>
@@ -12302,8 +12379,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S43" t="n">
-        <v>2</v>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -12441,23 +12520,23 @@
       <c r="CK43" t="inlineStr"/>
       <c r="CL43" t="inlineStr"/>
       <c r="CM43" t="inlineStr"/>
-      <c r="CN43" t="inlineStr">
-        <is>
-          <t>0, 0.776</t>
-        </is>
-      </c>
+      <c r="CN43" t="inlineStr"/>
       <c r="CO43" t="inlineStr"/>
       <c r="CP43" t="inlineStr"/>
       <c r="CQ43" t="inlineStr"/>
-      <c r="CR43" t="n">
-        <v>2.44</v>
-      </c>
+      <c r="CR43" t="inlineStr"/>
       <c r="CS43" t="inlineStr"/>
-      <c r="CT43" t="inlineStr"/>
+      <c r="CT43" t="inlineStr">
+        <is>
+          <t>0, 0.776</t>
+        </is>
+      </c>
       <c r="CU43" t="inlineStr"/>
       <c r="CV43" t="inlineStr"/>
       <c r="CW43" t="inlineStr"/>
-      <c r="CX43" t="inlineStr"/>
+      <c r="CX43" t="n">
+        <v>2.44</v>
+      </c>
       <c r="CY43" t="inlineStr"/>
       <c r="CZ43" t="inlineStr"/>
       <c r="DA43" t="inlineStr"/>
@@ -12469,22 +12548,22 @@
       <c r="DG43" t="inlineStr"/>
       <c r="DH43" t="inlineStr"/>
       <c r="DI43" t="inlineStr"/>
-      <c r="DJ43" t="inlineStr">
-        <is>
-          <t>0, 0.859</t>
-        </is>
-      </c>
+      <c r="DJ43" t="inlineStr"/>
       <c r="DK43" t="inlineStr"/>
       <c r="DL43" t="inlineStr"/>
-      <c r="DM43" t="n">
-        <v>1</v>
-      </c>
+      <c r="DM43" t="inlineStr"/>
       <c r="DN43" t="inlineStr"/>
       <c r="DO43" t="inlineStr"/>
-      <c r="DP43" t="inlineStr"/>
+      <c r="DP43" t="inlineStr">
+        <is>
+          <t>0, 0.859</t>
+        </is>
+      </c>
       <c r="DQ43" t="inlineStr"/>
       <c r="DR43" t="inlineStr"/>
-      <c r="DS43" t="inlineStr"/>
+      <c r="DS43" t="n">
+        <v>1</v>
+      </c>
       <c r="DT43" t="inlineStr"/>
       <c r="DU43" t="inlineStr"/>
       <c r="DV43" t="inlineStr"/>
@@ -12585,8 +12664,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S44" t="n">
-        <v>2</v>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -12723,29 +12804,29 @@
       <c r="CL44" t="inlineStr"/>
       <c r="CM44" t="inlineStr"/>
       <c r="CN44" t="inlineStr"/>
-      <c r="CO44" t="n">
-        <v>1</v>
-      </c>
+      <c r="CO44" t="inlineStr"/>
       <c r="CP44" t="inlineStr"/>
       <c r="CQ44" t="inlineStr"/>
       <c r="CR44" t="inlineStr"/>
       <c r="CS44" t="inlineStr"/>
       <c r="CT44" t="inlineStr"/>
       <c r="CU44" t="n">
-        <v>4.814</v>
+        <v>1</v>
       </c>
       <c r="CV44" t="inlineStr"/>
-      <c r="CW44" t="inlineStr">
-        <is>
-          <t>0, 0.849</t>
-        </is>
-      </c>
+      <c r="CW44" t="inlineStr"/>
       <c r="CX44" t="inlineStr"/>
       <c r="CY44" t="inlineStr"/>
       <c r="CZ44" t="inlineStr"/>
-      <c r="DA44" t="inlineStr"/>
+      <c r="DA44" t="n">
+        <v>4.814</v>
+      </c>
       <c r="DB44" t="inlineStr"/>
-      <c r="DC44" t="inlineStr"/>
+      <c r="DC44" t="inlineStr">
+        <is>
+          <t>0, 0.849</t>
+        </is>
+      </c>
       <c r="DD44" t="inlineStr"/>
       <c r="DE44" t="inlineStr"/>
       <c r="DF44" t="inlineStr"/>
@@ -12862,8 +12943,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S45" t="n">
-        <v>1</v>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -12997,43 +13080,43 @@
       <c r="CE45" t="inlineStr"/>
       <c r="CF45" t="inlineStr"/>
       <c r="CG45" t="inlineStr"/>
-      <c r="CH45" t="inlineStr">
+      <c r="CH45" t="inlineStr"/>
+      <c r="CI45" t="inlineStr"/>
+      <c r="CJ45" t="inlineStr"/>
+      <c r="CK45" t="inlineStr"/>
+      <c r="CL45" t="inlineStr"/>
+      <c r="CM45" t="inlineStr"/>
+      <c r="CN45" t="inlineStr">
         <is>
           <t>0, 0.154</t>
         </is>
       </c>
-      <c r="CI45" t="inlineStr"/>
-      <c r="CJ45" t="n">
+      <c r="CO45" t="inlineStr"/>
+      <c r="CP45" t="n">
         <v>1</v>
       </c>
-      <c r="CK45" t="n">
+      <c r="CQ45" t="n">
         <v>0.062</v>
       </c>
-      <c r="CL45" t="inlineStr">
+      <c r="CR45" t="inlineStr">
         <is>
           <t>MEA_large</t>
         </is>
-      </c>
-      <c r="CM45" t="inlineStr"/>
-      <c r="CN45" t="inlineStr"/>
-      <c r="CO45" t="inlineStr"/>
-      <c r="CP45" t="inlineStr"/>
-      <c r="CQ45" t="inlineStr"/>
-      <c r="CR45" t="n">
-        <v>0.08699999999999999</v>
       </c>
       <c r="CS45" t="inlineStr"/>
       <c r="CT45" t="inlineStr"/>
       <c r="CU45" t="inlineStr"/>
-      <c r="CV45" t="n">
-        <v>1</v>
-      </c>
+      <c r="CV45" t="inlineStr"/>
       <c r="CW45" t="inlineStr"/>
-      <c r="CX45" t="inlineStr"/>
+      <c r="CX45" t="n">
+        <v>0.08699999999999999</v>
+      </c>
       <c r="CY45" t="inlineStr"/>
       <c r="CZ45" t="inlineStr"/>
       <c r="DA45" t="inlineStr"/>
-      <c r="DB45" t="inlineStr"/>
+      <c r="DB45" t="n">
+        <v>1</v>
+      </c>
       <c r="DC45" t="inlineStr"/>
       <c r="DD45" t="inlineStr"/>
       <c r="DE45" t="inlineStr"/>
@@ -13045,17 +13128,17 @@
       <c r="DK45" t="inlineStr"/>
       <c r="DL45" t="inlineStr"/>
       <c r="DM45" t="inlineStr"/>
-      <c r="DN45" t="inlineStr">
-        <is>
-          <t>0, 0.761</t>
-        </is>
-      </c>
+      <c r="DN45" t="inlineStr"/>
       <c r="DO45" t="inlineStr"/>
       <c r="DP45" t="inlineStr"/>
       <c r="DQ45" t="inlineStr"/>
       <c r="DR45" t="inlineStr"/>
       <c r="DS45" t="inlineStr"/>
-      <c r="DT45" t="inlineStr"/>
+      <c r="DT45" t="inlineStr">
+        <is>
+          <t>0, 0.761</t>
+        </is>
+      </c>
       <c r="DU45" t="inlineStr"/>
       <c r="DV45" t="inlineStr"/>
       <c r="DW45" t="inlineStr"/>
@@ -13145,8 +13228,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S46" t="n">
-        <v>1</v>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -13268,11 +13353,7 @@
       <c r="CE46" t="inlineStr"/>
       <c r="CF46" t="inlineStr"/>
       <c r="CG46" t="inlineStr"/>
-      <c r="CH46" t="inlineStr">
-        <is>
-          <t>0, 1.077</t>
-        </is>
-      </c>
+      <c r="CH46" t="inlineStr"/>
       <c r="CI46" t="inlineStr"/>
       <c r="CJ46" t="inlineStr"/>
       <c r="CK46" t="inlineStr"/>
@@ -13280,7 +13361,7 @@
       <c r="CM46" t="inlineStr"/>
       <c r="CN46" t="inlineStr">
         <is>
-          <t>0, 4.966</t>
+          <t>0, 1.077</t>
         </is>
       </c>
       <c r="CO46" t="inlineStr"/>
@@ -13290,7 +13371,7 @@
       <c r="CS46" t="inlineStr"/>
       <c r="CT46" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>0, 4.966</t>
         </is>
       </c>
       <c r="CU46" t="inlineStr"/>
@@ -13298,54 +13379,58 @@
       <c r="CW46" t="inlineStr"/>
       <c r="CX46" t="inlineStr"/>
       <c r="CY46" t="inlineStr"/>
-      <c r="CZ46" t="inlineStr"/>
+      <c r="CZ46" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
       <c r="DA46" t="inlineStr"/>
       <c r="DB46" t="inlineStr"/>
       <c r="DC46" t="inlineStr"/>
-      <c r="DD46" t="n">
-        <v>1</v>
-      </c>
+      <c r="DD46" t="inlineStr"/>
       <c r="DE46" t="inlineStr"/>
       <c r="DF46" t="inlineStr"/>
       <c r="DG46" t="inlineStr"/>
       <c r="DH46" t="inlineStr"/>
       <c r="DI46" t="inlineStr"/>
-      <c r="DJ46" t="inlineStr"/>
+      <c r="DJ46" t="n">
+        <v>1</v>
+      </c>
       <c r="DK46" t="inlineStr"/>
       <c r="DL46" t="inlineStr"/>
       <c r="DM46" t="inlineStr"/>
       <c r="DN46" t="inlineStr"/>
-      <c r="DO46" t="n">
+      <c r="DO46" t="inlineStr"/>
+      <c r="DP46" t="inlineStr"/>
+      <c r="DQ46" t="inlineStr"/>
+      <c r="DR46" t="inlineStr"/>
+      <c r="DS46" t="inlineStr"/>
+      <c r="DT46" t="inlineStr"/>
+      <c r="DU46" t="n">
         <v>1</v>
       </c>
-      <c r="DP46" t="n">
+      <c r="DV46" t="n">
         <v>1</v>
       </c>
-      <c r="DQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR46" t="inlineStr">
+      <c r="DW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX46" t="inlineStr">
         <is>
           <t>not defined</t>
         </is>
       </c>
-      <c r="DS46" t="inlineStr">
+      <c r="DY46" t="inlineStr">
         <is>
           <t>not defined</t>
         </is>
       </c>
-      <c r="DT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU46" t="n">
+      <c r="DZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA46" t="n">
         <v>0.039</v>
       </c>
-      <c r="DV46" t="inlineStr"/>
-      <c r="DW46" t="inlineStr"/>
-      <c r="DX46" t="inlineStr"/>
-      <c r="DY46" t="inlineStr"/>
-      <c r="DZ46" t="inlineStr"/>
-      <c r="EA46" t="inlineStr"/>
       <c r="EB46" t="inlineStr"/>
       <c r="EC46" t="inlineStr"/>
       <c r="ED46" t="inlineStr"/>
@@ -13597,37 +13682,37 @@
       <c r="DS47" t="inlineStr"/>
       <c r="DT47" t="inlineStr"/>
       <c r="DU47" t="inlineStr"/>
-      <c r="DV47" t="inlineStr">
+      <c r="DV47" t="inlineStr"/>
+      <c r="DW47" t="inlineStr"/>
+      <c r="DX47" t="inlineStr"/>
+      <c r="DY47" t="inlineStr"/>
+      <c r="DZ47" t="inlineStr"/>
+      <c r="EA47" t="inlineStr"/>
+      <c r="EB47" t="inlineStr">
         <is>
           <t>as hp/mp steam</t>
         </is>
       </c>
-      <c r="DW47" t="inlineStr">
+      <c r="EC47" t="inlineStr">
         <is>
           <t>OHB</t>
         </is>
       </c>
-      <c r="DX47" t="n">
+      <c r="ED47" t="n">
         <v>0.98</v>
       </c>
-      <c r="DY47" t="n">
+      <c r="EE47" t="n">
         <v>24</v>
       </c>
-      <c r="DZ47" t="n">
+      <c r="EF47" t="n">
         <v>24</v>
       </c>
-      <c r="EA47" t="n">
+      <c r="EG47" t="n">
         <v>24</v>
       </c>
-      <c r="EB47" t="n">
+      <c r="EH47" t="n">
         <v>0.05</v>
       </c>
-      <c r="EC47" t="inlineStr"/>
-      <c r="ED47" t="inlineStr"/>
-      <c r="EE47" t="inlineStr"/>
-      <c r="EF47" t="inlineStr"/>
-      <c r="EG47" t="inlineStr"/>
-      <c r="EH47" t="inlineStr"/>
       <c r="EI47" t="inlineStr"/>
       <c r="EJ47" t="inlineStr"/>
       <c r="EK47" t="inlineStr"/>
@@ -13853,43 +13938,43 @@
       <c r="DZ48" t="inlineStr"/>
       <c r="EA48" t="inlineStr"/>
       <c r="EB48" t="inlineStr"/>
-      <c r="EC48" t="n">
+      <c r="EC48" t="inlineStr"/>
+      <c r="ED48" t="inlineStr"/>
+      <c r="EE48" t="inlineStr"/>
+      <c r="EF48" t="inlineStr"/>
+      <c r="EG48" t="inlineStr"/>
+      <c r="EH48" t="inlineStr"/>
+      <c r="EI48" t="n">
         <v>10</v>
       </c>
-      <c r="ED48" t="n">
+      <c r="EJ48" t="n">
         <v>20.468</v>
       </c>
-      <c r="EE48" t="n">
+      <c r="EK48" t="n">
         <v>33.289</v>
       </c>
-      <c r="EF48" t="n">
+      <c r="EL48" t="n">
         <v>0.3916</v>
       </c>
-      <c r="EG48" t="n">
+      <c r="EM48" t="n">
         <v>-3.011</v>
       </c>
-      <c r="EH48" t="inlineStr">
+      <c r="EN48" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI48" t="inlineStr">
+      <c r="EO48" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ48" t="n">
+      <c r="EP48" t="n">
         <v>15</v>
       </c>
-      <c r="EK48" t="n">
+      <c r="EQ48" t="n">
         <v>0.955</v>
       </c>
-      <c r="EL48" t="inlineStr"/>
-      <c r="EM48" t="inlineStr"/>
-      <c r="EN48" t="inlineStr"/>
-      <c r="EO48" t="inlineStr"/>
-      <c r="EP48" t="inlineStr"/>
-      <c r="EQ48" t="inlineStr"/>
       <c r="ER48" t="inlineStr"/>
       <c r="ES48" t="inlineStr"/>
       <c r="ET48" t="inlineStr"/>
@@ -14106,43 +14191,43 @@
       <c r="DZ49" t="inlineStr"/>
       <c r="EA49" t="inlineStr"/>
       <c r="EB49" t="inlineStr"/>
-      <c r="EC49" t="n">
+      <c r="EC49" t="inlineStr"/>
+      <c r="ED49" t="inlineStr"/>
+      <c r="EE49" t="inlineStr"/>
+      <c r="EF49" t="inlineStr"/>
+      <c r="EG49" t="inlineStr"/>
+      <c r="EH49" t="inlineStr"/>
+      <c r="EI49" t="n">
         <v>100</v>
       </c>
-      <c r="ED49" t="n">
+      <c r="EJ49" t="n">
         <v>129.04</v>
       </c>
-      <c r="EE49" t="n">
+      <c r="EK49" t="n">
         <v>226.884</v>
       </c>
-      <c r="EF49" t="n">
+      <c r="EL49" t="n">
         <v>0.4633</v>
       </c>
-      <c r="EG49" t="n">
+      <c r="EM49" t="n">
         <v>-15.458</v>
       </c>
-      <c r="EH49" t="inlineStr">
+      <c r="EN49" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI49" t="inlineStr">
+      <c r="EO49" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ49" t="n">
+      <c r="EP49" t="n">
         <v>15</v>
       </c>
-      <c r="EK49" t="n">
+      <c r="EQ49" t="n">
         <v>0.955</v>
       </c>
-      <c r="EL49" t="inlineStr"/>
-      <c r="EM49" t="inlineStr"/>
-      <c r="EN49" t="inlineStr"/>
-      <c r="EO49" t="inlineStr"/>
-      <c r="EP49" t="inlineStr"/>
-      <c r="EQ49" t="inlineStr"/>
       <c r="ER49" t="inlineStr"/>
       <c r="ES49" t="inlineStr"/>
       <c r="ET49" t="inlineStr"/>
@@ -14359,43 +14444,43 @@
       <c r="DZ50" t="inlineStr"/>
       <c r="EA50" t="inlineStr"/>
       <c r="EB50" t="inlineStr"/>
-      <c r="EC50" t="n">
+      <c r="EC50" t="inlineStr"/>
+      <c r="ED50" t="inlineStr"/>
+      <c r="EE50" t="inlineStr"/>
+      <c r="EF50" t="inlineStr"/>
+      <c r="EG50" t="inlineStr"/>
+      <c r="EH50" t="inlineStr"/>
+      <c r="EI50" t="n">
         <v>250</v>
       </c>
-      <c r="ED50" t="n">
+      <c r="EJ50" t="n">
         <v>396.035</v>
       </c>
-      <c r="EE50" t="n">
+      <c r="EK50" t="n">
         <v>625.735</v>
       </c>
-      <c r="EF50" t="n">
+      <c r="EL50" t="n">
         <v>0.5486</v>
       </c>
-      <c r="EG50" t="n">
+      <c r="EM50" t="n">
         <v>-93.08499999999999</v>
       </c>
-      <c r="EH50" t="inlineStr">
+      <c r="EN50" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI50" t="inlineStr">
+      <c r="EO50" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ50" t="n">
+      <c r="EP50" t="n">
         <v>15</v>
       </c>
-      <c r="EK50" t="n">
+      <c r="EQ50" t="n">
         <v>0.955</v>
       </c>
-      <c r="EL50" t="inlineStr"/>
-      <c r="EM50" t="inlineStr"/>
-      <c r="EN50" t="inlineStr"/>
-      <c r="EO50" t="inlineStr"/>
-      <c r="EP50" t="inlineStr"/>
-      <c r="EQ50" t="inlineStr"/>
       <c r="ER50" t="inlineStr"/>
       <c r="ES50" t="inlineStr"/>
       <c r="ET50" t="inlineStr"/>
@@ -14612,43 +14697,43 @@
       <c r="DZ51" t="inlineStr"/>
       <c r="EA51" t="inlineStr"/>
       <c r="EB51" t="inlineStr"/>
-      <c r="EC51" t="n">
+      <c r="EC51" t="inlineStr"/>
+      <c r="ED51" t="inlineStr"/>
+      <c r="EE51" t="inlineStr"/>
+      <c r="EF51" t="inlineStr"/>
+      <c r="EG51" t="inlineStr"/>
+      <c r="EH51" t="inlineStr"/>
+      <c r="EI51" t="n">
         <v>400</v>
       </c>
-      <c r="ED51" t="n">
+      <c r="EJ51" t="n">
         <v>720.256</v>
       </c>
-      <c r="EE51" t="n">
+      <c r="EK51" t="n">
         <v>1138.004</v>
       </c>
-      <c r="EF51" t="n">
+      <c r="EL51" t="n">
         <v>0.5486</v>
       </c>
-      <c r="EG51" t="n">
+      <c r="EM51" t="n">
         <v>-169.291</v>
       </c>
-      <c r="EH51" t="inlineStr">
+      <c r="EN51" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI51" t="inlineStr">
+      <c r="EO51" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ51" t="n">
+      <c r="EP51" t="n">
         <v>15</v>
       </c>
-      <c r="EK51" t="n">
+      <c r="EQ51" t="n">
         <v>0.955</v>
       </c>
-      <c r="EL51" t="inlineStr"/>
-      <c r="EM51" t="inlineStr"/>
-      <c r="EN51" t="inlineStr"/>
-      <c r="EO51" t="inlineStr"/>
-      <c r="EP51" t="inlineStr"/>
-      <c r="EQ51" t="inlineStr"/>
       <c r="ER51" t="inlineStr"/>
       <c r="ES51" t="inlineStr"/>
       <c r="ET51" t="inlineStr"/>
@@ -14865,46 +14950,46 @@
       <c r="DZ52" t="inlineStr"/>
       <c r="EA52" t="inlineStr"/>
       <c r="EB52" t="inlineStr"/>
-      <c r="EC52" t="n">
+      <c r="EC52" t="inlineStr"/>
+      <c r="ED52" t="inlineStr"/>
+      <c r="EE52" t="inlineStr"/>
+      <c r="EF52" t="inlineStr"/>
+      <c r="EG52" t="inlineStr"/>
+      <c r="EH52" t="inlineStr"/>
+      <c r="EI52" t="n">
         <v>10</v>
       </c>
-      <c r="ED52" t="n">
+      <c r="EJ52" t="n">
         <v>19.907</v>
       </c>
-      <c r="EE52" t="n">
+      <c r="EK52" t="n">
         <v>32.376</v>
       </c>
-      <c r="EF52" t="n">
+      <c r="EL52" t="n">
         <v>0.4026</v>
       </c>
-      <c r="EG52" t="n">
+      <c r="EM52" t="n">
         <v>-3.0104</v>
       </c>
-      <c r="EH52" t="inlineStr">
+      <c r="EN52" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI52" t="inlineStr">
+      <c r="EO52" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ52" t="n">
+      <c r="EP52" t="n">
         <v>15</v>
       </c>
-      <c r="EK52" t="n">
+      <c r="EQ52" t="n">
         <v>0.871207034372502</v>
       </c>
-      <c r="EL52" t="n">
+      <c r="ER52" t="n">
         <v>0.05</v>
       </c>
-      <c r="EM52" t="inlineStr"/>
-      <c r="EN52" t="inlineStr"/>
-      <c r="EO52" t="inlineStr"/>
-      <c r="EP52" t="inlineStr"/>
-      <c r="EQ52" t="inlineStr"/>
-      <c r="ER52" t="inlineStr"/>
       <c r="ES52" t="inlineStr"/>
       <c r="ET52" t="inlineStr"/>
       <c r="EU52" t="inlineStr"/>
@@ -15120,46 +15205,46 @@
       <c r="DZ53" t="inlineStr"/>
       <c r="EA53" t="inlineStr"/>
       <c r="EB53" t="inlineStr"/>
-      <c r="EC53" t="n">
+      <c r="EC53" t="inlineStr"/>
+      <c r="ED53" t="inlineStr"/>
+      <c r="EE53" t="inlineStr"/>
+      <c r="EF53" t="inlineStr"/>
+      <c r="EG53" t="inlineStr"/>
+      <c r="EH53" t="inlineStr"/>
+      <c r="EI53" t="n">
         <v>100</v>
       </c>
-      <c r="ED53" t="n">
+      <c r="EJ53" t="n">
         <v>123.951</v>
       </c>
-      <c r="EE53" t="n">
+      <c r="EK53" t="n">
         <v>220.66</v>
       </c>
-      <c r="EF53" t="n">
+      <c r="EL53" t="n">
         <v>0.5218</v>
       </c>
-      <c r="EG53" t="n">
+      <c r="EM53" t="n">
         <v>-14.309</v>
       </c>
-      <c r="EH53" t="inlineStr">
+      <c r="EN53" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI53" t="inlineStr">
+      <c r="EO53" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ53" t="n">
+      <c r="EP53" t="n">
         <v>15</v>
       </c>
-      <c r="EK53" t="n">
+      <c r="EQ53" t="n">
         <v>0.871207034372502</v>
       </c>
-      <c r="EL53" t="n">
+      <c r="ER53" t="n">
         <v>0.05</v>
       </c>
-      <c r="EM53" t="inlineStr"/>
-      <c r="EN53" t="inlineStr"/>
-      <c r="EO53" t="inlineStr"/>
-      <c r="EP53" t="inlineStr"/>
-      <c r="EQ53" t="inlineStr"/>
-      <c r="ER53" t="inlineStr"/>
       <c r="ES53" t="inlineStr"/>
       <c r="ET53" t="inlineStr"/>
       <c r="EU53" t="inlineStr"/>
@@ -15375,46 +15460,46 @@
       <c r="DZ54" t="inlineStr"/>
       <c r="EA54" t="inlineStr"/>
       <c r="EB54" t="inlineStr"/>
-      <c r="EC54" t="n">
+      <c r="EC54" t="inlineStr"/>
+      <c r="ED54" t="inlineStr"/>
+      <c r="EE54" t="inlineStr"/>
+      <c r="EF54" t="inlineStr"/>
+      <c r="EG54" t="inlineStr"/>
+      <c r="EH54" t="inlineStr"/>
+      <c r="EI54" t="n">
         <v>250</v>
       </c>
-      <c r="ED54" t="n">
+      <c r="EJ54" t="n">
         <v>351.617</v>
       </c>
-      <c r="EE54" t="n">
+      <c r="EK54" t="n">
         <v>555.556</v>
       </c>
-      <c r="EF54" t="n">
+      <c r="EL54" t="n">
         <v>0.5488</v>
       </c>
-      <c r="EG54" t="n">
+      <c r="EM54" t="n">
         <v>-104.969</v>
       </c>
-      <c r="EH54" t="inlineStr">
+      <c r="EN54" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI54" t="inlineStr">
+      <c r="EO54" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ54" t="n">
+      <c r="EP54" t="n">
         <v>15</v>
       </c>
-      <c r="EK54" t="n">
+      <c r="EQ54" t="n">
         <v>0.871207034372502</v>
       </c>
-      <c r="EL54" t="n">
+      <c r="ER54" t="n">
         <v>0.05</v>
       </c>
-      <c r="EM54" t="inlineStr"/>
-      <c r="EN54" t="inlineStr"/>
-      <c r="EO54" t="inlineStr"/>
-      <c r="EP54" t="inlineStr"/>
-      <c r="EQ54" t="inlineStr"/>
-      <c r="ER54" t="inlineStr"/>
       <c r="ES54" t="inlineStr"/>
       <c r="ET54" t="inlineStr"/>
       <c r="EU54" t="inlineStr"/>
@@ -15630,46 +15715,46 @@
       <c r="DZ55" t="inlineStr"/>
       <c r="EA55" t="inlineStr"/>
       <c r="EB55" t="inlineStr"/>
-      <c r="EC55" t="n">
+      <c r="EC55" t="inlineStr"/>
+      <c r="ED55" t="inlineStr"/>
+      <c r="EE55" t="inlineStr"/>
+      <c r="EF55" t="inlineStr"/>
+      <c r="EG55" t="inlineStr"/>
+      <c r="EH55" t="inlineStr"/>
+      <c r="EI55" t="n">
         <v>400</v>
       </c>
-      <c r="ED55" t="n">
+      <c r="EJ55" t="n">
         <v>685.696</v>
       </c>
-      <c r="EE55" t="n">
+      <c r="EK55" t="n">
         <v>1083.4</v>
       </c>
-      <c r="EF55" t="n">
+      <c r="EL55" t="n">
         <v>0.5763</v>
       </c>
-      <c r="EG55" t="n">
+      <c r="EM55" t="n">
         <v>-169.291</v>
       </c>
-      <c r="EH55" t="inlineStr">
+      <c r="EN55" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI55" t="inlineStr">
+      <c r="EO55" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ55" t="n">
+      <c r="EP55" t="n">
         <v>15</v>
       </c>
-      <c r="EK55" t="n">
+      <c r="EQ55" t="n">
         <v>0.871207034372502</v>
       </c>
-      <c r="EL55" t="n">
+      <c r="ER55" t="n">
         <v>0.05</v>
       </c>
-      <c r="EM55" t="inlineStr"/>
-      <c r="EN55" t="inlineStr"/>
-      <c r="EO55" t="inlineStr"/>
-      <c r="EP55" t="inlineStr"/>
-      <c r="EQ55" t="inlineStr"/>
-      <c r="ER55" t="inlineStr"/>
       <c r="ES55" t="inlineStr"/>
       <c r="ET55" t="inlineStr"/>
       <c r="EU55" t="inlineStr"/>
@@ -15747,8 +15832,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S56" t="n">
-        <v>1</v>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -15931,15 +16018,15 @@
       <c r="EJ56" t="inlineStr"/>
       <c r="EK56" t="inlineStr"/>
       <c r="EL56" t="inlineStr"/>
-      <c r="EM56" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="EM56" t="inlineStr"/>
       <c r="EN56" t="inlineStr"/>
       <c r="EO56" t="inlineStr"/>
       <c r="EP56" t="inlineStr"/>
       <c r="EQ56" t="inlineStr"/>
       <c r="ER56" t="inlineStr"/>
-      <c r="ES56" t="inlineStr"/>
+      <c r="ES56" t="n">
+        <v>0.05</v>
+      </c>
       <c r="ET56" t="inlineStr"/>
       <c r="EU56" t="inlineStr"/>
       <c r="EV56" t="inlineStr"/>
@@ -16016,8 +16103,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S57" t="n">
-        <v>1</v>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -16139,23 +16228,23 @@
       <c r="CG57" t="inlineStr"/>
       <c r="CH57" t="inlineStr"/>
       <c r="CI57" t="inlineStr"/>
-      <c r="CJ57" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK57" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="CL57" t="inlineStr">
-        <is>
-          <t>MEA_medium</t>
-        </is>
-      </c>
+      <c r="CJ57" t="inlineStr"/>
+      <c r="CK57" t="inlineStr"/>
+      <c r="CL57" t="inlineStr"/>
       <c r="CM57" t="inlineStr"/>
       <c r="CN57" t="inlineStr"/>
       <c r="CO57" t="inlineStr"/>
-      <c r="CP57" t="inlineStr"/>
-      <c r="CQ57" t="inlineStr"/>
-      <c r="CR57" t="inlineStr"/>
+      <c r="CP57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>MEA_medium</t>
+        </is>
+      </c>
       <c r="CS57" t="inlineStr"/>
       <c r="CT57" t="inlineStr"/>
       <c r="CU57" t="inlineStr"/>
@@ -16202,18 +16291,18 @@
       <c r="EJ57" t="inlineStr"/>
       <c r="EK57" t="inlineStr"/>
       <c r="EL57" t="inlineStr"/>
-      <c r="EM57" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="EN57" t="n">
-        <v>-1</v>
-      </c>
+      <c r="EM57" t="inlineStr"/>
+      <c r="EN57" t="inlineStr"/>
       <c r="EO57" t="inlineStr"/>
       <c r="EP57" t="inlineStr"/>
       <c r="EQ57" t="inlineStr"/>
       <c r="ER57" t="inlineStr"/>
-      <c r="ES57" t="inlineStr"/>
-      <c r="ET57" t="inlineStr"/>
+      <c r="ES57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="ET57" t="n">
+        <v>-1</v>
+      </c>
       <c r="EU57" t="inlineStr"/>
       <c r="EV57" t="inlineStr"/>
       <c r="EW57" t="inlineStr"/>
@@ -16287,8 +16376,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S58" t="n">
-        <v>1</v>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -16678,15 +16769,15 @@
       <c r="EL59" t="inlineStr"/>
       <c r="EM59" t="inlineStr"/>
       <c r="EN59" t="inlineStr"/>
-      <c r="EO59" t="n">
-        <v>1</v>
-      </c>
+      <c r="EO59" t="inlineStr"/>
       <c r="EP59" t="inlineStr"/>
       <c r="EQ59" t="inlineStr"/>
       <c r="ER59" t="inlineStr"/>
       <c r="ES59" t="inlineStr"/>
       <c r="ET59" t="inlineStr"/>
-      <c r="EU59" t="inlineStr"/>
+      <c r="EU59" t="n">
+        <v>1</v>
+      </c>
       <c r="EV59" t="inlineStr"/>
       <c r="EW59" t="inlineStr"/>
       <c r="EX59" t="inlineStr"/>
@@ -16899,15 +16990,15 @@
       <c r="EL60" t="inlineStr"/>
       <c r="EM60" t="inlineStr"/>
       <c r="EN60" t="inlineStr"/>
-      <c r="EO60" t="n">
-        <v>1</v>
-      </c>
+      <c r="EO60" t="inlineStr"/>
       <c r="EP60" t="inlineStr"/>
       <c r="EQ60" t="inlineStr"/>
       <c r="ER60" t="inlineStr"/>
       <c r="ES60" t="inlineStr"/>
       <c r="ET60" t="inlineStr"/>
-      <c r="EU60" t="inlineStr"/>
+      <c r="EU60" t="n">
+        <v>1</v>
+      </c>
       <c r="EV60" t="inlineStr"/>
       <c r="EW60" t="inlineStr"/>
       <c r="EX60" t="inlineStr"/>
@@ -17055,15 +17146,15 @@
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="inlineStr"/>
       <c r="CA61" t="inlineStr"/>
-      <c r="CB61" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB61" t="inlineStr"/>
       <c r="CC61" t="inlineStr"/>
       <c r="CD61" t="inlineStr"/>
       <c r="CE61" t="inlineStr"/>
       <c r="CF61" t="inlineStr"/>
       <c r="CG61" t="inlineStr"/>
-      <c r="CH61" t="inlineStr"/>
+      <c r="CH61" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI61" t="inlineStr"/>
       <c r="CJ61" t="inlineStr"/>
       <c r="CK61" t="inlineStr"/>
@@ -17122,18 +17213,18 @@
       <c r="EL61" t="inlineStr"/>
       <c r="EM61" t="inlineStr"/>
       <c r="EN61" t="inlineStr"/>
-      <c r="EO61" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP61" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO61" t="inlineStr"/>
+      <c r="EP61" t="inlineStr"/>
       <c r="EQ61" t="inlineStr"/>
       <c r="ER61" t="inlineStr"/>
       <c r="ES61" t="inlineStr"/>
       <c r="ET61" t="inlineStr"/>
-      <c r="EU61" t="inlineStr"/>
-      <c r="EV61" t="inlineStr"/>
+      <c r="EU61" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV61" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW61" t="inlineStr"/>
       <c r="EX61" t="inlineStr"/>
       <c r="EY61" t="inlineStr"/>
@@ -17280,15 +17371,15 @@
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="inlineStr"/>
       <c r="CA62" t="inlineStr"/>
-      <c r="CB62" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB62" t="inlineStr"/>
       <c r="CC62" t="inlineStr"/>
       <c r="CD62" t="inlineStr"/>
       <c r="CE62" t="inlineStr"/>
       <c r="CF62" t="inlineStr"/>
       <c r="CG62" t="inlineStr"/>
-      <c r="CH62" t="inlineStr"/>
+      <c r="CH62" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI62" t="inlineStr"/>
       <c r="CJ62" t="inlineStr"/>
       <c r="CK62" t="inlineStr"/>
@@ -17347,18 +17438,18 @@
       <c r="EL62" t="inlineStr"/>
       <c r="EM62" t="inlineStr"/>
       <c r="EN62" t="inlineStr"/>
-      <c r="EO62" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP62" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO62" t="inlineStr"/>
+      <c r="EP62" t="inlineStr"/>
       <c r="EQ62" t="inlineStr"/>
       <c r="ER62" t="inlineStr"/>
       <c r="ES62" t="inlineStr"/>
       <c r="ET62" t="inlineStr"/>
-      <c r="EU62" t="inlineStr"/>
-      <c r="EV62" t="inlineStr"/>
+      <c r="EU62" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV62" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW62" t="inlineStr"/>
       <c r="EX62" t="inlineStr"/>
       <c r="EY62" t="inlineStr"/>
@@ -17505,15 +17596,15 @@
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="inlineStr"/>
       <c r="CA63" t="inlineStr"/>
-      <c r="CB63" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB63" t="inlineStr"/>
       <c r="CC63" t="inlineStr"/>
       <c r="CD63" t="inlineStr"/>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="inlineStr"/>
       <c r="CG63" t="inlineStr"/>
-      <c r="CH63" t="inlineStr"/>
+      <c r="CH63" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI63" t="inlineStr"/>
       <c r="CJ63" t="inlineStr"/>
       <c r="CK63" t="inlineStr"/>
@@ -17572,18 +17663,18 @@
       <c r="EL63" t="inlineStr"/>
       <c r="EM63" t="inlineStr"/>
       <c r="EN63" t="inlineStr"/>
-      <c r="EO63" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP63" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO63" t="inlineStr"/>
+      <c r="EP63" t="inlineStr"/>
       <c r="EQ63" t="inlineStr"/>
       <c r="ER63" t="inlineStr"/>
       <c r="ES63" t="inlineStr"/>
       <c r="ET63" t="inlineStr"/>
-      <c r="EU63" t="inlineStr"/>
-      <c r="EV63" t="inlineStr"/>
+      <c r="EU63" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV63" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW63" t="inlineStr"/>
       <c r="EX63" t="inlineStr"/>
       <c r="EY63" t="inlineStr"/>
@@ -17730,15 +17821,15 @@
       <c r="BY64" t="inlineStr"/>
       <c r="BZ64" t="inlineStr"/>
       <c r="CA64" t="inlineStr"/>
-      <c r="CB64" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB64" t="inlineStr"/>
       <c r="CC64" t="inlineStr"/>
       <c r="CD64" t="inlineStr"/>
       <c r="CE64" t="inlineStr"/>
       <c r="CF64" t="inlineStr"/>
       <c r="CG64" t="inlineStr"/>
-      <c r="CH64" t="inlineStr"/>
+      <c r="CH64" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI64" t="inlineStr"/>
       <c r="CJ64" t="inlineStr"/>
       <c r="CK64" t="inlineStr"/>
@@ -17797,18 +17888,18 @@
       <c r="EL64" t="inlineStr"/>
       <c r="EM64" t="inlineStr"/>
       <c r="EN64" t="inlineStr"/>
-      <c r="EO64" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP64" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO64" t="inlineStr"/>
+      <c r="EP64" t="inlineStr"/>
       <c r="EQ64" t="inlineStr"/>
       <c r="ER64" t="inlineStr"/>
       <c r="ES64" t="inlineStr"/>
       <c r="ET64" t="inlineStr"/>
-      <c r="EU64" t="inlineStr"/>
-      <c r="EV64" t="inlineStr"/>
+      <c r="EU64" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV64" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW64" t="inlineStr"/>
       <c r="EX64" t="inlineStr"/>
       <c r="EY64" t="inlineStr"/>
@@ -17955,15 +18046,15 @@
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="inlineStr"/>
       <c r="CA65" t="inlineStr"/>
-      <c r="CB65" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB65" t="inlineStr"/>
       <c r="CC65" t="inlineStr"/>
       <c r="CD65" t="inlineStr"/>
       <c r="CE65" t="inlineStr"/>
       <c r="CF65" t="inlineStr"/>
       <c r="CG65" t="inlineStr"/>
-      <c r="CH65" t="inlineStr"/>
+      <c r="CH65" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI65" t="inlineStr"/>
       <c r="CJ65" t="inlineStr"/>
       <c r="CK65" t="inlineStr"/>
@@ -18022,18 +18113,18 @@
       <c r="EL65" t="inlineStr"/>
       <c r="EM65" t="inlineStr"/>
       <c r="EN65" t="inlineStr"/>
-      <c r="EO65" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP65" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO65" t="inlineStr"/>
+      <c r="EP65" t="inlineStr"/>
       <c r="EQ65" t="inlineStr"/>
       <c r="ER65" t="inlineStr"/>
       <c r="ES65" t="inlineStr"/>
       <c r="ET65" t="inlineStr"/>
-      <c r="EU65" t="inlineStr"/>
-      <c r="EV65" t="inlineStr"/>
+      <c r="EU65" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV65" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW65" t="inlineStr"/>
       <c r="EX65" t="inlineStr"/>
       <c r="EY65" t="inlineStr"/>
@@ -18180,15 +18271,15 @@
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="inlineStr"/>
       <c r="CA66" t="inlineStr"/>
-      <c r="CB66" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB66" t="inlineStr"/>
       <c r="CC66" t="inlineStr"/>
       <c r="CD66" t="inlineStr"/>
       <c r="CE66" t="inlineStr"/>
       <c r="CF66" t="inlineStr"/>
       <c r="CG66" t="inlineStr"/>
-      <c r="CH66" t="inlineStr"/>
+      <c r="CH66" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI66" t="inlineStr"/>
       <c r="CJ66" t="inlineStr"/>
       <c r="CK66" t="inlineStr"/>
@@ -18247,18 +18338,18 @@
       <c r="EL66" t="inlineStr"/>
       <c r="EM66" t="inlineStr"/>
       <c r="EN66" t="inlineStr"/>
-      <c r="EO66" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP66" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO66" t="inlineStr"/>
+      <c r="EP66" t="inlineStr"/>
       <c r="EQ66" t="inlineStr"/>
       <c r="ER66" t="inlineStr"/>
       <c r="ES66" t="inlineStr"/>
       <c r="ET66" t="inlineStr"/>
-      <c r="EU66" t="inlineStr"/>
-      <c r="EV66" t="inlineStr"/>
+      <c r="EU66" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV66" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW66" t="inlineStr"/>
       <c r="EX66" t="inlineStr"/>
       <c r="EY66" t="inlineStr"/>
@@ -18412,7 +18503,11 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="inlineStr"/>
-      <c r="CA67" t="inlineStr"/>
+      <c r="CA67" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
       <c r="CB67" t="inlineStr"/>
       <c r="CC67" t="inlineStr"/>
       <c r="CD67" t="inlineStr"/>
@@ -18480,28 +18575,24 @@
       <c r="EN67" t="inlineStr"/>
       <c r="EO67" t="inlineStr"/>
       <c r="EP67" t="inlineStr"/>
-      <c r="EQ67" t="n">
+      <c r="EQ67" t="inlineStr"/>
+      <c r="ER67" t="inlineStr"/>
+      <c r="ES67" t="inlineStr"/>
+      <c r="ET67" t="inlineStr"/>
+      <c r="EU67" t="inlineStr"/>
+      <c r="EV67" t="inlineStr"/>
+      <c r="EW67" t="n">
         <v>0.034</v>
       </c>
-      <c r="ER67" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
-      <c r="ES67" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET67" t="n">
+      <c r="EX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY67" t="n">
         <v>114</v>
       </c>
-      <c r="EU67" t="n">
-        <v>0</v>
-      </c>
-      <c r="EV67" t="inlineStr"/>
-      <c r="EW67" t="inlineStr"/>
-      <c r="EX67" t="inlineStr"/>
-      <c r="EY67" t="inlineStr"/>
-      <c r="EZ67" t="inlineStr"/>
+      <c r="EZ67" t="n">
+        <v>0</v>
+      </c>
       <c r="FA67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -18673,12 +18764,28 @@
       <c r="BZ68" t="n">
         <v>0</v>
       </c>
-      <c r="CA68" t="inlineStr"/>
-      <c r="CB68" t="inlineStr"/>
-      <c r="CC68" t="inlineStr"/>
-      <c r="CD68" t="inlineStr"/>
-      <c r="CE68" t="inlineStr"/>
-      <c r="CF68" t="inlineStr"/>
+      <c r="CA68" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB68" t="inlineStr">
+        <is>
+          <t>fixedcapacity</t>
+        </is>
+      </c>
+      <c r="CC68" t="n">
+        <v>250</v>
+      </c>
+      <c r="CD68" t="n">
+        <v>250</v>
+      </c>
+      <c r="CE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF68" t="n">
+        <v>0</v>
+      </c>
       <c r="CG68" t="inlineStr"/>
       <c r="CH68" t="inlineStr"/>
       <c r="CI68" t="inlineStr"/>
@@ -18741,34 +18848,18 @@
       <c r="EN68" t="inlineStr"/>
       <c r="EO68" t="inlineStr"/>
       <c r="EP68" t="inlineStr"/>
-      <c r="EQ68" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="ER68" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="EQ68" t="inlineStr"/>
+      <c r="ER68" t="inlineStr"/>
       <c r="ES68" t="inlineStr"/>
       <c r="ET68" t="inlineStr"/>
       <c r="EU68" t="inlineStr"/>
-      <c r="EV68" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW68" t="inlineStr">
-        <is>
-          <t>fixedcapacity</t>
-        </is>
-      </c>
-      <c r="EX68" t="n">
-        <v>250</v>
-      </c>
-      <c r="EY68" t="n">
-        <v>250</v>
-      </c>
-      <c r="EZ68" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV68" t="inlineStr"/>
+      <c r="EW68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="EX68" t="inlineStr"/>
+      <c r="EY68" t="inlineStr"/>
+      <c r="EZ68" t="inlineStr"/>
       <c r="FA68" t="n">
         <v>0</v>
       </c>
@@ -18942,24 +19033,40 @@
       <c r="BZ69" t="n">
         <v>0</v>
       </c>
-      <c r="CA69" t="inlineStr"/>
-      <c r="CB69" t="n">
+      <c r="CA69" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB69" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC69" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG69" t="inlineStr"/>
+      <c r="CH69" t="n">
         <v>0.001</v>
       </c>
-      <c r="CC69" t="inlineStr"/>
-      <c r="CD69" t="inlineStr"/>
-      <c r="CE69" t="n">
-        <v>100</v>
-      </c>
-      <c r="CF69" t="n">
-        <v>100</v>
-      </c>
-      <c r="CG69" t="inlineStr"/>
-      <c r="CH69" t="inlineStr"/>
       <c r="CI69" t="inlineStr"/>
       <c r="CJ69" t="inlineStr"/>
-      <c r="CK69" t="inlineStr"/>
-      <c r="CL69" t="inlineStr"/>
+      <c r="CK69" t="n">
+        <v>100</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>100</v>
+      </c>
       <c r="CM69" t="inlineStr"/>
       <c r="CN69" t="inlineStr"/>
       <c r="CO69" t="inlineStr"/>
@@ -19015,36 +19122,20 @@
       <c r="EM69" t="inlineStr"/>
       <c r="EN69" t="inlineStr"/>
       <c r="EO69" t="inlineStr"/>
-      <c r="EP69" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EP69" t="inlineStr"/>
       <c r="EQ69" t="inlineStr"/>
-      <c r="ER69" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER69" t="inlineStr"/>
       <c r="ES69" t="inlineStr"/>
       <c r="ET69" t="inlineStr"/>
       <c r="EU69" t="inlineStr"/>
-      <c r="EV69" t="inlineStr"/>
-      <c r="EW69" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX69" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="EY69" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="EZ69" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA69" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="EW69" t="inlineStr"/>
+      <c r="EX69" t="inlineStr"/>
+      <c r="EY69" t="inlineStr"/>
+      <c r="EZ69" t="inlineStr"/>
+      <c r="FA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -19215,12 +19306,28 @@
       <c r="BZ70" t="n">
         <v>0</v>
       </c>
-      <c r="CA70" t="inlineStr"/>
-      <c r="CB70" t="inlineStr"/>
-      <c r="CC70" t="inlineStr"/>
-      <c r="CD70" t="inlineStr"/>
-      <c r="CE70" t="inlineStr"/>
-      <c r="CF70" t="inlineStr"/>
+      <c r="CA70" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB70" t="inlineStr">
+        <is>
+          <t>fixedcapacity</t>
+        </is>
+      </c>
+      <c r="CC70" t="n">
+        <v>650</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>650</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0</v>
+      </c>
       <c r="CG70" t="inlineStr"/>
       <c r="CH70" t="inlineStr"/>
       <c r="CI70" t="inlineStr"/>
@@ -19283,34 +19390,18 @@
       <c r="EN70" t="inlineStr"/>
       <c r="EO70" t="inlineStr"/>
       <c r="EP70" t="inlineStr"/>
-      <c r="EQ70" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="ER70" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="EQ70" t="inlineStr"/>
+      <c r="ER70" t="inlineStr"/>
       <c r="ES70" t="inlineStr"/>
       <c r="ET70" t="inlineStr"/>
       <c r="EU70" t="inlineStr"/>
-      <c r="EV70" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW70" t="inlineStr">
-        <is>
-          <t>fixedcapacity</t>
-        </is>
-      </c>
-      <c r="EX70" t="n">
-        <v>650</v>
-      </c>
-      <c r="EY70" t="n">
-        <v>650</v>
-      </c>
-      <c r="EZ70" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV70" t="inlineStr"/>
+      <c r="EW70" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="EX70" t="inlineStr"/>
+      <c r="EY70" t="inlineStr"/>
+      <c r="EZ70" t="inlineStr"/>
       <c r="FA70" t="n">
         <v>0</v>
       </c>
@@ -19484,12 +19575,28 @@
       <c r="BZ71" t="n">
         <v>0</v>
       </c>
-      <c r="CA71" t="inlineStr"/>
-      <c r="CB71" t="inlineStr"/>
-      <c r="CC71" t="inlineStr"/>
-      <c r="CD71" t="inlineStr"/>
-      <c r="CE71" t="inlineStr"/>
-      <c r="CF71" t="inlineStr"/>
+      <c r="CA71" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB71" t="inlineStr">
+        <is>
+          <t>fixedcapacity</t>
+        </is>
+      </c>
+      <c r="CC71" t="n">
+        <v>250</v>
+      </c>
+      <c r="CD71" t="n">
+        <v>250</v>
+      </c>
+      <c r="CE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF71" t="n">
+        <v>0</v>
+      </c>
       <c r="CG71" t="inlineStr"/>
       <c r="CH71" t="inlineStr"/>
       <c r="CI71" t="inlineStr"/>
@@ -19553,31 +19660,15 @@
       <c r="EO71" t="inlineStr"/>
       <c r="EP71" t="inlineStr"/>
       <c r="EQ71" t="inlineStr"/>
-      <c r="ER71" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER71" t="inlineStr"/>
       <c r="ES71" t="inlineStr"/>
       <c r="ET71" t="inlineStr"/>
       <c r="EU71" t="inlineStr"/>
-      <c r="EV71" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW71" t="inlineStr">
-        <is>
-          <t>fixedcapacity</t>
-        </is>
-      </c>
-      <c r="EX71" t="n">
-        <v>250</v>
-      </c>
-      <c r="EY71" t="n">
-        <v>250</v>
-      </c>
-      <c r="EZ71" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV71" t="inlineStr"/>
+      <c r="EW71" t="inlineStr"/>
+      <c r="EX71" t="inlineStr"/>
+      <c r="EY71" t="inlineStr"/>
+      <c r="EZ71" t="inlineStr"/>
       <c r="FA71" t="n">
         <v>0</v>
       </c>
@@ -19751,12 +19842,28 @@
       <c r="BZ72" t="n">
         <v>0</v>
       </c>
-      <c r="CA72" t="inlineStr"/>
-      <c r="CB72" t="inlineStr"/>
-      <c r="CC72" t="inlineStr"/>
-      <c r="CD72" t="inlineStr"/>
-      <c r="CE72" t="inlineStr"/>
-      <c r="CF72" t="inlineStr"/>
+      <c r="CA72" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB72" t="inlineStr">
+        <is>
+          <t>fixedcapacity</t>
+        </is>
+      </c>
+      <c r="CC72" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CD72" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF72" t="n">
+        <v>0</v>
+      </c>
       <c r="CG72" t="inlineStr"/>
       <c r="CH72" t="inlineStr"/>
       <c r="CI72" t="inlineStr"/>
@@ -19820,31 +19927,15 @@
       <c r="EO72" t="inlineStr"/>
       <c r="EP72" t="inlineStr"/>
       <c r="EQ72" t="inlineStr"/>
-      <c r="ER72" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER72" t="inlineStr"/>
       <c r="ES72" t="inlineStr"/>
       <c r="ET72" t="inlineStr"/>
       <c r="EU72" t="inlineStr"/>
-      <c r="EV72" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW72" t="inlineStr">
-        <is>
-          <t>fixedcapacity</t>
-        </is>
-      </c>
-      <c r="EX72" t="n">
-        <v>1500</v>
-      </c>
-      <c r="EY72" t="n">
-        <v>1500</v>
-      </c>
-      <c r="EZ72" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV72" t="inlineStr"/>
+      <c r="EW72" t="inlineStr"/>
+      <c r="EX72" t="inlineStr"/>
+      <c r="EY72" t="inlineStr"/>
+      <c r="EZ72" t="inlineStr"/>
       <c r="FA72" t="n">
         <v>0</v>
       </c>
@@ -20018,12 +20109,28 @@
       <c r="BZ73" t="n">
         <v>0</v>
       </c>
-      <c r="CA73" t="inlineStr"/>
-      <c r="CB73" t="inlineStr"/>
-      <c r="CC73" t="inlineStr"/>
-      <c r="CD73" t="inlineStr"/>
-      <c r="CE73" t="inlineStr"/>
-      <c r="CF73" t="inlineStr"/>
+      <c r="CA73" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB73" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CD73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF73" t="n">
+        <v>0</v>
+      </c>
       <c r="CG73" t="inlineStr"/>
       <c r="CH73" t="inlineStr"/>
       <c r="CI73" t="inlineStr"/>
@@ -20086,35 +20193,19 @@
       <c r="EN73" t="inlineStr"/>
       <c r="EO73" t="inlineStr"/>
       <c r="EP73" t="inlineStr"/>
-      <c r="EQ73" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="ER73" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="EQ73" t="inlineStr"/>
+      <c r="ER73" t="inlineStr"/>
       <c r="ES73" t="inlineStr"/>
       <c r="ET73" t="inlineStr"/>
       <c r="EU73" t="inlineStr"/>
       <c r="EV73" t="inlineStr"/>
-      <c r="EW73" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX73" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="EY73" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="EZ73" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA73" t="n">
-        <v>0</v>
-      </c>
+      <c r="EW73" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="EX73" t="inlineStr"/>
+      <c r="EY73" t="inlineStr"/>
+      <c r="EZ73" t="inlineStr"/>
+      <c r="FA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -20285,12 +20376,28 @@
       <c r="BZ74" t="n">
         <v>0.0005</v>
       </c>
-      <c r="CA74" t="inlineStr"/>
-      <c r="CB74" t="inlineStr"/>
-      <c r="CC74" t="inlineStr"/>
-      <c r="CD74" t="inlineStr"/>
-      <c r="CE74" t="inlineStr"/>
-      <c r="CF74" t="inlineStr"/>
+      <c r="CA74" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB74" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC74" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CD74" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF74" t="n">
+        <v>0</v>
+      </c>
       <c r="CG74" t="inlineStr"/>
       <c r="CH74" t="inlineStr"/>
       <c r="CI74" t="inlineStr"/>
@@ -20354,32 +20461,16 @@
       <c r="EO74" t="inlineStr"/>
       <c r="EP74" t="inlineStr"/>
       <c r="EQ74" t="inlineStr"/>
-      <c r="ER74" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER74" t="inlineStr"/>
       <c r="ES74" t="inlineStr"/>
       <c r="ET74" t="inlineStr"/>
       <c r="EU74" t="inlineStr"/>
       <c r="EV74" t="inlineStr"/>
-      <c r="EW74" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX74" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="EY74" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="EZ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA74" t="n">
-        <v>0</v>
-      </c>
+      <c r="EW74" t="inlineStr"/>
+      <c r="EX74" t="inlineStr"/>
+      <c r="EY74" t="inlineStr"/>
+      <c r="EZ74" t="inlineStr"/>
+      <c r="FA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -20550,12 +20641,28 @@
       <c r="BZ75" t="n">
         <v>0</v>
       </c>
-      <c r="CA75" t="inlineStr"/>
-      <c r="CB75" t="inlineStr"/>
-      <c r="CC75" t="inlineStr"/>
-      <c r="CD75" t="inlineStr"/>
-      <c r="CE75" t="inlineStr"/>
-      <c r="CF75" t="inlineStr"/>
+      <c r="CA75" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB75" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
       <c r="CG75" t="inlineStr"/>
       <c r="CH75" t="inlineStr"/>
       <c r="CI75" t="inlineStr"/>
@@ -20619,32 +20726,16 @@
       <c r="EO75" t="inlineStr"/>
       <c r="EP75" t="inlineStr"/>
       <c r="EQ75" t="inlineStr"/>
-      <c r="ER75" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER75" t="inlineStr"/>
       <c r="ES75" t="inlineStr"/>
       <c r="ET75" t="inlineStr"/>
       <c r="EU75" t="inlineStr"/>
       <c r="EV75" t="inlineStr"/>
-      <c r="EW75" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX75" t="n">
-        <v>1</v>
-      </c>
-      <c r="EY75" t="n">
-        <v>1</v>
-      </c>
-      <c r="EZ75" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA75" t="n">
-        <v>0</v>
-      </c>
+      <c r="EW75" t="inlineStr"/>
+      <c r="EX75" t="inlineStr"/>
+      <c r="EY75" t="inlineStr"/>
+      <c r="EZ75" t="inlineStr"/>
+      <c r="FA75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -20815,12 +20906,28 @@
       <c r="BZ76" t="n">
         <v>0</v>
       </c>
-      <c r="CA76" t="inlineStr"/>
-      <c r="CB76" t="inlineStr"/>
-      <c r="CC76" t="inlineStr"/>
-      <c r="CD76" t="inlineStr"/>
-      <c r="CE76" t="inlineStr"/>
-      <c r="CF76" t="inlineStr"/>
+      <c r="CA76" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB76" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
       <c r="CG76" t="inlineStr"/>
       <c r="CH76" t="inlineStr"/>
       <c r="CI76" t="inlineStr"/>
@@ -20884,32 +20991,16 @@
       <c r="EO76" t="inlineStr"/>
       <c r="EP76" t="inlineStr"/>
       <c r="EQ76" t="inlineStr"/>
-      <c r="ER76" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER76" t="inlineStr"/>
       <c r="ES76" t="inlineStr"/>
       <c r="ET76" t="inlineStr"/>
       <c r="EU76" t="inlineStr"/>
       <c r="EV76" t="inlineStr"/>
-      <c r="EW76" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX76" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="EY76" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="EZ76" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA76" t="n">
-        <v>0</v>
-      </c>
+      <c r="EW76" t="inlineStr"/>
+      <c r="EX76" t="inlineStr"/>
+      <c r="EY76" t="inlineStr"/>
+      <c r="EZ76" t="inlineStr"/>
+      <c r="FA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21080,12 +21171,28 @@
       <c r="BZ77" t="n">
         <v>0</v>
       </c>
-      <c r="CA77" t="inlineStr"/>
-      <c r="CB77" t="inlineStr"/>
-      <c r="CC77" t="inlineStr"/>
-      <c r="CD77" t="inlineStr"/>
-      <c r="CE77" t="inlineStr"/>
-      <c r="CF77" t="inlineStr"/>
+      <c r="CA77" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB77" t="inlineStr">
+        <is>
+          <t>fixedcapacity</t>
+        </is>
+      </c>
+      <c r="CC77" t="n">
+        <v>250</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>250</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>0</v>
+      </c>
       <c r="CG77" t="inlineStr"/>
       <c r="CH77" t="inlineStr"/>
       <c r="CI77" t="inlineStr"/>
@@ -21149,31 +21256,15 @@
       <c r="EO77" t="inlineStr"/>
       <c r="EP77" t="inlineStr"/>
       <c r="EQ77" t="inlineStr"/>
-      <c r="ER77" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER77" t="inlineStr"/>
       <c r="ES77" t="inlineStr"/>
       <c r="ET77" t="inlineStr"/>
       <c r="EU77" t="inlineStr"/>
-      <c r="EV77" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW77" t="inlineStr">
-        <is>
-          <t>fixedcapacity</t>
-        </is>
-      </c>
-      <c r="EX77" t="n">
-        <v>250</v>
-      </c>
-      <c r="EY77" t="n">
-        <v>250</v>
-      </c>
-      <c r="EZ77" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV77" t="inlineStr"/>
+      <c r="EW77" t="inlineStr"/>
+      <c r="EX77" t="inlineStr"/>
+      <c r="EY77" t="inlineStr"/>
+      <c r="EZ77" t="inlineStr"/>
       <c r="FA77" t="n">
         <v>0</v>
       </c>
@@ -21339,12 +21430,28 @@
       <c r="BZ78" t="n">
         <v>0</v>
       </c>
-      <c r="CA78" t="inlineStr"/>
-      <c r="CB78" t="inlineStr"/>
-      <c r="CC78" t="inlineStr"/>
-      <c r="CD78" t="inlineStr"/>
-      <c r="CE78" t="inlineStr"/>
-      <c r="CF78" t="inlineStr"/>
+      <c r="CA78" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB78" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>0</v>
+      </c>
       <c r="CG78" t="inlineStr"/>
       <c r="CH78" t="inlineStr"/>
       <c r="CI78" t="inlineStr"/>
@@ -21408,48 +21515,32 @@
       <c r="EO78" t="inlineStr"/>
       <c r="EP78" t="inlineStr"/>
       <c r="EQ78" t="inlineStr"/>
-      <c r="ER78" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER78" t="inlineStr"/>
       <c r="ES78" t="inlineStr"/>
       <c r="ET78" t="inlineStr"/>
       <c r="EU78" t="inlineStr"/>
       <c r="EV78" t="inlineStr"/>
-      <c r="EW78" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX78" t="n">
-        <v>1</v>
-      </c>
-      <c r="EY78" t="n">
-        <v>1</v>
-      </c>
-      <c r="EZ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA78" t="n">
-        <v>0</v>
-      </c>
+      <c r="EW78" t="inlineStr"/>
+      <c r="EX78" t="inlineStr"/>
+      <c r="EY78" t="inlineStr"/>
+      <c r="EZ78" t="inlineStr"/>
+      <c r="FA78" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="EW1:FA1"/>
+    <mergeCell ref="BJ1:BZ1"/>
+    <mergeCell ref="CA1:CF1"/>
     <mergeCell ref="R1:AN1"/>
     <mergeCell ref="AW1:BB1"/>
     <mergeCell ref="AT1:AV1"/>
     <mergeCell ref="AO1:AQ1"/>
-    <mergeCell ref="DO1:DU1"/>
-    <mergeCell ref="DV1:EO1"/>
-    <mergeCell ref="CB1:CF1"/>
-    <mergeCell ref="ER1:EU1"/>
-    <mergeCell ref="BJ1:CA1"/>
+    <mergeCell ref="EB1:EU1"/>
+    <mergeCell ref="DU1:EA1"/>
+    <mergeCell ref="CH1:CL1"/>
     <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="CG1:DN1"/>
+    <mergeCell ref="CM1:DT1"/>
     <mergeCell ref="BE1:BH1"/>
+    <mergeCell ref="EX1:EZ1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/adopt_net0/database/data/Components_database.xlsx
+++ b/adopt_net0/database/data/Components_database.xlsx
@@ -527,49 +527,54 @@
           <t>Performance</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Flow_capacity_relation</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>ScalingFactors</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>Economics</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>ScalingFactors</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>Flexibility</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>Flow_capacity_relation</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>Performance</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>Flexibility</t>
         </is>
       </c>
     </row>
@@ -911,397 +916,397 @@
       </c>
       <c r="CA2" s="2" t="inlineStr">
         <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="CB2" s="2" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="CC2" s="2" t="inlineStr">
+        <is>
+          <t>charge_rate</t>
+        </is>
+      </c>
+      <c r="CD2" s="2" t="inlineStr">
+        <is>
+          <t>discharge_rate</t>
+        </is>
+      </c>
+      <c r="CE2" s="2" t="inlineStr">
+        <is>
+          <t>capex_charging_rate</t>
+        </is>
+      </c>
+      <c r="CF2" s="2" t="inlineStr">
+        <is>
+          <t>capex_discharging_rate</t>
+        </is>
+      </c>
+      <c r="CG2" s="2" t="inlineStr">
+        <is>
           <t>performance.out.nitrogen</t>
         </is>
       </c>
-      <c r="CB2" s="2" t="inlineStr">
+      <c r="CH2" s="2" t="inlineStr">
         <is>
           <t>const_capex_aux</t>
         </is>
       </c>
-      <c r="CC2" s="2" t="inlineStr">
+      <c r="CI2" s="2" t="inlineStr">
         <is>
           <t>const_input_output</t>
         </is>
       </c>
-      <c r="CD2" s="2" t="inlineStr">
+      <c r="CJ2" s="2" t="inlineStr">
         <is>
           <t>const_max_input</t>
         </is>
       </c>
-      <c r="CE2" s="2" t="inlineStr">
+      <c r="CK2" s="2" t="inlineStr">
         <is>
           <t>const_opex_variable</t>
         </is>
       </c>
-      <c r="CF2" s="2" t="inlineStr">
+      <c r="CL2" s="2" t="inlineStr">
         <is>
           <t>const_opex_fixed</t>
         </is>
       </c>
-      <c r="CG2" s="2" t="inlineStr">
+      <c r="CM2" s="2" t="inlineStr">
         <is>
           <t>performance.out.methanol</t>
         </is>
       </c>
-      <c r="CH2" s="2" t="inlineStr">
+      <c r="CN2" s="2" t="inlineStr">
         <is>
           <t>performance.out.CO2</t>
         </is>
       </c>
-      <c r="CI2" s="2" t="inlineStr">
+      <c r="CO2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.MPW</t>
         </is>
       </c>
-      <c r="CJ2" s="2" t="inlineStr">
+      <c r="CP2" s="2" t="inlineStr">
         <is>
           <t>ccs.possible</t>
         </is>
       </c>
-      <c r="CK2" s="2" t="inlineStr">
+      <c r="CQ2" s="2" t="inlineStr">
         <is>
           <t>ccs.co2_concentration</t>
         </is>
       </c>
-      <c r="CL2" s="2" t="inlineStr">
+      <c r="CR2" s="2" t="inlineStr">
         <is>
           <t>ccs.ccs_type</t>
         </is>
       </c>
-      <c r="CM2" s="2" t="inlineStr">
+      <c r="CS2" s="2" t="inlineStr">
         <is>
           <t>performance.out.ethylene</t>
         </is>
       </c>
-      <c r="CN2" s="2" t="inlineStr">
+      <c r="CT2" s="2" t="inlineStr">
         <is>
           <t>performance.out.hydrogen</t>
         </is>
       </c>
-      <c r="CO2" s="2" t="inlineStr">
+      <c r="CU2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.CO2</t>
         </is>
       </c>
-      <c r="CP2" s="2" t="inlineStr">
+      <c r="CV2" s="2" t="inlineStr">
         <is>
           <t>performance.out.olefins</t>
         </is>
       </c>
-      <c r="CQ2" s="2" t="inlineStr">
+      <c r="CW2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.naphtha</t>
         </is>
       </c>
-      <c r="CR2" s="2" t="inlineStr">
+      <c r="CX2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.steam</t>
         </is>
       </c>
-      <c r="CS2" s="2" t="inlineStr">
+      <c r="CY2" s="2" t="inlineStr">
         <is>
           <t>performance.out.steam</t>
         </is>
       </c>
-      <c r="CT2" s="2" t="inlineStr">
+      <c r="CZ2" s="2" t="inlineStr">
         <is>
           <t>standby_power_carrier</t>
         </is>
       </c>
-      <c r="CU2" s="2" t="inlineStr">
+      <c r="DA2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.hydrogen</t>
         </is>
       </c>
-      <c r="CV2" s="2" t="inlineStr">
+      <c r="DB2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.feedgas</t>
         </is>
       </c>
-      <c r="CW2" s="2" t="inlineStr">
+      <c r="DC2" s="2" t="inlineStr">
         <is>
           <t>performance.out.syngas</t>
         </is>
       </c>
-      <c r="CX2" s="2" t="inlineStr">
+      <c r="DD2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.ethanol</t>
         </is>
       </c>
-      <c r="CY2" s="2" t="inlineStr">
+      <c r="DE2" s="2" t="inlineStr">
         <is>
           <t>performance.out.crackedgas</t>
         </is>
       </c>
-      <c r="CZ2" s="2" t="inlineStr">
+      <c r="DF2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.crackedgas</t>
         </is>
       </c>
-      <c r="DA2" s="2" t="inlineStr">
+      <c r="DG2" s="2" t="inlineStr">
         <is>
           <t>performance.out.gas</t>
         </is>
       </c>
-      <c r="DB2" s="2" t="inlineStr">
+      <c r="DH2" s="2" t="inlineStr">
         <is>
           <t>performance.out.ammonia</t>
         </is>
       </c>
-      <c r="DC2" s="2" t="inlineStr">
+      <c r="DI2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.HBfeed</t>
         </is>
       </c>
-      <c r="DD2" s="2" t="inlineStr">
+      <c r="DJ2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.syngas</t>
         </is>
       </c>
-      <c r="DE2" s="2" t="inlineStr">
+      <c r="DK2" s="2" t="inlineStr">
         <is>
           <t>performance.out.BTX</t>
         </is>
       </c>
-      <c r="DF2" s="2" t="inlineStr">
+      <c r="DL2" s="2" t="inlineStr">
         <is>
           <t>performance.out.LPG</t>
         </is>
       </c>
-      <c r="DG2" s="2" t="inlineStr">
+      <c r="DM2" s="2" t="inlineStr">
         <is>
           <t>performance.out.pentane</t>
         </is>
       </c>
-      <c r="DH2" s="2" t="inlineStr">
+      <c r="DN2" s="2" t="inlineStr">
         <is>
           <t>performance.out.heatlowT</t>
         </is>
       </c>
-      <c r="DI2" s="2" t="inlineStr">
+      <c r="DO2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.methanol</t>
         </is>
       </c>
-      <c r="DJ2" s="2" t="inlineStr">
+      <c r="DP2" s="2" t="inlineStr">
         <is>
           <t>performance.out.propylene</t>
         </is>
       </c>
-      <c r="DK2" s="2" t="inlineStr">
+      <c r="DQ2" s="2" t="inlineStr">
         <is>
           <t>performance.out.crackergas</t>
         </is>
       </c>
-      <c r="DL2" s="2" t="inlineStr">
+      <c r="DR2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.olefins</t>
         </is>
       </c>
-      <c r="DM2" s="2" t="inlineStr">
+      <c r="DS2" s="2" t="inlineStr">
         <is>
           <t>input_ratios.propane</t>
         </is>
       </c>
-      <c r="DN2" s="2" t="inlineStr">
+      <c r="DT2" s="2" t="inlineStr">
         <is>
           <t>performance.out.HBfeed</t>
         </is>
       </c>
-      <c r="DO2" s="2" t="inlineStr">
+      <c r="DU2" s="2" t="inlineStr">
         <is>
           <t>CAPEX_model</t>
         </is>
       </c>
-      <c r="DP2" s="2" t="inlineStr">
+      <c r="DV2" s="2" t="inlineStr">
         <is>
           <t>unit_CAPEX</t>
         </is>
       </c>
-      <c r="DQ2" s="2" t="inlineStr">
+      <c r="DW2" s="2" t="inlineStr">
         <is>
           <t>fix_CAPEX</t>
         </is>
       </c>
-      <c r="DR2" s="2" t="inlineStr">
+      <c r="DX2" s="2" t="inlineStr">
         <is>
           <t>piecewise_CAPEX.bp_x</t>
         </is>
       </c>
-      <c r="DS2" s="2" t="inlineStr">
+      <c r="DY2" s="2" t="inlineStr">
         <is>
           <t>piecewise_CAPEX.bp_y</t>
         </is>
       </c>
-      <c r="DT2" s="2" t="inlineStr">
+      <c r="DZ2" s="2" t="inlineStr">
         <is>
           <t>OPEX_variable</t>
         </is>
       </c>
-      <c r="DU2" s="2" t="inlineStr">
+      <c r="EA2" s="2" t="inlineStr">
         <is>
           <t>OPEX_fixed</t>
         </is>
       </c>
-      <c r="DV2" s="2" t="inlineStr">
+      <c r="EB2" s="2" t="inlineStr">
         <is>
           <t>steam_production</t>
         </is>
       </c>
-      <c r="DW2" s="2" t="inlineStr">
+      <c r="EC2" s="2" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="DX2" s="2" t="inlineStr">
+      <c r="ED2" s="2" t="inlineStr">
         <is>
           <t>steam_turbine_generator_efficiency</t>
         </is>
       </c>
-      <c r="DY2" s="2" t="inlineStr">
+      <c r="EE2" s="2" t="inlineStr">
         <is>
           <t>size_db</t>
         </is>
       </c>
-      <c r="DZ2" s="2" t="inlineStr">
+      <c r="EF2" s="2" t="inlineStr">
         <is>
           <t>size_ohb</t>
         </is>
       </c>
-      <c r="EA2" s="2" t="inlineStr">
+      <c r="EG2" s="2" t="inlineStr">
         <is>
           <t>max_h2_in</t>
         </is>
       </c>
-      <c r="EB2" s="2" t="inlineStr">
+      <c r="EH2" s="2" t="inlineStr">
         <is>
           <t>max_h2_in_gt</t>
         </is>
       </c>
-      <c r="EC2" s="2" t="inlineStr">
+      <c r="EI2" s="2" t="inlineStr">
         <is>
           <t>rated_power</t>
         </is>
       </c>
-      <c r="ED2" s="2" t="inlineStr">
+      <c r="EJ2" s="2" t="inlineStr">
         <is>
           <t>in_min</t>
         </is>
       </c>
-      <c r="EE2" s="2" t="inlineStr">
+      <c r="EK2" s="2" t="inlineStr">
         <is>
           <t>in_max</t>
         </is>
       </c>
-      <c r="EF2" s="2" t="inlineStr">
+      <c r="EL2" s="2" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="EG2" s="2" t="inlineStr">
+      <c r="EM2" s="2" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="EH2" s="2" t="inlineStr">
+      <c r="EN2" s="2" t="inlineStr">
         <is>
           <t>gamma</t>
         </is>
       </c>
-      <c r="EI2" s="2" t="inlineStr">
+      <c r="EO2" s="2" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="EJ2" s="2" t="inlineStr">
+      <c r="EP2" s="2" t="inlineStr">
         <is>
           <t>T_iso</t>
         </is>
       </c>
-      <c r="EK2" s="2" t="inlineStr">
+      <c r="EQ2" s="2" t="inlineStr">
         <is>
           <t>epsilon</t>
         </is>
       </c>
-      <c r="EL2" s="2" t="inlineStr">
+      <c r="ER2" s="2" t="inlineStr">
         <is>
           <t>max_H2_admixture</t>
         </is>
       </c>
-      <c r="EM2" s="2" t="inlineStr">
+      <c r="ES2" s="2" t="inlineStr">
         <is>
           <t>max_input.hydrogen</t>
         </is>
       </c>
-      <c r="EN2" s="2" t="inlineStr">
+      <c r="ET2" s="2" t="inlineStr">
         <is>
           <t>ramping_rate</t>
         </is>
       </c>
-      <c r="EO2" s="2" t="inlineStr">
+      <c r="EU2" s="2" t="inlineStr">
         <is>
           <t>curtailment</t>
         </is>
       </c>
-      <c r="EP2" s="2" t="inlineStr">
+      <c r="EV2" s="2" t="inlineStr">
         <is>
           <t>var_capex_aux</t>
         </is>
       </c>
-      <c r="EQ2" s="2" t="inlineStr">
+      <c r="EW2" s="2" t="inlineStr">
         <is>
           <t>performance.energy_consumption.in.electricity</t>
         </is>
       </c>
-      <c r="ER2" s="2" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="ES2" s="2" t="inlineStr">
+      <c r="EX2" s="2" t="inlineStr">
         <is>
           <t>injection_capacity_is_decision_var</t>
         </is>
       </c>
-      <c r="ET2" s="2" t="inlineStr">
+      <c r="EY2" s="2" t="inlineStr">
         <is>
           <t>injection_rate_max</t>
         </is>
       </c>
-      <c r="EU2" s="2" t="inlineStr">
+      <c r="EZ2" s="2" t="inlineStr">
         <is>
           <t>capex_injection_cap</t>
         </is>
       </c>
-      <c r="EV2" s="2" t="inlineStr">
+      <c r="FA2" s="2" t="inlineStr">
         <is>
           <t>allow_only_one_direction_precise</t>
-        </is>
-      </c>
-      <c r="EW2" s="2" t="inlineStr">
-        <is>
-          <t>power_energy_ratio</t>
-        </is>
-      </c>
-      <c r="EX2" s="2" t="inlineStr">
-        <is>
-          <t>charge_rate</t>
-        </is>
-      </c>
-      <c r="EY2" s="2" t="inlineStr">
-        <is>
-          <t>discharge_rate</t>
-        </is>
-      </c>
-      <c r="EZ2" s="2" t="inlineStr">
-        <is>
-          <t>capex_charging_power</t>
-        </is>
-      </c>
-      <c r="FA2" s="2" t="inlineStr">
-        <is>
-          <t>capex_discharging_power</t>
         </is>
       </c>
     </row>
@@ -1374,8 +1379,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1602,11 +1609,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>impossible</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>CAPEX in EUR/(t/hCO2_out) after pre-processing, opex_variable in EUR/(t/h_CO2_out), opex_fixed in % of up-front CAPEX</t>
@@ -1847,11 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>impossible</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>CAPEX in EUR/(t/hCO2_out) after pre-processing, opex_variable in EUR/(t/h_CO2_out), opex_fixed in % of up-front CAPEX</t>
@@ -2092,11 +2091,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>impossible</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>CAPEX in EUR/(t/hCO2_out) after pre-processing, opex_variable in EUR/(t/h_CO2_out), opex_fixed in % of up-front CAPEX</t>
@@ -2629,8 +2624,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>2</v>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2902,8 +2899,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v>1</v>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3175,8 +3174,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S10" t="n">
-        <v>1</v>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3448,8 +3449,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S11" t="n">
-        <v>1</v>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -3721,8 +3724,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>2</v>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3994,8 +3999,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>2</v>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -4267,8 +4274,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>1</v>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -4516,8 +4525,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S15" t="n">
-        <v>1</v>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -4767,8 +4778,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>1</v>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -5018,8 +5031,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>1</v>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -5271,8 +5286,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S18" t="n">
-        <v>1</v>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -5548,8 +5565,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S19" t="n">
-        <v>1</v>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -6178,22 +6197,34 @@
       <c r="BV21" t="n">
         <v>0</v>
       </c>
-      <c r="BW21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
         <v>0</v>
       </c>
-      <c r="CA21" t="inlineStr"/>
-      <c r="CB21" t="inlineStr"/>
-      <c r="CC21" t="inlineStr"/>
-      <c r="CD21" t="inlineStr"/>
-      <c r="CE21" t="inlineStr"/>
-      <c r="CF21" t="inlineStr"/>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0</v>
+      </c>
       <c r="CG21" t="inlineStr"/>
       <c r="CH21" t="inlineStr"/>
       <c r="CI21" t="inlineStr"/>
@@ -6590,8 +6621,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S23" t="n">
-        <v>2</v>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -6714,32 +6747,32 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="inlineStr"/>
-      <c r="CA23" t="inlineStr">
+      <c r="CA23" t="inlineStr"/>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr">
         <is>
           <t>0, 4</t>
         </is>
       </c>
-      <c r="CB23" t="n">
+      <c r="CH23" t="n">
         <v>0.001</v>
       </c>
-      <c r="CC23" t="n">
+      <c r="CI23" t="n">
         <v>1</v>
       </c>
-      <c r="CD23" t="n">
+      <c r="CJ23" t="n">
         <v>1</v>
       </c>
-      <c r="CE23" t="n">
+      <c r="CK23" t="n">
         <v>1</v>
       </c>
-      <c r="CF23" t="n">
+      <c r="CL23" t="n">
         <v>1</v>
       </c>
-      <c r="CG23" t="inlineStr"/>
-      <c r="CH23" t="inlineStr"/>
-      <c r="CI23" t="inlineStr"/>
-      <c r="CJ23" t="inlineStr"/>
-      <c r="CK23" t="inlineStr"/>
-      <c r="CL23" t="inlineStr"/>
       <c r="CM23" t="inlineStr"/>
       <c r="CN23" t="inlineStr"/>
       <c r="CO23" t="inlineStr"/>
@@ -6873,8 +6906,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S24" t="n">
-        <v>2</v>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -7003,36 +7038,36 @@
       <c r="CD24" t="inlineStr"/>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="inlineStr"/>
-      <c r="CG24" t="inlineStr">
+      <c r="CG24" t="inlineStr"/>
+      <c r="CH24" t="inlineStr"/>
+      <c r="CI24" t="inlineStr"/>
+      <c r="CJ24" t="inlineStr"/>
+      <c r="CK24" t="inlineStr"/>
+      <c r="CL24" t="inlineStr"/>
+      <c r="CM24" t="inlineStr">
         <is>
           <t>0, 0.322</t>
         </is>
       </c>
-      <c r="CH24" t="inlineStr">
+      <c r="CN24" t="inlineStr">
         <is>
           <t>0, 0.272</t>
         </is>
       </c>
-      <c r="CI24" t="n">
+      <c r="CO24" t="n">
         <v>1</v>
       </c>
-      <c r="CJ24" t="n">
+      <c r="CP24" t="n">
         <v>1</v>
       </c>
-      <c r="CK24" t="n">
+      <c r="CQ24" t="n">
         <v>0.145</v>
       </c>
-      <c r="CL24" t="inlineStr">
+      <c r="CR24" t="inlineStr">
         <is>
           <t>MEA_large</t>
         </is>
       </c>
-      <c r="CM24" t="inlineStr"/>
-      <c r="CN24" t="inlineStr"/>
-      <c r="CO24" t="inlineStr"/>
-      <c r="CP24" t="inlineStr"/>
-      <c r="CQ24" t="inlineStr"/>
-      <c r="CR24" t="inlineStr"/>
       <c r="CS24" t="inlineStr"/>
       <c r="CT24" t="inlineStr"/>
       <c r="CU24" t="inlineStr"/>
@@ -7160,8 +7195,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S25" t="n">
-        <v>2</v>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -7298,25 +7335,25 @@
       <c r="CJ25" t="inlineStr"/>
       <c r="CK25" t="inlineStr"/>
       <c r="CL25" t="inlineStr"/>
-      <c r="CM25" t="inlineStr">
-        <is>
-          <t>0, 0.602</t>
-        </is>
-      </c>
-      <c r="CN25" t="inlineStr">
-        <is>
-          <t>0, 0.019</t>
-        </is>
-      </c>
-      <c r="CO25" t="n">
-        <v>1</v>
-      </c>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
       <c r="CP25" t="inlineStr"/>
       <c r="CQ25" t="inlineStr"/>
       <c r="CR25" t="inlineStr"/>
-      <c r="CS25" t="inlineStr"/>
-      <c r="CT25" t="inlineStr"/>
-      <c r="CU25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>0, 0.602</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
+          <t>0, 0.019</t>
+        </is>
+      </c>
+      <c r="CU25" t="n">
+        <v>1</v>
+      </c>
       <c r="CV25" t="inlineStr"/>
       <c r="CW25" t="inlineStr"/>
       <c r="CX25" t="inlineStr"/>
@@ -7441,8 +7478,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S26" t="n">
-        <v>1</v>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -7568,55 +7607,55 @@
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="inlineStr"/>
       <c r="CA26" t="inlineStr"/>
-      <c r="CB26" t="n">
+      <c r="CB26" t="inlineStr"/>
+      <c r="CC26" t="inlineStr"/>
+      <c r="CD26" t="inlineStr"/>
+      <c r="CE26" t="inlineStr"/>
+      <c r="CF26" t="inlineStr"/>
+      <c r="CG26" t="inlineStr"/>
+      <c r="CH26" t="n">
         <v>1</v>
       </c>
-      <c r="CC26" t="n">
+      <c r="CI26" t="n">
         <v>1</v>
       </c>
-      <c r="CD26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG26" t="inlineStr"/>
-      <c r="CH26" t="inlineStr"/>
-      <c r="CI26" t="inlineStr"/>
       <c r="CJ26" t="n">
         <v>1</v>
       </c>
       <c r="CK26" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="CL26" t="inlineStr">
-        <is>
-          <t>MEA_large</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="CL26" t="n">
+        <v>1</v>
       </c>
       <c r="CM26" t="inlineStr"/>
       <c r="CN26" t="inlineStr"/>
       <c r="CO26" t="inlineStr"/>
-      <c r="CP26" t="inlineStr">
-        <is>
-          <t>0, 1</t>
-        </is>
+      <c r="CP26" t="n">
+        <v>1</v>
       </c>
       <c r="CQ26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>0.082</v>
+        <v>0.062</v>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>MEA_large</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr"/>
       <c r="CT26" t="inlineStr"/>
       <c r="CU26" t="inlineStr"/>
-      <c r="CV26" t="inlineStr"/>
-      <c r="CW26" t="inlineStr"/>
-      <c r="CX26" t="inlineStr"/>
+      <c r="CV26" t="inlineStr">
+        <is>
+          <t>0, 1</t>
+        </is>
+      </c>
+      <c r="CW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX26" t="n">
+        <v>0.082</v>
+      </c>
       <c r="CY26" t="inlineStr"/>
       <c r="CZ26" t="inlineStr"/>
       <c r="DA26" t="inlineStr"/>
@@ -7738,8 +7777,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S27" t="n">
-        <v>2</v>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -7879,31 +7920,31 @@
       <c r="CM27" t="inlineStr"/>
       <c r="CN27" t="inlineStr"/>
       <c r="CO27" t="inlineStr"/>
-      <c r="CP27" t="inlineStr">
+      <c r="CP27" t="inlineStr"/>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="inlineStr"/>
+      <c r="CS27" t="inlineStr"/>
+      <c r="CT27" t="inlineStr"/>
+      <c r="CU27" t="inlineStr"/>
+      <c r="CV27" t="inlineStr">
         <is>
           <t>0, 1</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
+      <c r="CW27" t="n">
         <v>1</v>
       </c>
-      <c r="CR27" t="inlineStr"/>
-      <c r="CS27" t="inlineStr">
+      <c r="CX27" t="inlineStr"/>
+      <c r="CY27" t="inlineStr">
         <is>
           <t>0, 0.05</t>
         </is>
       </c>
-      <c r="CT27" t="inlineStr">
+      <c r="CZ27" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
       </c>
-      <c r="CU27" t="inlineStr"/>
-      <c r="CV27" t="inlineStr"/>
-      <c r="CW27" t="inlineStr"/>
-      <c r="CX27" t="inlineStr"/>
-      <c r="CY27" t="inlineStr"/>
-      <c r="CZ27" t="inlineStr"/>
       <c r="DA27" t="inlineStr"/>
       <c r="DB27" t="inlineStr"/>
       <c r="DC27" t="inlineStr"/>
@@ -8023,8 +8064,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S28" t="n">
-        <v>2</v>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -8155,35 +8198,35 @@
       <c r="CD28" t="inlineStr"/>
       <c r="CE28" t="inlineStr"/>
       <c r="CF28" t="inlineStr"/>
-      <c r="CG28" t="inlineStr">
-        <is>
-          <t>0, 0.679</t>
-        </is>
-      </c>
+      <c r="CG28" t="inlineStr"/>
       <c r="CH28" t="inlineStr"/>
       <c r="CI28" t="inlineStr"/>
       <c r="CJ28" t="inlineStr"/>
       <c r="CK28" t="inlineStr"/>
       <c r="CL28" t="inlineStr"/>
-      <c r="CM28" t="inlineStr"/>
+      <c r="CM28" t="inlineStr">
+        <is>
+          <t>0, 0.679</t>
+        </is>
+      </c>
       <c r="CN28" t="inlineStr"/>
-      <c r="CO28" t="n">
-        <v>1</v>
-      </c>
+      <c r="CO28" t="inlineStr"/>
       <c r="CP28" t="inlineStr"/>
       <c r="CQ28" t="inlineStr"/>
       <c r="CR28" t="inlineStr"/>
       <c r="CS28" t="inlineStr"/>
       <c r="CT28" t="inlineStr"/>
       <c r="CU28" t="n">
-        <v>4.58</v>
+        <v>1</v>
       </c>
       <c r="CV28" t="inlineStr"/>
       <c r="CW28" t="inlineStr"/>
       <c r="CX28" t="inlineStr"/>
       <c r="CY28" t="inlineStr"/>
       <c r="CZ28" t="inlineStr"/>
-      <c r="DA28" t="inlineStr"/>
+      <c r="DA28" t="n">
+        <v>4.58</v>
+      </c>
       <c r="DB28" t="inlineStr"/>
       <c r="DC28" t="inlineStr"/>
       <c r="DD28" t="inlineStr"/>
@@ -8302,8 +8345,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S29" t="n">
-        <v>2</v>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -8435,11 +8480,7 @@
       <c r="CE29" t="inlineStr"/>
       <c r="CF29" t="inlineStr"/>
       <c r="CG29" t="inlineStr"/>
-      <c r="CH29" t="inlineStr">
-        <is>
-          <t>0, 0.201</t>
-        </is>
-      </c>
+      <c r="CH29" t="inlineStr"/>
       <c r="CI29" t="inlineStr"/>
       <c r="CJ29" t="inlineStr"/>
       <c r="CK29" t="inlineStr"/>
@@ -8447,7 +8488,7 @@
       <c r="CM29" t="inlineStr"/>
       <c r="CN29" t="inlineStr">
         <is>
-          <t>0, 0.927</t>
+          <t>0, 0.201</t>
         </is>
       </c>
       <c r="CO29" t="inlineStr"/>
@@ -8457,19 +8498,23 @@
       <c r="CS29" t="inlineStr"/>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>0, 0.927</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr"/>
-      <c r="CV29" t="n">
-        <v>1</v>
-      </c>
+      <c r="CV29" t="inlineStr"/>
       <c r="CW29" t="inlineStr"/>
       <c r="CX29" t="inlineStr"/>
       <c r="CY29" t="inlineStr"/>
-      <c r="CZ29" t="inlineStr"/>
+      <c r="CZ29" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
       <c r="DA29" t="inlineStr"/>
-      <c r="DB29" t="inlineStr"/>
+      <c r="DB29" t="n">
+        <v>1</v>
+      </c>
       <c r="DC29" t="inlineStr"/>
       <c r="DD29" t="inlineStr"/>
       <c r="DE29" t="inlineStr"/>
@@ -8587,8 +8632,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S30" t="n">
-        <v>2</v>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -8732,26 +8779,26 @@
       <c r="CQ30" t="inlineStr"/>
       <c r="CR30" t="inlineStr"/>
       <c r="CS30" t="inlineStr"/>
-      <c r="CT30" t="inlineStr">
-        <is>
-          <t>electricity</t>
-        </is>
-      </c>
+      <c r="CT30" t="inlineStr"/>
       <c r="CU30" t="inlineStr"/>
-      <c r="CV30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW30" t="inlineStr">
-        <is>
-          <t>0, 0.187</t>
-        </is>
-      </c>
+      <c r="CV30" t="inlineStr"/>
+      <c r="CW30" t="inlineStr"/>
       <c r="CX30" t="inlineStr"/>
       <c r="CY30" t="inlineStr"/>
-      <c r="CZ30" t="inlineStr"/>
+      <c r="CZ30" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
       <c r="DA30" t="inlineStr"/>
-      <c r="DB30" t="inlineStr"/>
-      <c r="DC30" t="inlineStr"/>
+      <c r="DB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC30" t="inlineStr">
+        <is>
+          <t>0, 0.187</t>
+        </is>
+      </c>
       <c r="DD30" t="inlineStr"/>
       <c r="DE30" t="inlineStr"/>
       <c r="DF30" t="inlineStr"/>
@@ -8868,8 +8915,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S31" t="n">
-        <v>2</v>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -9006,32 +9055,32 @@
       <c r="CJ31" t="inlineStr"/>
       <c r="CK31" t="inlineStr"/>
       <c r="CL31" t="inlineStr"/>
-      <c r="CM31" t="inlineStr">
-        <is>
-          <t>0, 0.592</t>
-        </is>
-      </c>
+      <c r="CM31" t="inlineStr"/>
       <c r="CN31" t="inlineStr"/>
       <c r="CO31" t="inlineStr"/>
       <c r="CP31" t="inlineStr"/>
       <c r="CQ31" t="inlineStr"/>
-      <c r="CR31" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="CS31" t="inlineStr"/>
+      <c r="CR31" t="inlineStr"/>
+      <c r="CS31" t="inlineStr">
+        <is>
+          <t>0, 0.592</t>
+        </is>
+      </c>
       <c r="CT31" t="inlineStr"/>
       <c r="CU31" t="inlineStr"/>
       <c r="CV31" t="inlineStr"/>
       <c r="CW31" t="inlineStr"/>
       <c r="CX31" t="n">
-        <v>1</v>
+        <v>0.313</v>
       </c>
       <c r="CY31" t="inlineStr"/>
       <c r="CZ31" t="inlineStr"/>
       <c r="DA31" t="inlineStr"/>
       <c r="DB31" t="inlineStr"/>
       <c r="DC31" t="inlineStr"/>
-      <c r="DD31" t="inlineStr"/>
+      <c r="DD31" t="n">
+        <v>1</v>
+      </c>
       <c r="DE31" t="inlineStr"/>
       <c r="DF31" t="inlineStr"/>
       <c r="DG31" t="inlineStr"/>
@@ -9147,8 +9196,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S32" t="n">
-        <v>1</v>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -9292,29 +9343,29 @@
       <c r="CO32" t="inlineStr"/>
       <c r="CP32" t="inlineStr"/>
       <c r="CQ32" t="inlineStr"/>
-      <c r="CR32" t="n">
-        <v>0.431</v>
-      </c>
+      <c r="CR32" t="inlineStr"/>
       <c r="CS32" t="inlineStr"/>
       <c r="CT32" t="inlineStr"/>
       <c r="CU32" t="inlineStr"/>
       <c r="CV32" t="inlineStr"/>
       <c r="CW32" t="inlineStr"/>
-      <c r="CX32" t="inlineStr"/>
-      <c r="CY32" t="inlineStr">
-        <is>
-          <t>0, 1</t>
-        </is>
-      </c>
-      <c r="CZ32" t="n">
-        <v>1</v>
-      </c>
+      <c r="CX32" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="CY32" t="inlineStr"/>
+      <c r="CZ32" t="inlineStr"/>
       <c r="DA32" t="inlineStr"/>
       <c r="DB32" t="inlineStr"/>
       <c r="DC32" t="inlineStr"/>
       <c r="DD32" t="inlineStr"/>
-      <c r="DE32" t="inlineStr"/>
-      <c r="DF32" t="inlineStr"/>
+      <c r="DE32" t="inlineStr">
+        <is>
+          <t>0, 1</t>
+        </is>
+      </c>
+      <c r="DF32" t="n">
+        <v>1</v>
+      </c>
       <c r="DG32" t="inlineStr"/>
       <c r="DH32" t="inlineStr"/>
       <c r="DI32" t="inlineStr"/>
@@ -9428,8 +9479,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S33" t="n">
-        <v>1</v>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -9582,20 +9635,20 @@
       <c r="CV33" t="inlineStr"/>
       <c r="CW33" t="inlineStr"/>
       <c r="CX33" t="inlineStr"/>
-      <c r="CY33" t="inlineStr">
-        <is>
-          <t>0, 1</t>
-        </is>
-      </c>
-      <c r="CZ33" t="n">
-        <v>1</v>
-      </c>
+      <c r="CY33" t="inlineStr"/>
+      <c r="CZ33" t="inlineStr"/>
       <c r="DA33" t="inlineStr"/>
       <c r="DB33" t="inlineStr"/>
       <c r="DC33" t="inlineStr"/>
       <c r="DD33" t="inlineStr"/>
-      <c r="DE33" t="inlineStr"/>
-      <c r="DF33" t="inlineStr"/>
+      <c r="DE33" t="inlineStr">
+        <is>
+          <t>0, 1</t>
+        </is>
+      </c>
+      <c r="DF33" t="n">
+        <v>1</v>
+      </c>
       <c r="DG33" t="inlineStr"/>
       <c r="DH33" t="inlineStr"/>
       <c r="DI33" t="inlineStr"/>
@@ -9709,8 +9762,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S34" t="n">
-        <v>1</v>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -9851,39 +9906,39 @@
       <c r="CJ34" t="inlineStr"/>
       <c r="CK34" t="inlineStr"/>
       <c r="CL34" t="inlineStr"/>
-      <c r="CM34" t="inlineStr">
-        <is>
-          <t>0, 0.3025</t>
-        </is>
-      </c>
+      <c r="CM34" t="inlineStr"/>
       <c r="CN34" t="inlineStr"/>
       <c r="CO34" t="inlineStr"/>
       <c r="CP34" t="inlineStr"/>
       <c r="CQ34" t="inlineStr"/>
-      <c r="CR34" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="CS34" t="inlineStr"/>
+      <c r="CR34" t="inlineStr"/>
+      <c r="CS34" t="inlineStr">
+        <is>
+          <t>0, 0.3025</t>
+        </is>
+      </c>
       <c r="CT34" t="inlineStr"/>
       <c r="CU34" t="inlineStr"/>
       <c r="CV34" t="inlineStr"/>
       <c r="CW34" t="inlineStr"/>
-      <c r="CX34" t="inlineStr"/>
+      <c r="CX34" t="n">
+        <v>0.492</v>
+      </c>
       <c r="CY34" t="inlineStr"/>
-      <c r="CZ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="DA34" t="inlineStr">
-        <is>
-          <t>0, 2.3491</t>
-        </is>
-      </c>
+      <c r="CZ34" t="inlineStr"/>
+      <c r="DA34" t="inlineStr"/>
       <c r="DB34" t="inlineStr"/>
       <c r="DC34" t="inlineStr"/>
       <c r="DD34" t="inlineStr"/>
       <c r="DE34" t="inlineStr"/>
-      <c r="DF34" t="inlineStr"/>
-      <c r="DG34" t="inlineStr"/>
+      <c r="DF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG34" t="inlineStr">
+        <is>
+          <t>0, 2.3491</t>
+        </is>
+      </c>
       <c r="DH34" t="inlineStr"/>
       <c r="DI34" t="inlineStr"/>
       <c r="DJ34" t="inlineStr"/>
@@ -9996,8 +10051,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S35" t="n">
-        <v>2</v>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -10140,33 +10197,33 @@
       <c r="CP35" t="inlineStr"/>
       <c r="CQ35" t="inlineStr"/>
       <c r="CR35" t="inlineStr"/>
-      <c r="CS35" t="inlineStr">
-        <is>
-          <t>0, 0.114</t>
-        </is>
-      </c>
+      <c r="CS35" t="inlineStr"/>
       <c r="CT35" t="inlineStr"/>
       <c r="CU35" t="inlineStr"/>
       <c r="CV35" t="inlineStr"/>
       <c r="CW35" t="inlineStr"/>
       <c r="CX35" t="inlineStr"/>
-      <c r="CY35" t="inlineStr"/>
+      <c r="CY35" t="inlineStr">
+        <is>
+          <t>0, 0.114</t>
+        </is>
+      </c>
       <c r="CZ35" t="inlineStr"/>
       <c r="DA35" t="inlineStr"/>
-      <c r="DB35" t="inlineStr">
-        <is>
-          <t>0, 0.168</t>
-        </is>
-      </c>
-      <c r="DC35" t="n">
-        <v>1</v>
-      </c>
+      <c r="DB35" t="inlineStr"/>
+      <c r="DC35" t="inlineStr"/>
       <c r="DD35" t="inlineStr"/>
       <c r="DE35" t="inlineStr"/>
       <c r="DF35" t="inlineStr"/>
       <c r="DG35" t="inlineStr"/>
-      <c r="DH35" t="inlineStr"/>
-      <c r="DI35" t="inlineStr"/>
+      <c r="DH35" t="inlineStr">
+        <is>
+          <t>0, 0.168</t>
+        </is>
+      </c>
+      <c r="DI35" t="n">
+        <v>1</v>
+      </c>
       <c r="DJ35" t="inlineStr"/>
       <c r="DK35" t="inlineStr"/>
       <c r="DL35" t="inlineStr"/>
@@ -10277,8 +10334,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S36" t="n">
-        <v>2</v>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -10409,44 +10468,44 @@
       <c r="CD36" t="inlineStr"/>
       <c r="CE36" t="inlineStr"/>
       <c r="CF36" t="inlineStr"/>
-      <c r="CG36" t="inlineStr">
-        <is>
-          <t>0, 0.823</t>
-        </is>
-      </c>
+      <c r="CG36" t="inlineStr"/>
       <c r="CH36" t="inlineStr"/>
       <c r="CI36" t="inlineStr"/>
       <c r="CJ36" t="inlineStr"/>
       <c r="CK36" t="inlineStr"/>
       <c r="CL36" t="inlineStr"/>
-      <c r="CM36" t="inlineStr"/>
+      <c r="CM36" t="inlineStr">
+        <is>
+          <t>0, 0.823</t>
+        </is>
+      </c>
       <c r="CN36" t="inlineStr"/>
       <c r="CO36" t="inlineStr"/>
       <c r="CP36" t="inlineStr"/>
       <c r="CQ36" t="inlineStr"/>
-      <c r="CR36" t="n">
-        <v>0.572</v>
-      </c>
+      <c r="CR36" t="inlineStr"/>
       <c r="CS36" t="inlineStr"/>
       <c r="CT36" t="inlineStr"/>
       <c r="CU36" t="inlineStr"/>
       <c r="CV36" t="inlineStr"/>
       <c r="CW36" t="inlineStr"/>
-      <c r="CX36" t="inlineStr"/>
+      <c r="CX36" t="n">
+        <v>0.572</v>
+      </c>
       <c r="CY36" t="inlineStr"/>
       <c r="CZ36" t="inlineStr"/>
       <c r="DA36" t="inlineStr"/>
       <c r="DB36" t="inlineStr"/>
       <c r="DC36" t="inlineStr"/>
-      <c r="DD36" t="n">
-        <v>1</v>
-      </c>
+      <c r="DD36" t="inlineStr"/>
       <c r="DE36" t="inlineStr"/>
       <c r="DF36" t="inlineStr"/>
       <c r="DG36" t="inlineStr"/>
       <c r="DH36" t="inlineStr"/>
       <c r="DI36" t="inlineStr"/>
-      <c r="DJ36" t="inlineStr"/>
+      <c r="DJ36" t="n">
+        <v>1</v>
+      </c>
       <c r="DK36" t="inlineStr"/>
       <c r="DL36" t="inlineStr"/>
       <c r="DM36" t="inlineStr"/>
@@ -10556,8 +10615,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S37" t="n">
-        <v>1</v>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -10699,50 +10760,50 @@
       <c r="CO37" t="inlineStr"/>
       <c r="CP37" t="inlineStr"/>
       <c r="CQ37" t="inlineStr"/>
-      <c r="CR37" t="n">
-        <v>0.149</v>
-      </c>
+      <c r="CR37" t="inlineStr"/>
       <c r="CS37" t="inlineStr"/>
       <c r="CT37" t="inlineStr"/>
       <c r="CU37" t="inlineStr"/>
       <c r="CV37" t="inlineStr"/>
       <c r="CW37" t="inlineStr"/>
-      <c r="CX37" t="inlineStr"/>
+      <c r="CX37" t="n">
+        <v>0.149</v>
+      </c>
       <c r="CY37" t="inlineStr"/>
       <c r="CZ37" t="inlineStr"/>
       <c r="DA37" t="inlineStr"/>
       <c r="DB37" t="inlineStr"/>
       <c r="DC37" t="inlineStr"/>
       <c r="DD37" t="inlineStr"/>
-      <c r="DE37" t="inlineStr">
+      <c r="DE37" t="inlineStr"/>
+      <c r="DF37" t="inlineStr"/>
+      <c r="DG37" t="inlineStr"/>
+      <c r="DH37" t="inlineStr"/>
+      <c r="DI37" t="inlineStr"/>
+      <c r="DJ37" t="inlineStr"/>
+      <c r="DK37" t="inlineStr">
         <is>
           <t>0, 0.155</t>
         </is>
       </c>
-      <c r="DF37" t="inlineStr">
+      <c r="DL37" t="inlineStr">
         <is>
           <t>0, 0.196</t>
         </is>
       </c>
-      <c r="DG37" t="inlineStr">
+      <c r="DM37" t="inlineStr">
         <is>
           <t>0, 0.043</t>
         </is>
       </c>
-      <c r="DH37" t="inlineStr">
+      <c r="DN37" t="inlineStr">
         <is>
           <t>0, 0.236</t>
         </is>
       </c>
-      <c r="DI37" t="n">
+      <c r="DO37" t="n">
         <v>1</v>
       </c>
-      <c r="DJ37" t="inlineStr"/>
-      <c r="DK37" t="inlineStr"/>
-      <c r="DL37" t="inlineStr"/>
-      <c r="DM37" t="inlineStr"/>
-      <c r="DN37" t="inlineStr"/>
-      <c r="DO37" t="inlineStr"/>
       <c r="DP37" t="inlineStr"/>
       <c r="DQ37" t="inlineStr"/>
       <c r="DR37" t="inlineStr"/>
@@ -10847,8 +10908,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S38" t="n">
-        <v>2</v>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -10985,17 +11048,17 @@
       <c r="CJ38" t="inlineStr"/>
       <c r="CK38" t="inlineStr"/>
       <c r="CL38" t="inlineStr"/>
-      <c r="CM38" t="inlineStr">
-        <is>
-          <t>0, 0.163</t>
-        </is>
-      </c>
+      <c r="CM38" t="inlineStr"/>
       <c r="CN38" t="inlineStr"/>
       <c r="CO38" t="inlineStr"/>
       <c r="CP38" t="inlineStr"/>
       <c r="CQ38" t="inlineStr"/>
       <c r="CR38" t="inlineStr"/>
-      <c r="CS38" t="inlineStr"/>
+      <c r="CS38" t="inlineStr">
+        <is>
+          <t>0, 0.163</t>
+        </is>
+      </c>
       <c r="CT38" t="inlineStr"/>
       <c r="CU38" t="inlineStr"/>
       <c r="CV38" t="inlineStr"/>
@@ -11011,20 +11074,20 @@
       <c r="DF38" t="inlineStr"/>
       <c r="DG38" t="inlineStr"/>
       <c r="DH38" t="inlineStr"/>
-      <c r="DI38" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ38" t="inlineStr">
-        <is>
-          <t>0, 0.165</t>
-        </is>
-      </c>
+      <c r="DI38" t="inlineStr"/>
+      <c r="DJ38" t="inlineStr"/>
       <c r="DK38" t="inlineStr"/>
       <c r="DL38" t="inlineStr"/>
       <c r="DM38" t="inlineStr"/>
       <c r="DN38" t="inlineStr"/>
-      <c r="DO38" t="inlineStr"/>
-      <c r="DP38" t="inlineStr"/>
+      <c r="DO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP38" t="inlineStr">
+        <is>
+          <t>0, 0.165</t>
+        </is>
+      </c>
       <c r="DQ38" t="inlineStr"/>
       <c r="DR38" t="inlineStr"/>
       <c r="DS38" t="inlineStr"/>
@@ -11128,8 +11191,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S39" t="n">
-        <v>1</v>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -11255,55 +11320,55 @@
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="inlineStr"/>
       <c r="CA39" t="inlineStr"/>
-      <c r="CB39" t="n">
+      <c r="CB39" t="inlineStr"/>
+      <c r="CC39" t="inlineStr"/>
+      <c r="CD39" t="inlineStr"/>
+      <c r="CE39" t="inlineStr"/>
+      <c r="CF39" t="inlineStr"/>
+      <c r="CG39" t="inlineStr"/>
+      <c r="CH39" t="n">
         <v>1</v>
       </c>
-      <c r="CC39" t="n">
+      <c r="CI39" t="n">
         <v>1</v>
       </c>
-      <c r="CD39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG39" t="inlineStr"/>
-      <c r="CH39" t="inlineStr"/>
-      <c r="CI39" t="inlineStr"/>
       <c r="CJ39" t="n">
         <v>1</v>
       </c>
       <c r="CK39" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="CL39" t="inlineStr">
-        <is>
-          <t>MEA_large</t>
-        </is>
-      </c>
-      <c r="CM39" t="inlineStr">
-        <is>
-          <t>0, 0.3025</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="CL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM39" t="inlineStr"/>
       <c r="CN39" t="inlineStr"/>
       <c r="CO39" t="inlineStr"/>
-      <c r="CP39" t="inlineStr"/>
+      <c r="CP39" t="n">
+        <v>1</v>
+      </c>
       <c r="CQ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="CS39" t="inlineStr"/>
+        <v>0.062</v>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>MEA_large</t>
+        </is>
+      </c>
+      <c r="CS39" t="inlineStr">
+        <is>
+          <t>0, 0.3025</t>
+        </is>
+      </c>
       <c r="CT39" t="inlineStr"/>
       <c r="CU39" t="inlineStr"/>
       <c r="CV39" t="inlineStr"/>
-      <c r="CW39" t="inlineStr"/>
-      <c r="CX39" t="inlineStr"/>
+      <c r="CW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX39" t="n">
+        <v>0.082</v>
+      </c>
       <c r="CY39" t="inlineStr"/>
       <c r="CZ39" t="inlineStr"/>
       <c r="DA39" t="inlineStr"/>
@@ -11315,22 +11380,22 @@
       <c r="DG39" t="inlineStr"/>
       <c r="DH39" t="inlineStr"/>
       <c r="DI39" t="inlineStr"/>
-      <c r="DJ39" t="inlineStr">
-        <is>
-          <t>0, 0.1363</t>
-        </is>
-      </c>
-      <c r="DK39" t="inlineStr">
-        <is>
-          <t>0, 0.781</t>
-        </is>
-      </c>
+      <c r="DJ39" t="inlineStr"/>
+      <c r="DK39" t="inlineStr"/>
       <c r="DL39" t="inlineStr"/>
       <c r="DM39" t="inlineStr"/>
       <c r="DN39" t="inlineStr"/>
       <c r="DO39" t="inlineStr"/>
-      <c r="DP39" t="inlineStr"/>
-      <c r="DQ39" t="inlineStr"/>
+      <c r="DP39" t="inlineStr">
+        <is>
+          <t>0, 0.1363</t>
+        </is>
+      </c>
+      <c r="DQ39" t="inlineStr">
+        <is>
+          <t>0, 0.781</t>
+        </is>
+      </c>
       <c r="DR39" t="inlineStr"/>
       <c r="DS39" t="inlineStr"/>
       <c r="DT39" t="inlineStr"/>
@@ -11433,8 +11498,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S40" t="n">
-        <v>2</v>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -11571,34 +11638,34 @@
       <c r="CJ40" t="inlineStr"/>
       <c r="CK40" t="inlineStr"/>
       <c r="CL40" t="inlineStr"/>
-      <c r="CM40" t="inlineStr">
-        <is>
-          <t>0, 0.3025</t>
-        </is>
-      </c>
+      <c r="CM40" t="inlineStr"/>
       <c r="CN40" t="inlineStr"/>
       <c r="CO40" t="inlineStr"/>
       <c r="CP40" t="inlineStr"/>
-      <c r="CQ40" t="n">
-        <v>1</v>
-      </c>
+      <c r="CQ40" t="inlineStr"/>
       <c r="CR40" t="inlineStr"/>
       <c r="CS40" t="inlineStr">
         <is>
-          <t>0, 0.05</t>
-        </is>
-      </c>
-      <c r="CT40" t="inlineStr">
-        <is>
-          <t>electricity</t>
-        </is>
-      </c>
+          <t>0, 0.3025</t>
+        </is>
+      </c>
+      <c r="CT40" t="inlineStr"/>
       <c r="CU40" t="inlineStr"/>
       <c r="CV40" t="inlineStr"/>
-      <c r="CW40" t="inlineStr"/>
+      <c r="CW40" t="n">
+        <v>1</v>
+      </c>
       <c r="CX40" t="inlineStr"/>
-      <c r="CY40" t="inlineStr"/>
-      <c r="CZ40" t="inlineStr"/>
+      <c r="CY40" t="inlineStr">
+        <is>
+          <t>0, 0.05</t>
+        </is>
+      </c>
+      <c r="CZ40" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
       <c r="DA40" t="inlineStr"/>
       <c r="DB40" t="inlineStr"/>
       <c r="DC40" t="inlineStr"/>
@@ -11608,22 +11675,22 @@
       <c r="DG40" t="inlineStr"/>
       <c r="DH40" t="inlineStr"/>
       <c r="DI40" t="inlineStr"/>
-      <c r="DJ40" t="inlineStr">
-        <is>
-          <t>0, 0.1363</t>
-        </is>
-      </c>
-      <c r="DK40" t="inlineStr">
-        <is>
-          <t>0, 2.649</t>
-        </is>
-      </c>
+      <c r="DJ40" t="inlineStr"/>
+      <c r="DK40" t="inlineStr"/>
       <c r="DL40" t="inlineStr"/>
       <c r="DM40" t="inlineStr"/>
       <c r="DN40" t="inlineStr"/>
       <c r="DO40" t="inlineStr"/>
-      <c r="DP40" t="inlineStr"/>
-      <c r="DQ40" t="inlineStr"/>
+      <c r="DP40" t="inlineStr">
+        <is>
+          <t>0, 0.1363</t>
+        </is>
+      </c>
+      <c r="DQ40" t="inlineStr">
+        <is>
+          <t>0, 2.649</t>
+        </is>
+      </c>
       <c r="DR40" t="inlineStr"/>
       <c r="DS40" t="inlineStr"/>
       <c r="DT40" t="inlineStr"/>
@@ -11726,8 +11793,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S41" t="n">
-        <v>1</v>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -11862,28 +11931,28 @@
       <c r="CJ41" t="inlineStr"/>
       <c r="CK41" t="inlineStr"/>
       <c r="CL41" t="inlineStr"/>
-      <c r="CM41" t="inlineStr">
-        <is>
-          <t>0, 0.3025</t>
-        </is>
-      </c>
+      <c r="CM41" t="inlineStr"/>
       <c r="CN41" t="inlineStr"/>
       <c r="CO41" t="inlineStr"/>
       <c r="CP41" t="inlineStr"/>
       <c r="CQ41" t="inlineStr"/>
       <c r="CR41" t="inlineStr"/>
-      <c r="CS41" t="inlineStr"/>
-      <c r="CT41" t="inlineStr">
-        <is>
-          <t>electricity</t>
-        </is>
-      </c>
+      <c r="CS41" t="inlineStr">
+        <is>
+          <t>0, 0.3025</t>
+        </is>
+      </c>
+      <c r="CT41" t="inlineStr"/>
       <c r="CU41" t="inlineStr"/>
       <c r="CV41" t="inlineStr"/>
       <c r="CW41" t="inlineStr"/>
       <c r="CX41" t="inlineStr"/>
       <c r="CY41" t="inlineStr"/>
-      <c r="CZ41" t="inlineStr"/>
+      <c r="CZ41" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
       <c r="DA41" t="inlineStr"/>
       <c r="DB41" t="inlineStr"/>
       <c r="DC41" t="inlineStr"/>
@@ -11893,25 +11962,25 @@
       <c r="DG41" t="inlineStr"/>
       <c r="DH41" t="inlineStr"/>
       <c r="DI41" t="inlineStr"/>
-      <c r="DJ41" t="inlineStr">
-        <is>
-          <t>0, 0.1363</t>
-        </is>
-      </c>
-      <c r="DK41" t="inlineStr">
-        <is>
-          <t>0, 0.781</t>
-        </is>
-      </c>
-      <c r="DL41" t="n">
-        <v>1</v>
-      </c>
+      <c r="DJ41" t="inlineStr"/>
+      <c r="DK41" t="inlineStr"/>
+      <c r="DL41" t="inlineStr"/>
       <c r="DM41" t="inlineStr"/>
       <c r="DN41" t="inlineStr"/>
       <c r="DO41" t="inlineStr"/>
-      <c r="DP41" t="inlineStr"/>
-      <c r="DQ41" t="inlineStr"/>
-      <c r="DR41" t="inlineStr"/>
+      <c r="DP41" t="inlineStr">
+        <is>
+          <t>0, 0.1363</t>
+        </is>
+      </c>
+      <c r="DQ41" t="inlineStr">
+        <is>
+          <t>0, 0.781</t>
+        </is>
+      </c>
+      <c r="DR41" t="n">
+        <v>1</v>
+      </c>
       <c r="DS41" t="inlineStr"/>
       <c r="DT41" t="inlineStr"/>
       <c r="DU41" t="inlineStr"/>
@@ -12013,8 +12082,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S42" t="n">
-        <v>2</v>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -12143,32 +12214,32 @@
       <c r="CD42" t="inlineStr"/>
       <c r="CE42" t="inlineStr"/>
       <c r="CF42" t="inlineStr"/>
-      <c r="CG42" t="inlineStr">
+      <c r="CG42" t="inlineStr"/>
+      <c r="CH42" t="inlineStr"/>
+      <c r="CI42" t="inlineStr"/>
+      <c r="CJ42" t="inlineStr"/>
+      <c r="CK42" t="inlineStr"/>
+      <c r="CL42" t="inlineStr"/>
+      <c r="CM42" t="inlineStr">
         <is>
           <t>0, 1.47</t>
         </is>
       </c>
-      <c r="CH42" t="inlineStr"/>
-      <c r="CI42" t="n">
+      <c r="CN42" t="inlineStr"/>
+      <c r="CO42" t="n">
         <v>1</v>
       </c>
-      <c r="CJ42" t="n">
+      <c r="CP42" t="n">
         <v>1</v>
       </c>
-      <c r="CK42" t="n">
+      <c r="CQ42" t="n">
         <v>0.157</v>
       </c>
-      <c r="CL42" t="inlineStr">
+      <c r="CR42" t="inlineStr">
         <is>
           <t>MEA_large</t>
         </is>
       </c>
-      <c r="CM42" t="inlineStr"/>
-      <c r="CN42" t="inlineStr"/>
-      <c r="CO42" t="inlineStr"/>
-      <c r="CP42" t="inlineStr"/>
-      <c r="CQ42" t="inlineStr"/>
-      <c r="CR42" t="inlineStr"/>
       <c r="CS42" t="inlineStr"/>
       <c r="CT42" t="inlineStr"/>
       <c r="CU42" t="inlineStr"/>
@@ -12296,8 +12367,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S43" t="n">
-        <v>2</v>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -12435,23 +12508,23 @@
       <c r="CK43" t="inlineStr"/>
       <c r="CL43" t="inlineStr"/>
       <c r="CM43" t="inlineStr"/>
-      <c r="CN43" t="inlineStr">
-        <is>
-          <t>0, 0.776</t>
-        </is>
-      </c>
+      <c r="CN43" t="inlineStr"/>
       <c r="CO43" t="inlineStr"/>
       <c r="CP43" t="inlineStr"/>
       <c r="CQ43" t="inlineStr"/>
-      <c r="CR43" t="n">
-        <v>2.44</v>
-      </c>
+      <c r="CR43" t="inlineStr"/>
       <c r="CS43" t="inlineStr"/>
-      <c r="CT43" t="inlineStr"/>
+      <c r="CT43" t="inlineStr">
+        <is>
+          <t>0, 0.776</t>
+        </is>
+      </c>
       <c r="CU43" t="inlineStr"/>
       <c r="CV43" t="inlineStr"/>
       <c r="CW43" t="inlineStr"/>
-      <c r="CX43" t="inlineStr"/>
+      <c r="CX43" t="n">
+        <v>2.44</v>
+      </c>
       <c r="CY43" t="inlineStr"/>
       <c r="CZ43" t="inlineStr"/>
       <c r="DA43" t="inlineStr"/>
@@ -12463,22 +12536,22 @@
       <c r="DG43" t="inlineStr"/>
       <c r="DH43" t="inlineStr"/>
       <c r="DI43" t="inlineStr"/>
-      <c r="DJ43" t="inlineStr">
-        <is>
-          <t>0, 0.859</t>
-        </is>
-      </c>
+      <c r="DJ43" t="inlineStr"/>
       <c r="DK43" t="inlineStr"/>
       <c r="DL43" t="inlineStr"/>
-      <c r="DM43" t="n">
-        <v>1</v>
-      </c>
+      <c r="DM43" t="inlineStr"/>
       <c r="DN43" t="inlineStr"/>
       <c r="DO43" t="inlineStr"/>
-      <c r="DP43" t="inlineStr"/>
+      <c r="DP43" t="inlineStr">
+        <is>
+          <t>0, 0.859</t>
+        </is>
+      </c>
       <c r="DQ43" t="inlineStr"/>
       <c r="DR43" t="inlineStr"/>
-      <c r="DS43" t="inlineStr"/>
+      <c r="DS43" t="n">
+        <v>1</v>
+      </c>
       <c r="DT43" t="inlineStr"/>
       <c r="DU43" t="inlineStr"/>
       <c r="DV43" t="inlineStr"/>
@@ -12579,8 +12652,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S44" t="n">
-        <v>2</v>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>linear_with_intercept</t>
+        </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -12717,29 +12792,29 @@
       <c r="CL44" t="inlineStr"/>
       <c r="CM44" t="inlineStr"/>
       <c r="CN44" t="inlineStr"/>
-      <c r="CO44" t="n">
-        <v>1</v>
-      </c>
+      <c r="CO44" t="inlineStr"/>
       <c r="CP44" t="inlineStr"/>
       <c r="CQ44" t="inlineStr"/>
       <c r="CR44" t="inlineStr"/>
       <c r="CS44" t="inlineStr"/>
       <c r="CT44" t="inlineStr"/>
       <c r="CU44" t="n">
-        <v>4.814</v>
+        <v>1</v>
       </c>
       <c r="CV44" t="inlineStr"/>
-      <c r="CW44" t="inlineStr">
-        <is>
-          <t>0, 0.849</t>
-        </is>
-      </c>
+      <c r="CW44" t="inlineStr"/>
       <c r="CX44" t="inlineStr"/>
       <c r="CY44" t="inlineStr"/>
       <c r="CZ44" t="inlineStr"/>
-      <c r="DA44" t="inlineStr"/>
+      <c r="DA44" t="n">
+        <v>4.814</v>
+      </c>
       <c r="DB44" t="inlineStr"/>
-      <c r="DC44" t="inlineStr"/>
+      <c r="DC44" t="inlineStr">
+        <is>
+          <t>0, 0.849</t>
+        </is>
+      </c>
       <c r="DD44" t="inlineStr"/>
       <c r="DE44" t="inlineStr"/>
       <c r="DF44" t="inlineStr"/>
@@ -12856,8 +12931,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S45" t="n">
-        <v>1</v>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -12991,43 +13068,43 @@
       <c r="CE45" t="inlineStr"/>
       <c r="CF45" t="inlineStr"/>
       <c r="CG45" t="inlineStr"/>
-      <c r="CH45" t="inlineStr">
+      <c r="CH45" t="inlineStr"/>
+      <c r="CI45" t="inlineStr"/>
+      <c r="CJ45" t="inlineStr"/>
+      <c r="CK45" t="inlineStr"/>
+      <c r="CL45" t="inlineStr"/>
+      <c r="CM45" t="inlineStr"/>
+      <c r="CN45" t="inlineStr">
         <is>
           <t>0, 0.154</t>
         </is>
       </c>
-      <c r="CI45" t="inlineStr"/>
-      <c r="CJ45" t="n">
+      <c r="CO45" t="inlineStr"/>
+      <c r="CP45" t="n">
         <v>1</v>
       </c>
-      <c r="CK45" t="n">
+      <c r="CQ45" t="n">
         <v>0.062</v>
       </c>
-      <c r="CL45" t="inlineStr">
+      <c r="CR45" t="inlineStr">
         <is>
           <t>MEA_large</t>
         </is>
-      </c>
-      <c r="CM45" t="inlineStr"/>
-      <c r="CN45" t="inlineStr"/>
-      <c r="CO45" t="inlineStr"/>
-      <c r="CP45" t="inlineStr"/>
-      <c r="CQ45" t="inlineStr"/>
-      <c r="CR45" t="n">
-        <v>0.08699999999999999</v>
       </c>
       <c r="CS45" t="inlineStr"/>
       <c r="CT45" t="inlineStr"/>
       <c r="CU45" t="inlineStr"/>
-      <c r="CV45" t="n">
-        <v>1</v>
-      </c>
+      <c r="CV45" t="inlineStr"/>
       <c r="CW45" t="inlineStr"/>
-      <c r="CX45" t="inlineStr"/>
+      <c r="CX45" t="n">
+        <v>0.08699999999999999</v>
+      </c>
       <c r="CY45" t="inlineStr"/>
       <c r="CZ45" t="inlineStr"/>
       <c r="DA45" t="inlineStr"/>
-      <c r="DB45" t="inlineStr"/>
+      <c r="DB45" t="n">
+        <v>1</v>
+      </c>
       <c r="DC45" t="inlineStr"/>
       <c r="DD45" t="inlineStr"/>
       <c r="DE45" t="inlineStr"/>
@@ -13039,17 +13116,17 @@
       <c r="DK45" t="inlineStr"/>
       <c r="DL45" t="inlineStr"/>
       <c r="DM45" t="inlineStr"/>
-      <c r="DN45" t="inlineStr">
-        <is>
-          <t>0, 0.761</t>
-        </is>
-      </c>
+      <c r="DN45" t="inlineStr"/>
       <c r="DO45" t="inlineStr"/>
       <c r="DP45" t="inlineStr"/>
       <c r="DQ45" t="inlineStr"/>
       <c r="DR45" t="inlineStr"/>
       <c r="DS45" t="inlineStr"/>
-      <c r="DT45" t="inlineStr"/>
+      <c r="DT45" t="inlineStr">
+        <is>
+          <t>0, 0.761</t>
+        </is>
+      </c>
       <c r="DU45" t="inlineStr"/>
       <c r="DV45" t="inlineStr"/>
       <c r="DW45" t="inlineStr"/>
@@ -13139,8 +13216,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S46" t="n">
-        <v>1</v>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -13262,11 +13341,7 @@
       <c r="CE46" t="inlineStr"/>
       <c r="CF46" t="inlineStr"/>
       <c r="CG46" t="inlineStr"/>
-      <c r="CH46" t="inlineStr">
-        <is>
-          <t>0, 1.077</t>
-        </is>
-      </c>
+      <c r="CH46" t="inlineStr"/>
       <c r="CI46" t="inlineStr"/>
       <c r="CJ46" t="inlineStr"/>
       <c r="CK46" t="inlineStr"/>
@@ -13274,7 +13349,7 @@
       <c r="CM46" t="inlineStr"/>
       <c r="CN46" t="inlineStr">
         <is>
-          <t>0, 4.966</t>
+          <t>0, 1.077</t>
         </is>
       </c>
       <c r="CO46" t="inlineStr"/>
@@ -13284,7 +13359,7 @@
       <c r="CS46" t="inlineStr"/>
       <c r="CT46" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>0, 4.966</t>
         </is>
       </c>
       <c r="CU46" t="inlineStr"/>
@@ -13292,54 +13367,58 @@
       <c r="CW46" t="inlineStr"/>
       <c r="CX46" t="inlineStr"/>
       <c r="CY46" t="inlineStr"/>
-      <c r="CZ46" t="inlineStr"/>
+      <c r="CZ46" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
       <c r="DA46" t="inlineStr"/>
       <c r="DB46" t="inlineStr"/>
       <c r="DC46" t="inlineStr"/>
-      <c r="DD46" t="n">
-        <v>1</v>
-      </c>
+      <c r="DD46" t="inlineStr"/>
       <c r="DE46" t="inlineStr"/>
       <c r="DF46" t="inlineStr"/>
       <c r="DG46" t="inlineStr"/>
       <c r="DH46" t="inlineStr"/>
       <c r="DI46" t="inlineStr"/>
-      <c r="DJ46" t="inlineStr"/>
+      <c r="DJ46" t="n">
+        <v>1</v>
+      </c>
       <c r="DK46" t="inlineStr"/>
       <c r="DL46" t="inlineStr"/>
       <c r="DM46" t="inlineStr"/>
       <c r="DN46" t="inlineStr"/>
-      <c r="DO46" t="n">
+      <c r="DO46" t="inlineStr"/>
+      <c r="DP46" t="inlineStr"/>
+      <c r="DQ46" t="inlineStr"/>
+      <c r="DR46" t="inlineStr"/>
+      <c r="DS46" t="inlineStr"/>
+      <c r="DT46" t="inlineStr"/>
+      <c r="DU46" t="n">
         <v>1</v>
       </c>
-      <c r="DP46" t="n">
+      <c r="DV46" t="n">
         <v>1</v>
       </c>
-      <c r="DQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR46" t="inlineStr">
+      <c r="DW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX46" t="inlineStr">
         <is>
           <t>not defined</t>
         </is>
       </c>
-      <c r="DS46" t="inlineStr">
+      <c r="DY46" t="inlineStr">
         <is>
           <t>not defined</t>
         </is>
       </c>
-      <c r="DT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU46" t="n">
+      <c r="DZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA46" t="n">
         <v>0.039</v>
       </c>
-      <c r="DV46" t="inlineStr"/>
-      <c r="DW46" t="inlineStr"/>
-      <c r="DX46" t="inlineStr"/>
-      <c r="DY46" t="inlineStr"/>
-      <c r="DZ46" t="inlineStr"/>
-      <c r="EA46" t="inlineStr"/>
       <c r="EB46" t="inlineStr"/>
       <c r="EC46" t="inlineStr"/>
       <c r="ED46" t="inlineStr"/>
@@ -13591,37 +13670,37 @@
       <c r="DS47" t="inlineStr"/>
       <c r="DT47" t="inlineStr"/>
       <c r="DU47" t="inlineStr"/>
-      <c r="DV47" t="inlineStr">
+      <c r="DV47" t="inlineStr"/>
+      <c r="DW47" t="inlineStr"/>
+      <c r="DX47" t="inlineStr"/>
+      <c r="DY47" t="inlineStr"/>
+      <c r="DZ47" t="inlineStr"/>
+      <c r="EA47" t="inlineStr"/>
+      <c r="EB47" t="inlineStr">
         <is>
           <t>as hp/mp steam</t>
         </is>
       </c>
-      <c r="DW47" t="inlineStr">
+      <c r="EC47" t="inlineStr">
         <is>
           <t>OHB</t>
         </is>
       </c>
-      <c r="DX47" t="n">
+      <c r="ED47" t="n">
         <v>0.98</v>
       </c>
-      <c r="DY47" t="n">
+      <c r="EE47" t="n">
         <v>24</v>
       </c>
-      <c r="DZ47" t="n">
+      <c r="EF47" t="n">
         <v>24</v>
       </c>
-      <c r="EA47" t="n">
+      <c r="EG47" t="n">
         <v>24</v>
       </c>
-      <c r="EB47" t="n">
+      <c r="EH47" t="n">
         <v>0.05</v>
       </c>
-      <c r="EC47" t="inlineStr"/>
-      <c r="ED47" t="inlineStr"/>
-      <c r="EE47" t="inlineStr"/>
-      <c r="EF47" t="inlineStr"/>
-      <c r="EG47" t="inlineStr"/>
-      <c r="EH47" t="inlineStr"/>
       <c r="EI47" t="inlineStr"/>
       <c r="EJ47" t="inlineStr"/>
       <c r="EK47" t="inlineStr"/>
@@ -13847,43 +13926,43 @@
       <c r="DZ48" t="inlineStr"/>
       <c r="EA48" t="inlineStr"/>
       <c r="EB48" t="inlineStr"/>
-      <c r="EC48" t="n">
+      <c r="EC48" t="inlineStr"/>
+      <c r="ED48" t="inlineStr"/>
+      <c r="EE48" t="inlineStr"/>
+      <c r="EF48" t="inlineStr"/>
+      <c r="EG48" t="inlineStr"/>
+      <c r="EH48" t="inlineStr"/>
+      <c r="EI48" t="n">
         <v>10</v>
       </c>
-      <c r="ED48" t="n">
+      <c r="EJ48" t="n">
         <v>20.468</v>
       </c>
-      <c r="EE48" t="n">
+      <c r="EK48" t="n">
         <v>33.289</v>
       </c>
-      <c r="EF48" t="n">
+      <c r="EL48" t="n">
         <v>0.3916</v>
       </c>
-      <c r="EG48" t="n">
+      <c r="EM48" t="n">
         <v>-3.011</v>
       </c>
-      <c r="EH48" t="inlineStr">
+      <c r="EN48" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI48" t="inlineStr">
+      <c r="EO48" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ48" t="n">
+      <c r="EP48" t="n">
         <v>15</v>
       </c>
-      <c r="EK48" t="n">
+      <c r="EQ48" t="n">
         <v>0.955</v>
       </c>
-      <c r="EL48" t="inlineStr"/>
-      <c r="EM48" t="inlineStr"/>
-      <c r="EN48" t="inlineStr"/>
-      <c r="EO48" t="inlineStr"/>
-      <c r="EP48" t="inlineStr"/>
-      <c r="EQ48" t="inlineStr"/>
       <c r="ER48" t="inlineStr"/>
       <c r="ES48" t="inlineStr"/>
       <c r="ET48" t="inlineStr"/>
@@ -14100,43 +14179,43 @@
       <c r="DZ49" t="inlineStr"/>
       <c r="EA49" t="inlineStr"/>
       <c r="EB49" t="inlineStr"/>
-      <c r="EC49" t="n">
+      <c r="EC49" t="inlineStr"/>
+      <c r="ED49" t="inlineStr"/>
+      <c r="EE49" t="inlineStr"/>
+      <c r="EF49" t="inlineStr"/>
+      <c r="EG49" t="inlineStr"/>
+      <c r="EH49" t="inlineStr"/>
+      <c r="EI49" t="n">
         <v>100</v>
       </c>
-      <c r="ED49" t="n">
+      <c r="EJ49" t="n">
         <v>129.04</v>
       </c>
-      <c r="EE49" t="n">
+      <c r="EK49" t="n">
         <v>226.884</v>
       </c>
-      <c r="EF49" t="n">
+      <c r="EL49" t="n">
         <v>0.4633</v>
       </c>
-      <c r="EG49" t="n">
+      <c r="EM49" t="n">
         <v>-15.458</v>
       </c>
-      <c r="EH49" t="inlineStr">
+      <c r="EN49" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI49" t="inlineStr">
+      <c r="EO49" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ49" t="n">
+      <c r="EP49" t="n">
         <v>15</v>
       </c>
-      <c r="EK49" t="n">
+      <c r="EQ49" t="n">
         <v>0.955</v>
       </c>
-      <c r="EL49" t="inlineStr"/>
-      <c r="EM49" t="inlineStr"/>
-      <c r="EN49" t="inlineStr"/>
-      <c r="EO49" t="inlineStr"/>
-      <c r="EP49" t="inlineStr"/>
-      <c r="EQ49" t="inlineStr"/>
       <c r="ER49" t="inlineStr"/>
       <c r="ES49" t="inlineStr"/>
       <c r="ET49" t="inlineStr"/>
@@ -14353,43 +14432,43 @@
       <c r="DZ50" t="inlineStr"/>
       <c r="EA50" t="inlineStr"/>
       <c r="EB50" t="inlineStr"/>
-      <c r="EC50" t="n">
+      <c r="EC50" t="inlineStr"/>
+      <c r="ED50" t="inlineStr"/>
+      <c r="EE50" t="inlineStr"/>
+      <c r="EF50" t="inlineStr"/>
+      <c r="EG50" t="inlineStr"/>
+      <c r="EH50" t="inlineStr"/>
+      <c r="EI50" t="n">
         <v>250</v>
       </c>
-      <c r="ED50" t="n">
+      <c r="EJ50" t="n">
         <v>396.035</v>
       </c>
-      <c r="EE50" t="n">
+      <c r="EK50" t="n">
         <v>625.735</v>
       </c>
-      <c r="EF50" t="n">
+      <c r="EL50" t="n">
         <v>0.5486</v>
       </c>
-      <c r="EG50" t="n">
+      <c r="EM50" t="n">
         <v>-93.08499999999999</v>
       </c>
-      <c r="EH50" t="inlineStr">
+      <c r="EN50" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI50" t="inlineStr">
+      <c r="EO50" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ50" t="n">
+      <c r="EP50" t="n">
         <v>15</v>
       </c>
-      <c r="EK50" t="n">
+      <c r="EQ50" t="n">
         <v>0.955</v>
       </c>
-      <c r="EL50" t="inlineStr"/>
-      <c r="EM50" t="inlineStr"/>
-      <c r="EN50" t="inlineStr"/>
-      <c r="EO50" t="inlineStr"/>
-      <c r="EP50" t="inlineStr"/>
-      <c r="EQ50" t="inlineStr"/>
       <c r="ER50" t="inlineStr"/>
       <c r="ES50" t="inlineStr"/>
       <c r="ET50" t="inlineStr"/>
@@ -14606,43 +14685,43 @@
       <c r="DZ51" t="inlineStr"/>
       <c r="EA51" t="inlineStr"/>
       <c r="EB51" t="inlineStr"/>
-      <c r="EC51" t="n">
+      <c r="EC51" t="inlineStr"/>
+      <c r="ED51" t="inlineStr"/>
+      <c r="EE51" t="inlineStr"/>
+      <c r="EF51" t="inlineStr"/>
+      <c r="EG51" t="inlineStr"/>
+      <c r="EH51" t="inlineStr"/>
+      <c r="EI51" t="n">
         <v>400</v>
       </c>
-      <c r="ED51" t="n">
+      <c r="EJ51" t="n">
         <v>720.256</v>
       </c>
-      <c r="EE51" t="n">
+      <c r="EK51" t="n">
         <v>1138.004</v>
       </c>
-      <c r="EF51" t="n">
+      <c r="EL51" t="n">
         <v>0.5486</v>
       </c>
-      <c r="EG51" t="n">
+      <c r="EM51" t="n">
         <v>-169.291</v>
       </c>
-      <c r="EH51" t="inlineStr">
+      <c r="EN51" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI51" t="inlineStr">
+      <c r="EO51" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ51" t="n">
+      <c r="EP51" t="n">
         <v>15</v>
       </c>
-      <c r="EK51" t="n">
+      <c r="EQ51" t="n">
         <v>0.955</v>
       </c>
-      <c r="EL51" t="inlineStr"/>
-      <c r="EM51" t="inlineStr"/>
-      <c r="EN51" t="inlineStr"/>
-      <c r="EO51" t="inlineStr"/>
-      <c r="EP51" t="inlineStr"/>
-      <c r="EQ51" t="inlineStr"/>
       <c r="ER51" t="inlineStr"/>
       <c r="ES51" t="inlineStr"/>
       <c r="ET51" t="inlineStr"/>
@@ -14859,46 +14938,46 @@
       <c r="DZ52" t="inlineStr"/>
       <c r="EA52" t="inlineStr"/>
       <c r="EB52" t="inlineStr"/>
-      <c r="EC52" t="n">
+      <c r="EC52" t="inlineStr"/>
+      <c r="ED52" t="inlineStr"/>
+      <c r="EE52" t="inlineStr"/>
+      <c r="EF52" t="inlineStr"/>
+      <c r="EG52" t="inlineStr"/>
+      <c r="EH52" t="inlineStr"/>
+      <c r="EI52" t="n">
         <v>10</v>
       </c>
-      <c r="ED52" t="n">
+      <c r="EJ52" t="n">
         <v>19.907</v>
       </c>
-      <c r="EE52" t="n">
+      <c r="EK52" t="n">
         <v>32.376</v>
       </c>
-      <c r="EF52" t="n">
+      <c r="EL52" t="n">
         <v>0.4026</v>
       </c>
-      <c r="EG52" t="n">
+      <c r="EM52" t="n">
         <v>-3.0104</v>
       </c>
-      <c r="EH52" t="inlineStr">
+      <c r="EN52" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI52" t="inlineStr">
+      <c r="EO52" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ52" t="n">
+      <c r="EP52" t="n">
         <v>15</v>
       </c>
-      <c r="EK52" t="n">
+      <c r="EQ52" t="n">
         <v>0.871207034372502</v>
       </c>
-      <c r="EL52" t="n">
+      <c r="ER52" t="n">
         <v>0.05</v>
       </c>
-      <c r="EM52" t="inlineStr"/>
-      <c r="EN52" t="inlineStr"/>
-      <c r="EO52" t="inlineStr"/>
-      <c r="EP52" t="inlineStr"/>
-      <c r="EQ52" t="inlineStr"/>
-      <c r="ER52" t="inlineStr"/>
       <c r="ES52" t="inlineStr"/>
       <c r="ET52" t="inlineStr"/>
       <c r="EU52" t="inlineStr"/>
@@ -15114,46 +15193,46 @@
       <c r="DZ53" t="inlineStr"/>
       <c r="EA53" t="inlineStr"/>
       <c r="EB53" t="inlineStr"/>
-      <c r="EC53" t="n">
+      <c r="EC53" t="inlineStr"/>
+      <c r="ED53" t="inlineStr"/>
+      <c r="EE53" t="inlineStr"/>
+      <c r="EF53" t="inlineStr"/>
+      <c r="EG53" t="inlineStr"/>
+      <c r="EH53" t="inlineStr"/>
+      <c r="EI53" t="n">
         <v>100</v>
       </c>
-      <c r="ED53" t="n">
+      <c r="EJ53" t="n">
         <v>123.951</v>
       </c>
-      <c r="EE53" t="n">
+      <c r="EK53" t="n">
         <v>220.66</v>
       </c>
-      <c r="EF53" t="n">
+      <c r="EL53" t="n">
         <v>0.5218</v>
       </c>
-      <c r="EG53" t="n">
+      <c r="EM53" t="n">
         <v>-14.309</v>
       </c>
-      <c r="EH53" t="inlineStr">
+      <c r="EN53" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI53" t="inlineStr">
+      <c r="EO53" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ53" t="n">
+      <c r="EP53" t="n">
         <v>15</v>
       </c>
-      <c r="EK53" t="n">
+      <c r="EQ53" t="n">
         <v>0.871207034372502</v>
       </c>
-      <c r="EL53" t="n">
+      <c r="ER53" t="n">
         <v>0.05</v>
       </c>
-      <c r="EM53" t="inlineStr"/>
-      <c r="EN53" t="inlineStr"/>
-      <c r="EO53" t="inlineStr"/>
-      <c r="EP53" t="inlineStr"/>
-      <c r="EQ53" t="inlineStr"/>
-      <c r="ER53" t="inlineStr"/>
       <c r="ES53" t="inlineStr"/>
       <c r="ET53" t="inlineStr"/>
       <c r="EU53" t="inlineStr"/>
@@ -15369,46 +15448,46 @@
       <c r="DZ54" t="inlineStr"/>
       <c r="EA54" t="inlineStr"/>
       <c r="EB54" t="inlineStr"/>
-      <c r="EC54" t="n">
+      <c r="EC54" t="inlineStr"/>
+      <c r="ED54" t="inlineStr"/>
+      <c r="EE54" t="inlineStr"/>
+      <c r="EF54" t="inlineStr"/>
+      <c r="EG54" t="inlineStr"/>
+      <c r="EH54" t="inlineStr"/>
+      <c r="EI54" t="n">
         <v>250</v>
       </c>
-      <c r="ED54" t="n">
+      <c r="EJ54" t="n">
         <v>351.617</v>
       </c>
-      <c r="EE54" t="n">
+      <c r="EK54" t="n">
         <v>555.556</v>
       </c>
-      <c r="EF54" t="n">
+      <c r="EL54" t="n">
         <v>0.5488</v>
       </c>
-      <c r="EG54" t="n">
+      <c r="EM54" t="n">
         <v>-104.969</v>
       </c>
-      <c r="EH54" t="inlineStr">
+      <c r="EN54" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI54" t="inlineStr">
+      <c r="EO54" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ54" t="n">
+      <c r="EP54" t="n">
         <v>15</v>
       </c>
-      <c r="EK54" t="n">
+      <c r="EQ54" t="n">
         <v>0.871207034372502</v>
       </c>
-      <c r="EL54" t="n">
+      <c r="ER54" t="n">
         <v>0.05</v>
       </c>
-      <c r="EM54" t="inlineStr"/>
-      <c r="EN54" t="inlineStr"/>
-      <c r="EO54" t="inlineStr"/>
-      <c r="EP54" t="inlineStr"/>
-      <c r="EQ54" t="inlineStr"/>
-      <c r="ER54" t="inlineStr"/>
       <c r="ES54" t="inlineStr"/>
       <c r="ET54" t="inlineStr"/>
       <c r="EU54" t="inlineStr"/>
@@ -15624,46 +15703,46 @@
       <c r="DZ55" t="inlineStr"/>
       <c r="EA55" t="inlineStr"/>
       <c r="EB55" t="inlineStr"/>
-      <c r="EC55" t="n">
+      <c r="EC55" t="inlineStr"/>
+      <c r="ED55" t="inlineStr"/>
+      <c r="EE55" t="inlineStr"/>
+      <c r="EF55" t="inlineStr"/>
+      <c r="EG55" t="inlineStr"/>
+      <c r="EH55" t="inlineStr"/>
+      <c r="EI55" t="n">
         <v>400</v>
       </c>
-      <c r="ED55" t="n">
+      <c r="EJ55" t="n">
         <v>685.696</v>
       </c>
-      <c r="EE55" t="n">
+      <c r="EK55" t="n">
         <v>1083.4</v>
       </c>
-      <c r="EF55" t="n">
+      <c r="EL55" t="n">
         <v>0.5763</v>
       </c>
-      <c r="EG55" t="n">
+      <c r="EM55" t="n">
         <v>-169.291</v>
       </c>
-      <c r="EH55" t="inlineStr">
+      <c r="EN55" t="inlineStr">
         <is>
           <t>0.0064, -0.0971</t>
         </is>
       </c>
-      <c r="EI55" t="inlineStr">
+      <c r="EO55" t="inlineStr">
         <is>
           <t>1.002, 1.0538</t>
         </is>
       </c>
-      <c r="EJ55" t="n">
+      <c r="EP55" t="n">
         <v>15</v>
       </c>
-      <c r="EK55" t="n">
+      <c r="EQ55" t="n">
         <v>0.871207034372502</v>
       </c>
-      <c r="EL55" t="n">
+      <c r="ER55" t="n">
         <v>0.05</v>
       </c>
-      <c r="EM55" t="inlineStr"/>
-      <c r="EN55" t="inlineStr"/>
-      <c r="EO55" t="inlineStr"/>
-      <c r="EP55" t="inlineStr"/>
-      <c r="EQ55" t="inlineStr"/>
-      <c r="ER55" t="inlineStr"/>
       <c r="ES55" t="inlineStr"/>
       <c r="ET55" t="inlineStr"/>
       <c r="EU55" t="inlineStr"/>
@@ -15741,8 +15820,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S56" t="n">
-        <v>1</v>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -15925,15 +16006,15 @@
       <c r="EJ56" t="inlineStr"/>
       <c r="EK56" t="inlineStr"/>
       <c r="EL56" t="inlineStr"/>
-      <c r="EM56" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="EM56" t="inlineStr"/>
       <c r="EN56" t="inlineStr"/>
       <c r="EO56" t="inlineStr"/>
       <c r="EP56" t="inlineStr"/>
       <c r="EQ56" t="inlineStr"/>
       <c r="ER56" t="inlineStr"/>
-      <c r="ES56" t="inlineStr"/>
+      <c r="ES56" t="n">
+        <v>0.05</v>
+      </c>
       <c r="ET56" t="inlineStr"/>
       <c r="EU56" t="inlineStr"/>
       <c r="EV56" t="inlineStr"/>
@@ -16010,8 +16091,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S57" t="n">
-        <v>1</v>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -16133,23 +16216,23 @@
       <c r="CG57" t="inlineStr"/>
       <c r="CH57" t="inlineStr"/>
       <c r="CI57" t="inlineStr"/>
-      <c r="CJ57" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK57" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="CL57" t="inlineStr">
-        <is>
-          <t>MEA_medium</t>
-        </is>
-      </c>
+      <c r="CJ57" t="inlineStr"/>
+      <c r="CK57" t="inlineStr"/>
+      <c r="CL57" t="inlineStr"/>
       <c r="CM57" t="inlineStr"/>
       <c r="CN57" t="inlineStr"/>
       <c r="CO57" t="inlineStr"/>
-      <c r="CP57" t="inlineStr"/>
-      <c r="CQ57" t="inlineStr"/>
-      <c r="CR57" t="inlineStr"/>
+      <c r="CP57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>MEA_medium</t>
+        </is>
+      </c>
       <c r="CS57" t="inlineStr"/>
       <c r="CT57" t="inlineStr"/>
       <c r="CU57" t="inlineStr"/>
@@ -16196,18 +16279,18 @@
       <c r="EJ57" t="inlineStr"/>
       <c r="EK57" t="inlineStr"/>
       <c r="EL57" t="inlineStr"/>
-      <c r="EM57" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="EN57" t="n">
-        <v>-1</v>
-      </c>
+      <c r="EM57" t="inlineStr"/>
+      <c r="EN57" t="inlineStr"/>
       <c r="EO57" t="inlineStr"/>
       <c r="EP57" t="inlineStr"/>
       <c r="EQ57" t="inlineStr"/>
       <c r="ER57" t="inlineStr"/>
-      <c r="ES57" t="inlineStr"/>
-      <c r="ET57" t="inlineStr"/>
+      <c r="ES57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="ET57" t="n">
+        <v>-1</v>
+      </c>
       <c r="EU57" t="inlineStr"/>
       <c r="EV57" t="inlineStr"/>
       <c r="EW57" t="inlineStr"/>
@@ -16281,8 +16364,10 @@
           <t>contains fitting data on unit of input, technology types and input/output carriers</t>
         </is>
       </c>
-      <c r="S58" t="n">
-        <v>1</v>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>linear_through_origin</t>
+        </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -16672,15 +16757,15 @@
       <c r="EL59" t="inlineStr"/>
       <c r="EM59" t="inlineStr"/>
       <c r="EN59" t="inlineStr"/>
-      <c r="EO59" t="n">
-        <v>1</v>
-      </c>
+      <c r="EO59" t="inlineStr"/>
       <c r="EP59" t="inlineStr"/>
       <c r="EQ59" t="inlineStr"/>
       <c r="ER59" t="inlineStr"/>
       <c r="ES59" t="inlineStr"/>
       <c r="ET59" t="inlineStr"/>
-      <c r="EU59" t="inlineStr"/>
+      <c r="EU59" t="n">
+        <v>1</v>
+      </c>
       <c r="EV59" t="inlineStr"/>
       <c r="EW59" t="inlineStr"/>
       <c r="EX59" t="inlineStr"/>
@@ -16893,15 +16978,15 @@
       <c r="EL60" t="inlineStr"/>
       <c r="EM60" t="inlineStr"/>
       <c r="EN60" t="inlineStr"/>
-      <c r="EO60" t="n">
-        <v>1</v>
-      </c>
+      <c r="EO60" t="inlineStr"/>
       <c r="EP60" t="inlineStr"/>
       <c r="EQ60" t="inlineStr"/>
       <c r="ER60" t="inlineStr"/>
       <c r="ES60" t="inlineStr"/>
       <c r="ET60" t="inlineStr"/>
-      <c r="EU60" t="inlineStr"/>
+      <c r="EU60" t="n">
+        <v>1</v>
+      </c>
       <c r="EV60" t="inlineStr"/>
       <c r="EW60" t="inlineStr"/>
       <c r="EX60" t="inlineStr"/>
@@ -17049,15 +17134,15 @@
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="inlineStr"/>
       <c r="CA61" t="inlineStr"/>
-      <c r="CB61" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB61" t="inlineStr"/>
       <c r="CC61" t="inlineStr"/>
       <c r="CD61" t="inlineStr"/>
       <c r="CE61" t="inlineStr"/>
       <c r="CF61" t="inlineStr"/>
       <c r="CG61" t="inlineStr"/>
-      <c r="CH61" t="inlineStr"/>
+      <c r="CH61" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI61" t="inlineStr"/>
       <c r="CJ61" t="inlineStr"/>
       <c r="CK61" t="inlineStr"/>
@@ -17116,18 +17201,18 @@
       <c r="EL61" t="inlineStr"/>
       <c r="EM61" t="inlineStr"/>
       <c r="EN61" t="inlineStr"/>
-      <c r="EO61" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP61" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO61" t="inlineStr"/>
+      <c r="EP61" t="inlineStr"/>
       <c r="EQ61" t="inlineStr"/>
       <c r="ER61" t="inlineStr"/>
       <c r="ES61" t="inlineStr"/>
       <c r="ET61" t="inlineStr"/>
-      <c r="EU61" t="inlineStr"/>
-      <c r="EV61" t="inlineStr"/>
+      <c r="EU61" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV61" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW61" t="inlineStr"/>
       <c r="EX61" t="inlineStr"/>
       <c r="EY61" t="inlineStr"/>
@@ -17274,15 +17359,15 @@
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="inlineStr"/>
       <c r="CA62" t="inlineStr"/>
-      <c r="CB62" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB62" t="inlineStr"/>
       <c r="CC62" t="inlineStr"/>
       <c r="CD62" t="inlineStr"/>
       <c r="CE62" t="inlineStr"/>
       <c r="CF62" t="inlineStr"/>
       <c r="CG62" t="inlineStr"/>
-      <c r="CH62" t="inlineStr"/>
+      <c r="CH62" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI62" t="inlineStr"/>
       <c r="CJ62" t="inlineStr"/>
       <c r="CK62" t="inlineStr"/>
@@ -17341,18 +17426,18 @@
       <c r="EL62" t="inlineStr"/>
       <c r="EM62" t="inlineStr"/>
       <c r="EN62" t="inlineStr"/>
-      <c r="EO62" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP62" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO62" t="inlineStr"/>
+      <c r="EP62" t="inlineStr"/>
       <c r="EQ62" t="inlineStr"/>
       <c r="ER62" t="inlineStr"/>
       <c r="ES62" t="inlineStr"/>
       <c r="ET62" t="inlineStr"/>
-      <c r="EU62" t="inlineStr"/>
-      <c r="EV62" t="inlineStr"/>
+      <c r="EU62" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV62" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW62" t="inlineStr"/>
       <c r="EX62" t="inlineStr"/>
       <c r="EY62" t="inlineStr"/>
@@ -17499,15 +17584,15 @@
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="inlineStr"/>
       <c r="CA63" t="inlineStr"/>
-      <c r="CB63" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB63" t="inlineStr"/>
       <c r="CC63" t="inlineStr"/>
       <c r="CD63" t="inlineStr"/>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="inlineStr"/>
       <c r="CG63" t="inlineStr"/>
-      <c r="CH63" t="inlineStr"/>
+      <c r="CH63" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI63" t="inlineStr"/>
       <c r="CJ63" t="inlineStr"/>
       <c r="CK63" t="inlineStr"/>
@@ -17566,18 +17651,18 @@
       <c r="EL63" t="inlineStr"/>
       <c r="EM63" t="inlineStr"/>
       <c r="EN63" t="inlineStr"/>
-      <c r="EO63" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP63" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO63" t="inlineStr"/>
+      <c r="EP63" t="inlineStr"/>
       <c r="EQ63" t="inlineStr"/>
       <c r="ER63" t="inlineStr"/>
       <c r="ES63" t="inlineStr"/>
       <c r="ET63" t="inlineStr"/>
-      <c r="EU63" t="inlineStr"/>
-      <c r="EV63" t="inlineStr"/>
+      <c r="EU63" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV63" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW63" t="inlineStr"/>
       <c r="EX63" t="inlineStr"/>
       <c r="EY63" t="inlineStr"/>
@@ -17724,15 +17809,15 @@
       <c r="BY64" t="inlineStr"/>
       <c r="BZ64" t="inlineStr"/>
       <c r="CA64" t="inlineStr"/>
-      <c r="CB64" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB64" t="inlineStr"/>
       <c r="CC64" t="inlineStr"/>
       <c r="CD64" t="inlineStr"/>
       <c r="CE64" t="inlineStr"/>
       <c r="CF64" t="inlineStr"/>
       <c r="CG64" t="inlineStr"/>
-      <c r="CH64" t="inlineStr"/>
+      <c r="CH64" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI64" t="inlineStr"/>
       <c r="CJ64" t="inlineStr"/>
       <c r="CK64" t="inlineStr"/>
@@ -17791,18 +17876,18 @@
       <c r="EL64" t="inlineStr"/>
       <c r="EM64" t="inlineStr"/>
       <c r="EN64" t="inlineStr"/>
-      <c r="EO64" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP64" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO64" t="inlineStr"/>
+      <c r="EP64" t="inlineStr"/>
       <c r="EQ64" t="inlineStr"/>
       <c r="ER64" t="inlineStr"/>
       <c r="ES64" t="inlineStr"/>
       <c r="ET64" t="inlineStr"/>
-      <c r="EU64" t="inlineStr"/>
-      <c r="EV64" t="inlineStr"/>
+      <c r="EU64" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV64" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW64" t="inlineStr"/>
       <c r="EX64" t="inlineStr"/>
       <c r="EY64" t="inlineStr"/>
@@ -17949,15 +18034,15 @@
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="inlineStr"/>
       <c r="CA65" t="inlineStr"/>
-      <c r="CB65" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB65" t="inlineStr"/>
       <c r="CC65" t="inlineStr"/>
       <c r="CD65" t="inlineStr"/>
       <c r="CE65" t="inlineStr"/>
       <c r="CF65" t="inlineStr"/>
       <c r="CG65" t="inlineStr"/>
-      <c r="CH65" t="inlineStr"/>
+      <c r="CH65" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI65" t="inlineStr"/>
       <c r="CJ65" t="inlineStr"/>
       <c r="CK65" t="inlineStr"/>
@@ -18016,18 +18101,18 @@
       <c r="EL65" t="inlineStr"/>
       <c r="EM65" t="inlineStr"/>
       <c r="EN65" t="inlineStr"/>
-      <c r="EO65" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP65" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO65" t="inlineStr"/>
+      <c r="EP65" t="inlineStr"/>
       <c r="EQ65" t="inlineStr"/>
       <c r="ER65" t="inlineStr"/>
       <c r="ES65" t="inlineStr"/>
       <c r="ET65" t="inlineStr"/>
-      <c r="EU65" t="inlineStr"/>
-      <c r="EV65" t="inlineStr"/>
+      <c r="EU65" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV65" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW65" t="inlineStr"/>
       <c r="EX65" t="inlineStr"/>
       <c r="EY65" t="inlineStr"/>
@@ -18174,15 +18259,15 @@
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="inlineStr"/>
       <c r="CA66" t="inlineStr"/>
-      <c r="CB66" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="CB66" t="inlineStr"/>
       <c r="CC66" t="inlineStr"/>
       <c r="CD66" t="inlineStr"/>
       <c r="CE66" t="inlineStr"/>
       <c r="CF66" t="inlineStr"/>
       <c r="CG66" t="inlineStr"/>
-      <c r="CH66" t="inlineStr"/>
+      <c r="CH66" t="n">
+        <v>0.001</v>
+      </c>
       <c r="CI66" t="inlineStr"/>
       <c r="CJ66" t="inlineStr"/>
       <c r="CK66" t="inlineStr"/>
@@ -18241,18 +18326,18 @@
       <c r="EL66" t="inlineStr"/>
       <c r="EM66" t="inlineStr"/>
       <c r="EN66" t="inlineStr"/>
-      <c r="EO66" t="n">
-        <v>2</v>
-      </c>
-      <c r="EP66" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EO66" t="inlineStr"/>
+      <c r="EP66" t="inlineStr"/>
       <c r="EQ66" t="inlineStr"/>
       <c r="ER66" t="inlineStr"/>
       <c r="ES66" t="inlineStr"/>
       <c r="ET66" t="inlineStr"/>
-      <c r="EU66" t="inlineStr"/>
-      <c r="EV66" t="inlineStr"/>
+      <c r="EU66" t="n">
+        <v>2</v>
+      </c>
+      <c r="EV66" t="n">
+        <v>0.1</v>
+      </c>
       <c r="EW66" t="inlineStr"/>
       <c r="EX66" t="inlineStr"/>
       <c r="EY66" t="inlineStr"/>
@@ -18406,7 +18491,11 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="inlineStr"/>
-      <c r="CA67" t="inlineStr"/>
+      <c r="CA67" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
       <c r="CB67" t="inlineStr"/>
       <c r="CC67" t="inlineStr"/>
       <c r="CD67" t="inlineStr"/>
@@ -18474,28 +18563,24 @@
       <c r="EN67" t="inlineStr"/>
       <c r="EO67" t="inlineStr"/>
       <c r="EP67" t="inlineStr"/>
-      <c r="EQ67" t="n">
+      <c r="EQ67" t="inlineStr"/>
+      <c r="ER67" t="inlineStr"/>
+      <c r="ES67" t="inlineStr"/>
+      <c r="ET67" t="inlineStr"/>
+      <c r="EU67" t="inlineStr"/>
+      <c r="EV67" t="inlineStr"/>
+      <c r="EW67" t="n">
         <v>0.034</v>
       </c>
-      <c r="ER67" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
-      <c r="ES67" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET67" t="n">
+      <c r="EX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY67" t="n">
         <v>114</v>
       </c>
-      <c r="EU67" t="n">
-        <v>0</v>
-      </c>
-      <c r="EV67" t="inlineStr"/>
-      <c r="EW67" t="inlineStr"/>
-      <c r="EX67" t="inlineStr"/>
-      <c r="EY67" t="inlineStr"/>
-      <c r="EZ67" t="inlineStr"/>
+      <c r="EZ67" t="n">
+        <v>0</v>
+      </c>
       <c r="FA67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -18667,12 +18752,28 @@
       <c r="BZ68" t="n">
         <v>0</v>
       </c>
-      <c r="CA68" t="inlineStr"/>
-      <c r="CB68" t="inlineStr"/>
-      <c r="CC68" t="inlineStr"/>
-      <c r="CD68" t="inlineStr"/>
-      <c r="CE68" t="inlineStr"/>
-      <c r="CF68" t="inlineStr"/>
+      <c r="CA68" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB68" t="inlineStr">
+        <is>
+          <t>fixedcapacity</t>
+        </is>
+      </c>
+      <c r="CC68" t="n">
+        <v>250</v>
+      </c>
+      <c r="CD68" t="n">
+        <v>250</v>
+      </c>
+      <c r="CE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF68" t="n">
+        <v>0</v>
+      </c>
       <c r="CG68" t="inlineStr"/>
       <c r="CH68" t="inlineStr"/>
       <c r="CI68" t="inlineStr"/>
@@ -18735,34 +18836,18 @@
       <c r="EN68" t="inlineStr"/>
       <c r="EO68" t="inlineStr"/>
       <c r="EP68" t="inlineStr"/>
-      <c r="EQ68" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="ER68" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="EQ68" t="inlineStr"/>
+      <c r="ER68" t="inlineStr"/>
       <c r="ES68" t="inlineStr"/>
       <c r="ET68" t="inlineStr"/>
       <c r="EU68" t="inlineStr"/>
-      <c r="EV68" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW68" t="inlineStr">
-        <is>
-          <t>fixedcapacity</t>
-        </is>
-      </c>
-      <c r="EX68" t="n">
-        <v>250</v>
-      </c>
-      <c r="EY68" t="n">
-        <v>250</v>
-      </c>
-      <c r="EZ68" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV68" t="inlineStr"/>
+      <c r="EW68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="EX68" t="inlineStr"/>
+      <c r="EY68" t="inlineStr"/>
+      <c r="EZ68" t="inlineStr"/>
       <c r="FA68" t="n">
         <v>0</v>
       </c>
@@ -18936,24 +19021,40 @@
       <c r="BZ69" t="n">
         <v>0</v>
       </c>
-      <c r="CA69" t="inlineStr"/>
-      <c r="CB69" t="n">
+      <c r="CA69" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB69" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC69" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG69" t="inlineStr"/>
+      <c r="CH69" t="n">
         <v>0.001</v>
       </c>
-      <c r="CC69" t="inlineStr"/>
-      <c r="CD69" t="inlineStr"/>
-      <c r="CE69" t="n">
-        <v>100</v>
-      </c>
-      <c r="CF69" t="n">
-        <v>100</v>
-      </c>
-      <c r="CG69" t="inlineStr"/>
-      <c r="CH69" t="inlineStr"/>
       <c r="CI69" t="inlineStr"/>
       <c r="CJ69" t="inlineStr"/>
-      <c r="CK69" t="inlineStr"/>
-      <c r="CL69" t="inlineStr"/>
+      <c r="CK69" t="n">
+        <v>100</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>100</v>
+      </c>
       <c r="CM69" t="inlineStr"/>
       <c r="CN69" t="inlineStr"/>
       <c r="CO69" t="inlineStr"/>
@@ -19009,36 +19110,20 @@
       <c r="EM69" t="inlineStr"/>
       <c r="EN69" t="inlineStr"/>
       <c r="EO69" t="inlineStr"/>
-      <c r="EP69" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="EP69" t="inlineStr"/>
       <c r="EQ69" t="inlineStr"/>
-      <c r="ER69" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER69" t="inlineStr"/>
       <c r="ES69" t="inlineStr"/>
       <c r="ET69" t="inlineStr"/>
       <c r="EU69" t="inlineStr"/>
-      <c r="EV69" t="inlineStr"/>
-      <c r="EW69" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX69" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="EY69" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="EZ69" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA69" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="EW69" t="inlineStr"/>
+      <c r="EX69" t="inlineStr"/>
+      <c r="EY69" t="inlineStr"/>
+      <c r="EZ69" t="inlineStr"/>
+      <c r="FA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -19209,12 +19294,28 @@
       <c r="BZ70" t="n">
         <v>0</v>
       </c>
-      <c r="CA70" t="inlineStr"/>
-      <c r="CB70" t="inlineStr"/>
-      <c r="CC70" t="inlineStr"/>
-      <c r="CD70" t="inlineStr"/>
-      <c r="CE70" t="inlineStr"/>
-      <c r="CF70" t="inlineStr"/>
+      <c r="CA70" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB70" t="inlineStr">
+        <is>
+          <t>fixedcapacity</t>
+        </is>
+      </c>
+      <c r="CC70" t="n">
+        <v>650</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>650</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0</v>
+      </c>
       <c r="CG70" t="inlineStr"/>
       <c r="CH70" t="inlineStr"/>
       <c r="CI70" t="inlineStr"/>
@@ -19277,34 +19378,18 @@
       <c r="EN70" t="inlineStr"/>
       <c r="EO70" t="inlineStr"/>
       <c r="EP70" t="inlineStr"/>
-      <c r="EQ70" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="ER70" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="EQ70" t="inlineStr"/>
+      <c r="ER70" t="inlineStr"/>
       <c r="ES70" t="inlineStr"/>
       <c r="ET70" t="inlineStr"/>
       <c r="EU70" t="inlineStr"/>
-      <c r="EV70" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW70" t="inlineStr">
-        <is>
-          <t>fixedcapacity</t>
-        </is>
-      </c>
-      <c r="EX70" t="n">
-        <v>650</v>
-      </c>
-      <c r="EY70" t="n">
-        <v>650</v>
-      </c>
-      <c r="EZ70" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV70" t="inlineStr"/>
+      <c r="EW70" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="EX70" t="inlineStr"/>
+      <c r="EY70" t="inlineStr"/>
+      <c r="EZ70" t="inlineStr"/>
       <c r="FA70" t="n">
         <v>0</v>
       </c>
@@ -19478,12 +19563,28 @@
       <c r="BZ71" t="n">
         <v>0</v>
       </c>
-      <c r="CA71" t="inlineStr"/>
-      <c r="CB71" t="inlineStr"/>
-      <c r="CC71" t="inlineStr"/>
-      <c r="CD71" t="inlineStr"/>
-      <c r="CE71" t="inlineStr"/>
-      <c r="CF71" t="inlineStr"/>
+      <c r="CA71" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB71" t="inlineStr">
+        <is>
+          <t>fixedcapacity</t>
+        </is>
+      </c>
+      <c r="CC71" t="n">
+        <v>250</v>
+      </c>
+      <c r="CD71" t="n">
+        <v>250</v>
+      </c>
+      <c r="CE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF71" t="n">
+        <v>0</v>
+      </c>
       <c r="CG71" t="inlineStr"/>
       <c r="CH71" t="inlineStr"/>
       <c r="CI71" t="inlineStr"/>
@@ -19547,31 +19648,15 @@
       <c r="EO71" t="inlineStr"/>
       <c r="EP71" t="inlineStr"/>
       <c r="EQ71" t="inlineStr"/>
-      <c r="ER71" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER71" t="inlineStr"/>
       <c r="ES71" t="inlineStr"/>
       <c r="ET71" t="inlineStr"/>
       <c r="EU71" t="inlineStr"/>
-      <c r="EV71" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW71" t="inlineStr">
-        <is>
-          <t>fixedcapacity</t>
-        </is>
-      </c>
-      <c r="EX71" t="n">
-        <v>250</v>
-      </c>
-      <c r="EY71" t="n">
-        <v>250</v>
-      </c>
-      <c r="EZ71" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV71" t="inlineStr"/>
+      <c r="EW71" t="inlineStr"/>
+      <c r="EX71" t="inlineStr"/>
+      <c r="EY71" t="inlineStr"/>
+      <c r="EZ71" t="inlineStr"/>
       <c r="FA71" t="n">
         <v>0</v>
       </c>
@@ -19745,12 +19830,28 @@
       <c r="BZ72" t="n">
         <v>0</v>
       </c>
-      <c r="CA72" t="inlineStr"/>
-      <c r="CB72" t="inlineStr"/>
-      <c r="CC72" t="inlineStr"/>
-      <c r="CD72" t="inlineStr"/>
-      <c r="CE72" t="inlineStr"/>
-      <c r="CF72" t="inlineStr"/>
+      <c r="CA72" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB72" t="inlineStr">
+        <is>
+          <t>fixedcapacity</t>
+        </is>
+      </c>
+      <c r="CC72" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CD72" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF72" t="n">
+        <v>0</v>
+      </c>
       <c r="CG72" t="inlineStr"/>
       <c r="CH72" t="inlineStr"/>
       <c r="CI72" t="inlineStr"/>
@@ -19814,31 +19915,15 @@
       <c r="EO72" t="inlineStr"/>
       <c r="EP72" t="inlineStr"/>
       <c r="EQ72" t="inlineStr"/>
-      <c r="ER72" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER72" t="inlineStr"/>
       <c r="ES72" t="inlineStr"/>
       <c r="ET72" t="inlineStr"/>
       <c r="EU72" t="inlineStr"/>
-      <c r="EV72" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW72" t="inlineStr">
-        <is>
-          <t>fixedcapacity</t>
-        </is>
-      </c>
-      <c r="EX72" t="n">
-        <v>1500</v>
-      </c>
-      <c r="EY72" t="n">
-        <v>1500</v>
-      </c>
-      <c r="EZ72" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV72" t="inlineStr"/>
+      <c r="EW72" t="inlineStr"/>
+      <c r="EX72" t="inlineStr"/>
+      <c r="EY72" t="inlineStr"/>
+      <c r="EZ72" t="inlineStr"/>
       <c r="FA72" t="n">
         <v>0</v>
       </c>
@@ -20012,12 +20097,28 @@
       <c r="BZ73" t="n">
         <v>0</v>
       </c>
-      <c r="CA73" t="inlineStr"/>
-      <c r="CB73" t="inlineStr"/>
-      <c r="CC73" t="inlineStr"/>
-      <c r="CD73" t="inlineStr"/>
-      <c r="CE73" t="inlineStr"/>
-      <c r="CF73" t="inlineStr"/>
+      <c r="CA73" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB73" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CD73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF73" t="n">
+        <v>0</v>
+      </c>
       <c r="CG73" t="inlineStr"/>
       <c r="CH73" t="inlineStr"/>
       <c r="CI73" t="inlineStr"/>
@@ -20080,35 +20181,19 @@
       <c r="EN73" t="inlineStr"/>
       <c r="EO73" t="inlineStr"/>
       <c r="EP73" t="inlineStr"/>
-      <c r="EQ73" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="ER73" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="EQ73" t="inlineStr"/>
+      <c r="ER73" t="inlineStr"/>
       <c r="ES73" t="inlineStr"/>
       <c r="ET73" t="inlineStr"/>
       <c r="EU73" t="inlineStr"/>
       <c r="EV73" t="inlineStr"/>
-      <c r="EW73" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX73" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="EY73" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="EZ73" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA73" t="n">
-        <v>0</v>
-      </c>
+      <c r="EW73" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="EX73" t="inlineStr"/>
+      <c r="EY73" t="inlineStr"/>
+      <c r="EZ73" t="inlineStr"/>
+      <c r="FA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -20279,12 +20364,28 @@
       <c r="BZ74" t="n">
         <v>0.0005</v>
       </c>
-      <c r="CA74" t="inlineStr"/>
-      <c r="CB74" t="inlineStr"/>
-      <c r="CC74" t="inlineStr"/>
-      <c r="CD74" t="inlineStr"/>
-      <c r="CE74" t="inlineStr"/>
-      <c r="CF74" t="inlineStr"/>
+      <c r="CA74" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB74" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC74" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CD74" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF74" t="n">
+        <v>0</v>
+      </c>
       <c r="CG74" t="inlineStr"/>
       <c r="CH74" t="inlineStr"/>
       <c r="CI74" t="inlineStr"/>
@@ -20348,32 +20449,16 @@
       <c r="EO74" t="inlineStr"/>
       <c r="EP74" t="inlineStr"/>
       <c r="EQ74" t="inlineStr"/>
-      <c r="ER74" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER74" t="inlineStr"/>
       <c r="ES74" t="inlineStr"/>
       <c r="ET74" t="inlineStr"/>
       <c r="EU74" t="inlineStr"/>
       <c r="EV74" t="inlineStr"/>
-      <c r="EW74" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX74" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="EY74" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="EZ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA74" t="n">
-        <v>0</v>
-      </c>
+      <c r="EW74" t="inlineStr"/>
+      <c r="EX74" t="inlineStr"/>
+      <c r="EY74" t="inlineStr"/>
+      <c r="EZ74" t="inlineStr"/>
+      <c r="FA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -20544,12 +20629,28 @@
       <c r="BZ75" t="n">
         <v>0</v>
       </c>
-      <c r="CA75" t="inlineStr"/>
-      <c r="CB75" t="inlineStr"/>
-      <c r="CC75" t="inlineStr"/>
-      <c r="CD75" t="inlineStr"/>
-      <c r="CE75" t="inlineStr"/>
-      <c r="CF75" t="inlineStr"/>
+      <c r="CA75" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB75" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
       <c r="CG75" t="inlineStr"/>
       <c r="CH75" t="inlineStr"/>
       <c r="CI75" t="inlineStr"/>
@@ -20613,32 +20714,16 @@
       <c r="EO75" t="inlineStr"/>
       <c r="EP75" t="inlineStr"/>
       <c r="EQ75" t="inlineStr"/>
-      <c r="ER75" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER75" t="inlineStr"/>
       <c r="ES75" t="inlineStr"/>
       <c r="ET75" t="inlineStr"/>
       <c r="EU75" t="inlineStr"/>
       <c r="EV75" t="inlineStr"/>
-      <c r="EW75" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX75" t="n">
-        <v>1</v>
-      </c>
-      <c r="EY75" t="n">
-        <v>1</v>
-      </c>
-      <c r="EZ75" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA75" t="n">
-        <v>0</v>
-      </c>
+      <c r="EW75" t="inlineStr"/>
+      <c r="EX75" t="inlineStr"/>
+      <c r="EY75" t="inlineStr"/>
+      <c r="EZ75" t="inlineStr"/>
+      <c r="FA75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -20809,12 +20894,28 @@
       <c r="BZ76" t="n">
         <v>0</v>
       </c>
-      <c r="CA76" t="inlineStr"/>
-      <c r="CB76" t="inlineStr"/>
-      <c r="CC76" t="inlineStr"/>
-      <c r="CD76" t="inlineStr"/>
-      <c r="CE76" t="inlineStr"/>
-      <c r="CF76" t="inlineStr"/>
+      <c r="CA76" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB76" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
       <c r="CG76" t="inlineStr"/>
       <c r="CH76" t="inlineStr"/>
       <c r="CI76" t="inlineStr"/>
@@ -20878,32 +20979,16 @@
       <c r="EO76" t="inlineStr"/>
       <c r="EP76" t="inlineStr"/>
       <c r="EQ76" t="inlineStr"/>
-      <c r="ER76" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER76" t="inlineStr"/>
       <c r="ES76" t="inlineStr"/>
       <c r="ET76" t="inlineStr"/>
       <c r="EU76" t="inlineStr"/>
       <c r="EV76" t="inlineStr"/>
-      <c r="EW76" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX76" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="EY76" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="EZ76" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA76" t="n">
-        <v>0</v>
-      </c>
+      <c r="EW76" t="inlineStr"/>
+      <c r="EX76" t="inlineStr"/>
+      <c r="EY76" t="inlineStr"/>
+      <c r="EZ76" t="inlineStr"/>
+      <c r="FA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21074,12 +21159,28 @@
       <c r="BZ77" t="n">
         <v>0</v>
       </c>
-      <c r="CA77" t="inlineStr"/>
-      <c r="CB77" t="inlineStr"/>
-      <c r="CC77" t="inlineStr"/>
-      <c r="CD77" t="inlineStr"/>
-      <c r="CE77" t="inlineStr"/>
-      <c r="CF77" t="inlineStr"/>
+      <c r="CA77" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB77" t="inlineStr">
+        <is>
+          <t>fixedcapacity</t>
+        </is>
+      </c>
+      <c r="CC77" t="n">
+        <v>250</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>250</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>0</v>
+      </c>
       <c r="CG77" t="inlineStr"/>
       <c r="CH77" t="inlineStr"/>
       <c r="CI77" t="inlineStr"/>
@@ -21143,31 +21244,15 @@
       <c r="EO77" t="inlineStr"/>
       <c r="EP77" t="inlineStr"/>
       <c r="EQ77" t="inlineStr"/>
-      <c r="ER77" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER77" t="inlineStr"/>
       <c r="ES77" t="inlineStr"/>
       <c r="ET77" t="inlineStr"/>
       <c r="EU77" t="inlineStr"/>
-      <c r="EV77" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW77" t="inlineStr">
-        <is>
-          <t>fixedcapacity</t>
-        </is>
-      </c>
-      <c r="EX77" t="n">
-        <v>250</v>
-      </c>
-      <c r="EY77" t="n">
-        <v>250</v>
-      </c>
-      <c r="EZ77" t="n">
-        <v>0</v>
-      </c>
+      <c r="EV77" t="inlineStr"/>
+      <c r="EW77" t="inlineStr"/>
+      <c r="EX77" t="inlineStr"/>
+      <c r="EY77" t="inlineStr"/>
+      <c r="EZ77" t="inlineStr"/>
       <c r="FA77" t="n">
         <v>0</v>
       </c>
@@ -21333,12 +21418,28 @@
       <c r="BZ78" t="n">
         <v>0</v>
       </c>
-      <c r="CA78" t="inlineStr"/>
-      <c r="CB78" t="inlineStr"/>
-      <c r="CC78" t="inlineStr"/>
-      <c r="CD78" t="inlineStr"/>
-      <c r="CE78" t="inlineStr"/>
-      <c r="CF78" t="inlineStr"/>
+      <c r="CA78" t="inlineStr">
+        <is>
+          <t>determines the relation between the storage capacity and the flow capacity</t>
+        </is>
+      </c>
+      <c r="CB78" t="inlineStr">
+        <is>
+          <t>fixedratio</t>
+        </is>
+      </c>
+      <c r="CC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>0</v>
+      </c>
       <c r="CG78" t="inlineStr"/>
       <c r="CH78" t="inlineStr"/>
       <c r="CI78" t="inlineStr"/>
@@ -21402,48 +21503,32 @@
       <c r="EO78" t="inlineStr"/>
       <c r="EP78" t="inlineStr"/>
       <c r="EQ78" t="inlineStr"/>
-      <c r="ER78" t="inlineStr">
-        <is>
-          <t>determines the flexibility of the power capacity compared to the energy capacity</t>
-        </is>
-      </c>
+      <c r="ER78" t="inlineStr"/>
       <c r="ES78" t="inlineStr"/>
       <c r="ET78" t="inlineStr"/>
       <c r="EU78" t="inlineStr"/>
       <c r="EV78" t="inlineStr"/>
-      <c r="EW78" t="inlineStr">
-        <is>
-          <t>fixedratio</t>
-        </is>
-      </c>
-      <c r="EX78" t="n">
-        <v>1</v>
-      </c>
-      <c r="EY78" t="n">
-        <v>1</v>
-      </c>
-      <c r="EZ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA78" t="n">
-        <v>0</v>
-      </c>
+      <c r="EW78" t="inlineStr"/>
+      <c r="EX78" t="inlineStr"/>
+      <c r="EY78" t="inlineStr"/>
+      <c r="EZ78" t="inlineStr"/>
+      <c r="FA78" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="EW1:FA1"/>
+    <mergeCell ref="BJ1:BZ1"/>
+    <mergeCell ref="CA1:CF1"/>
     <mergeCell ref="R1:AN1"/>
     <mergeCell ref="AW1:BB1"/>
     <mergeCell ref="AT1:AV1"/>
     <mergeCell ref="AO1:AQ1"/>
-    <mergeCell ref="DO1:DU1"/>
-    <mergeCell ref="DV1:EO1"/>
-    <mergeCell ref="CB1:CF1"/>
-    <mergeCell ref="ER1:EU1"/>
-    <mergeCell ref="BJ1:CA1"/>
+    <mergeCell ref="EB1:EU1"/>
+    <mergeCell ref="DU1:EA1"/>
+    <mergeCell ref="CH1:CL1"/>
     <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="CG1:DN1"/>
+    <mergeCell ref="CM1:DT1"/>
     <mergeCell ref="BE1:BH1"/>
+    <mergeCell ref="EX1:EZ1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
